--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -22486,7 +22486,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="D962" t="n">
-        <v>24.8999996185303</v>
+        <v>24.6499996185303</v>
       </c>
       <c r="E962" t="n">
         <v>25.1000003814697</v>
@@ -22495,6 +22495,29 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G962" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B963" t="n">
+        <v>42957</v>
+      </c>
+      <c r="C963" t="n">
+        <v>25.5499992370605</v>
+      </c>
+      <c r="D963" t="n">
+        <v>24.4500007629395</v>
+      </c>
+      <c r="E963" t="n">
+        <v>24.6499996185303</v>
+      </c>
+      <c r="F963" t="n">
+        <v>24.5499992370605</v>
+      </c>
+      <c r="G963" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -22521,6 +22521,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="964">
+      <c r="A964" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B964" t="n">
+        <v>37383</v>
+      </c>
+      <c r="C964" t="n">
+        <v>25.4500007629395</v>
+      </c>
+      <c r="D964" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E964" t="n">
+        <v>24.8500003814697</v>
+      </c>
+      <c r="F964" t="n">
+        <v>25</v>
+      </c>
+      <c r="G964" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -22544,6 +22544,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="965">
+      <c r="A965" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B965" t="n">
+        <v>40071</v>
+      </c>
+      <c r="C965" t="n">
+        <v>26.0499992370605</v>
+      </c>
+      <c r="D965" t="n">
+        <v>25</v>
+      </c>
+      <c r="E965" t="n">
+        <v>25.2999992370605</v>
+      </c>
+      <c r="F965" t="n">
+        <v>25.7000007629395</v>
+      </c>
+      <c r="G965" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -22567,6 +22567,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="966">
+      <c r="A966" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B966" t="n">
+        <v>37192</v>
+      </c>
+      <c r="C966" t="n">
+        <v>26.1499996185303</v>
+      </c>
+      <c r="D966" t="n">
+        <v>25.3500003814697</v>
+      </c>
+      <c r="E966" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F966" t="n">
+        <v>25.2000007629395</v>
+      </c>
+      <c r="G966" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -22408,22 +22408,22 @@
     </row>
     <row r="959">
       <c r="A959" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B959" t="n">
-        <v>55457</v>
+        <v>54392</v>
       </c>
       <c r="C959" t="n">
-        <v>24.5499992370605</v>
+        <v>24.8500003814697</v>
       </c>
       <c r="D959" t="n">
-        <v>23.1000003814697</v>
+        <v>24.3500003814697</v>
       </c>
       <c r="E959" t="n">
-        <v>24.25</v>
+        <v>24.6000003814697</v>
       </c>
       <c r="F959" t="n">
-        <v>24.5499992370605</v>
+        <v>24.4500007629395</v>
       </c>
       <c r="G959" t="s">
         <v>7</v>
@@ -22431,22 +22431,22 @@
     </row>
     <row r="960">
       <c r="A960" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B960" t="n">
-        <v>34472</v>
+        <v>55457</v>
       </c>
       <c r="C960" t="n">
-        <v>25.2000007629395</v>
+        <v>24.5499992370605</v>
       </c>
       <c r="D960" t="n">
-        <v>24.0499992370605</v>
+        <v>23.1000003814697</v>
       </c>
       <c r="E960" t="n">
-        <v>24.8500003814697</v>
+        <v>24.25</v>
       </c>
       <c r="F960" t="n">
-        <v>24.7999992370605</v>
+        <v>24.5499992370605</v>
       </c>
       <c r="G960" t="s">
         <v>7</v>
@@ -22454,22 +22454,22 @@
     </row>
     <row r="961">
       <c r="A961" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B961" t="n">
-        <v>50614</v>
+        <v>34472</v>
       </c>
       <c r="C961" t="n">
-        <v>26</v>
+        <v>25.2000007629395</v>
       </c>
       <c r="D961" t="n">
+        <v>24.0499992370605</v>
+      </c>
+      <c r="E961" t="n">
         <v>24.8500003814697</v>
       </c>
-      <c r="E961" t="n">
-        <v>25.1000003814697</v>
-      </c>
       <c r="F961" t="n">
-        <v>25</v>
+        <v>24.7999992370605</v>
       </c>
       <c r="G961" t="s">
         <v>7</v>
@@ -22477,22 +22477,22 @@
     </row>
     <row r="962">
       <c r="A962" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B962" t="n">
-        <v>41283</v>
+        <v>50614</v>
       </c>
       <c r="C962" t="n">
-        <v>25.7999992370605</v>
+        <v>26</v>
       </c>
       <c r="D962" t="n">
-        <v>24.6499996185303</v>
+        <v>24.8500003814697</v>
       </c>
       <c r="E962" t="n">
         <v>25.1000003814697</v>
       </c>
       <c r="F962" t="n">
-        <v>24.6499996185303</v>
+        <v>25</v>
       </c>
       <c r="G962" t="s">
         <v>7</v>
@@ -22500,22 +22500,22 @@
     </row>
     <row r="963">
       <c r="A963" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B963" t="n">
-        <v>42957</v>
+        <v>41283</v>
       </c>
       <c r="C963" t="n">
-        <v>25.5499992370605</v>
+        <v>25.7999992370605</v>
       </c>
       <c r="D963" t="n">
-        <v>24.4500007629395</v>
+        <v>24.6499996185303</v>
       </c>
       <c r="E963" t="n">
+        <v>25.1000003814697</v>
+      </c>
+      <c r="F963" t="n">
         <v>24.6499996185303</v>
-      </c>
-      <c r="F963" t="n">
-        <v>24.5499992370605</v>
       </c>
       <c r="G963" t="s">
         <v>7</v>
@@ -22523,22 +22523,22 @@
     </row>
     <row r="964">
       <c r="A964" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B964" t="n">
-        <v>37383</v>
+        <v>42957</v>
       </c>
       <c r="C964" t="n">
-        <v>25.4500007629395</v>
+        <v>25.5499992370605</v>
       </c>
       <c r="D964" t="n">
-        <v>24.5</v>
+        <v>24.4500007629395</v>
       </c>
       <c r="E964" t="n">
-        <v>24.8500003814697</v>
+        <v>24.6499996185303</v>
       </c>
       <c r="F964" t="n">
-        <v>25</v>
+        <v>24.5499992370605</v>
       </c>
       <c r="G964" t="s">
         <v>7</v>
@@ -22546,22 +22546,22 @@
     </row>
     <row r="965">
       <c r="A965" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B965" t="n">
-        <v>40071</v>
+        <v>37383</v>
       </c>
       <c r="C965" t="n">
-        <v>26.0499992370605</v>
+        <v>25.4500007629395</v>
       </c>
       <c r="D965" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E965" t="n">
+        <v>24.8500003814697</v>
+      </c>
+      <c r="F965" t="n">
         <v>25</v>
-      </c>
-      <c r="E965" t="n">
-        <v>25.2999992370605</v>
-      </c>
-      <c r="F965" t="n">
-        <v>25.7000007629395</v>
       </c>
       <c r="G965" t="s">
         <v>7</v>
@@ -22569,24 +22569,47 @@
     </row>
     <row r="966">
       <c r="A966" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B966" t="n">
-        <v>37192</v>
+        <v>40071</v>
       </c>
       <c r="C966" t="n">
-        <v>26.1499996185303</v>
+        <v>26.0499992370605</v>
       </c>
       <c r="D966" t="n">
+        <v>25</v>
+      </c>
+      <c r="E966" t="n">
+        <v>25.2999992370605</v>
+      </c>
+      <c r="F966" t="n">
+        <v>25.7000007629395</v>
+      </c>
+      <c r="G966" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B967" t="n">
+        <v>34620</v>
+      </c>
+      <c r="C967" t="n">
         <v>25.3500003814697</v>
       </c>
-      <c r="E966" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="F966" t="n">
-        <v>25.2000007629395</v>
-      </c>
-      <c r="G966" t="s">
+      <c r="D967" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="E967" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="F967" t="n">
+        <v>25.1000003814697</v>
+      </c>
+      <c r="G967" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -473,7 +473,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G4" t="n">
-        <v>8.13956832885742</v>
+        <v>8.13956737518311</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G6" t="n">
-        <v>8.18784523010254</v>
+        <v>8.18784427642822</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G7" t="n">
-        <v>8.08163547515869</v>
+        <v>8.08163452148438</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G9" t="n">
-        <v>8.10094547271729</v>
+        <v>8.1009464263916</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G13" t="n">
-        <v>8.18784523010254</v>
+        <v>8.18784427642822</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G17" t="n">
-        <v>7.94645738601685</v>
+        <v>7.946457862854</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G18" t="n">
-        <v>8.17818927764893</v>
+        <v>8.17819023132324</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G19" t="n">
-        <v>8.13956832885742</v>
+        <v>8.13956737518311</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G20" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G21" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G23" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G25" t="n">
-        <v>8.17818927764893</v>
+        <v>8.17819023132324</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G27" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G30" t="n">
-        <v>8.10094547271729</v>
+        <v>8.1009464263916</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G31" t="n">
-        <v>8.10094547271729</v>
+        <v>8.1009464263916</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G44" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G45" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G48" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G51" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G52" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G54" t="n">
-        <v>8.13956832885742</v>
+        <v>8.13956737518311</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G56" t="n">
-        <v>7.98508071899414</v>
+        <v>7.9850811958313</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G59" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G60" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>8.25543403625488</v>
+        <v>8.25543308258057</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.5</v>
       </c>
       <c r="G64" t="n">
-        <v>8.20715618133545</v>
+        <v>8.20715522766113</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G65" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G66" t="n">
-        <v>8.13956832885742</v>
+        <v>8.13956737518311</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G67" t="n">
-        <v>8.12025547027588</v>
+        <v>8.1202564239502</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G69" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G71" t="n">
-        <v>8.12991237640381</v>
+        <v>8.12991142272949</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G73" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G74" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G75" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G78" t="n">
-        <v>8.12025547027588</v>
+        <v>8.1202564239502</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G80" t="n">
-        <v>7.98508071899414</v>
+        <v>7.9850811958313</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G84" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G85" t="n">
-        <v>8.08163547515869</v>
+        <v>8.08163452148438</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>8.08163547515869</v>
+        <v>8.08163452148438</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G87" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G88" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G89" t="n">
-        <v>7.98508071899414</v>
+        <v>7.9850811958313</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G90" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G92" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G93" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G94" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G98" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>7.70507097244263</v>
+        <v>7.70507144927979</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>7.70507097244263</v>
+        <v>7.70507144927979</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8</v>
       </c>
       <c r="G105" t="n">
-        <v>7.7243824005127</v>
+        <v>7.72438192367554</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>8</v>
       </c>
       <c r="G106" t="n">
-        <v>7.7243824005127</v>
+        <v>7.72438192367554</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>7.6278281211853</v>
+        <v>7.62782764434814</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8</v>
       </c>
       <c r="G109" t="n">
-        <v>7.7243824005127</v>
+        <v>7.72438192367554</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G113" t="n">
-        <v>8.18784523010254</v>
+        <v>8.18784427642822</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.5</v>
       </c>
       <c r="G116" t="n">
-        <v>8.20715618133545</v>
+        <v>8.20715522766113</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G126" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G137" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G141" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G142" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G143" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G152" t="n">
-        <v>8.38095569610596</v>
+        <v>8.38095474243164</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G161" t="n">
-        <v>8.22646713256836</v>
+        <v>8.22646808624268</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G162" t="n">
-        <v>8.22646713256836</v>
+        <v>8.22646808624268</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>8.5</v>
       </c>
       <c r="G164" t="n">
-        <v>8.20715618133545</v>
+        <v>8.20715522766113</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G170" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G173" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G174" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G176" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G181" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G183" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G189" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G190" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G197" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G198" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G199" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G202" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>8</v>
       </c>
       <c r="G203" t="n">
-        <v>7.7243824005127</v>
+        <v>7.72438192367554</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G208" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G210" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G212" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G217" t="n">
-        <v>8.18784523010254</v>
+        <v>8.18784427642822</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G218" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G220" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G222" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G226" t="n">
-        <v>8.18784523010254</v>
+        <v>8.18784427642822</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G229" t="n">
-        <v>8.12991237640381</v>
+        <v>8.12991142272949</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G230" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G231" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G236" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G238" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G239" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G243" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G246" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G251" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G252" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G255" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G261" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>8</v>
       </c>
       <c r="G271" t="n">
-        <v>7.7243824005127</v>
+        <v>7.72438192367554</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G273" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G278" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G283" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G285" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G286" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G287" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G289" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G293" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>8.5</v>
       </c>
       <c r="G294" t="n">
-        <v>8.20715618133545</v>
+        <v>8.20715522766113</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G304" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G306" t="n">
-        <v>8.38095569610596</v>
+        <v>8.38095474243164</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G308" t="n">
-        <v>8.70924186706543</v>
+        <v>8.70924091339111</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G310" t="n">
-        <v>8.92166042327881</v>
+        <v>8.92166137695312</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G313" t="n">
-        <v>8.70924186706543</v>
+        <v>8.70924091339111</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G316" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G323" t="n">
-        <v>8.38095569610596</v>
+        <v>8.38095474243164</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>8.72855186462402</v>
+        <v>8.72855281829834</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G337" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G342" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G343" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G344" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G348" t="n">
-        <v>8.76717472076416</v>
+        <v>8.76717376708984</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G349" t="n">
-        <v>8.70924186706543</v>
+        <v>8.70924091339111</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G355" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G356" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G358" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G363" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G365" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G372" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -25566,6 +25566,32 @@
         <v>25.2000007629395</v>
       </c>
       <c r="H969" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B970" t="n">
+        <v>31663</v>
+      </c>
+      <c r="C970" t="n">
+        <v>25.5499992370605</v>
+      </c>
+      <c r="D970" t="n">
+        <v>24.8500003814697</v>
+      </c>
+      <c r="E970" t="n">
+        <v>25.0499992370605</v>
+      </c>
+      <c r="F970" t="n">
+        <v>25.1000003814697</v>
+      </c>
+      <c r="G970" t="n">
+        <v>25.1000003814697</v>
+      </c>
+      <c r="H970" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -421,7 +421,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2" t="n">
-        <v>8.30371189117432</v>
+        <v>8.3037109375</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G4" t="n">
-        <v>8.13956737518311</v>
+        <v>8.13956832885742</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G5" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G8" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G10" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G11" t="n">
-        <v>8.04301357269287</v>
+        <v>8.04301261901855</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>8.25</v>
       </c>
       <c r="G12" t="n">
-        <v>7.96576976776123</v>
+        <v>7.96576881408691</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G15" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G17" t="n">
-        <v>7.946457862854</v>
+        <v>7.94645881652832</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G19" t="n">
-        <v>8.13956737518311</v>
+        <v>8.13956832885742</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G20" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G21" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>8.25</v>
       </c>
       <c r="G22" t="n">
-        <v>7.96576976776123</v>
+        <v>7.96576881408691</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G23" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611429214478</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G24" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G27" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>8.25</v>
       </c>
       <c r="G32" t="n">
-        <v>7.96576976776123</v>
+        <v>7.96576881408691</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G36" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G40" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G41" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G44" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G45" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G48" t="n">
-        <v>7.91749143600464</v>
+        <v>7.9174919128418</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G49" t="n">
-        <v>7.90783596038818</v>
+        <v>7.90783548355103</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G51" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G52" t="n">
-        <v>7.91749143600464</v>
+        <v>7.9174919128418</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G54" t="n">
-        <v>8.13956737518311</v>
+        <v>8.13956832885742</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G56" t="n">
-        <v>7.9850811958313</v>
+        <v>7.98508024215698</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G59" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G60" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G61" t="n">
-        <v>8.30371189117432</v>
+        <v>8.3037109375</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>8.25543308258057</v>
+        <v>8.25543403625488</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G65" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G66" t="n">
-        <v>8.13956737518311</v>
+        <v>8.13956832885742</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G67" t="n">
-        <v>8.1202564239502</v>
+        <v>8.12025737762451</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G68" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G69" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G70" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G71" t="n">
-        <v>8.12991142272949</v>
+        <v>8.12991237640381</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G73" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611429214478</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G74" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611429214478</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G75" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G77" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G78" t="n">
-        <v>8.1202564239502</v>
+        <v>8.12025737762451</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>8.25</v>
       </c>
       <c r="G79" t="n">
-        <v>7.96576976776123</v>
+        <v>7.96576881408691</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G80" t="n">
-        <v>7.9850811958313</v>
+        <v>7.98508024215698</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G82" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G84" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G87" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G88" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G89" t="n">
-        <v>7.9850811958313</v>
+        <v>7.98508024215698</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G90" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G91" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G92" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G93" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G94" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G95" t="n">
-        <v>7.82093715667725</v>
+        <v>7.8209376335144</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>7.70507144927979</v>
+        <v>7.70507097244263</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>7.70507144927979</v>
+        <v>7.70507097244263</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8</v>
       </c>
       <c r="G105" t="n">
-        <v>7.72438192367554</v>
+        <v>7.7243824005127</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>8</v>
       </c>
       <c r="G106" t="n">
-        <v>7.72438192367554</v>
+        <v>7.7243824005127</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8</v>
       </c>
       <c r="G109" t="n">
-        <v>7.72438192367554</v>
+        <v>7.7243824005127</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G112" t="n">
-        <v>7.87886953353882</v>
+        <v>7.87887001037598</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853523254395</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853523254395</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G118" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G119" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G120" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G122" t="n">
-        <v>8.41957759857178</v>
+        <v>8.41957664489746</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G123" t="n">
-        <v>8.30371189117432</v>
+        <v>8.3037109375</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G126" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>8.61268615722656</v>
+        <v>8.61268711090088</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G128" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G130" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G131" t="n">
-        <v>8.30371189117432</v>
+        <v>8.3037109375</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G132" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>8.65130805969238</v>
+        <v>8.65130710601807</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G135" t="n">
-        <v>8.47751045227051</v>
+        <v>8.47750949859619</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G136" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G137" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G141" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G142" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G143" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G144" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G146" t="n">
-        <v>8.34233283996582</v>
+        <v>8.34233379364014</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G150" t="n">
-        <v>8.30371189117432</v>
+        <v>8.3037109375</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G151" t="n">
-        <v>8.34233283996582</v>
+        <v>8.34233379364014</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G152" t="n">
-        <v>8.38095474243164</v>
+        <v>8.38095569610596</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G153" t="n">
-        <v>8.34233283996582</v>
+        <v>8.34233379364014</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G156" t="n">
-        <v>8.41957759857178</v>
+        <v>8.41957664489746</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G157" t="n">
-        <v>8.41957759857178</v>
+        <v>8.41957664489746</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G161" t="n">
-        <v>8.22646808624268</v>
+        <v>8.22646713256836</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G162" t="n">
-        <v>8.22646808624268</v>
+        <v>8.22646713256836</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G166" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G170" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G173" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G174" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611429214478</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G175" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G176" t="n">
-        <v>7.91749143600464</v>
+        <v>7.9174919128418</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G178" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>7.91749143600464</v>
+        <v>7.9174919128418</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G181" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>7.91749143600464</v>
+        <v>7.9174919128418</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G183" t="n">
-        <v>7.91749143600464</v>
+        <v>7.9174919128418</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G185" t="n">
-        <v>7.82093715667725</v>
+        <v>7.8209376335144</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G187" t="n">
-        <v>7.87886953353882</v>
+        <v>7.87887001037598</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>7.82093715667725</v>
+        <v>7.8209376335144</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G189" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G190" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G191" t="n">
-        <v>7.82093715667725</v>
+        <v>7.8209376335144</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G192" t="n">
-        <v>7.82093715667725</v>
+        <v>7.8209376335144</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G194" t="n">
-        <v>7.82093715667725</v>
+        <v>7.8209376335144</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>7.82093715667725</v>
+        <v>7.8209376335144</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G197" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G198" t="n">
-        <v>7.91749143600464</v>
+        <v>7.9174919128418</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G199" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G202" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>8</v>
       </c>
       <c r="G203" t="n">
-        <v>7.72438192367554</v>
+        <v>7.7243824005127</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G208" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G210" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G212" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G214" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G215" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G216" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G218" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853523254395</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G220" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853523254395</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G222" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G223" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853523254395</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G229" t="n">
-        <v>8.12991142272949</v>
+        <v>8.12991237640381</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G230" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G231" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853523254395</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G234" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G236" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G238" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611429214478</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G239" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G243" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G246" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G249" t="n">
-        <v>7.87886953353882</v>
+        <v>7.87887001037598</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G250" t="n">
-        <v>7.87886953353882</v>
+        <v>7.87887001037598</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G251" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G252" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>7.91749143600464</v>
+        <v>7.9174919128418</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G255" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G260" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G261" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G264" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G265" t="n">
-        <v>7.87886953353882</v>
+        <v>7.87887001037598</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>8</v>
       </c>
       <c r="G271" t="n">
-        <v>7.72438192367554</v>
+        <v>7.7243824005127</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G273" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G280" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G282" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G283" t="n">
-        <v>7.91749143600464</v>
+        <v>7.9174919128418</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G284" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G285" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G286" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G287" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G288" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G289" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611429214478</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G291" t="n">
-        <v>7.87886953353882</v>
+        <v>7.87887001037598</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G292" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G293" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G296" t="n">
-        <v>8.30371189117432</v>
+        <v>8.3037109375</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G299" t="n">
-        <v>8.43888759613037</v>
+        <v>8.43888664245605</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G300" t="n">
-        <v>8.61268615722656</v>
+        <v>8.61268711090088</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G303" t="n">
-        <v>8.63199615478516</v>
+        <v>8.63199710845947</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>8.65130805969238</v>
+        <v>8.65130710601807</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G306" t="n">
-        <v>8.38095474243164</v>
+        <v>8.38095569610596</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G307" t="n">
-        <v>8.65130805969238</v>
+        <v>8.65130710601807</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>8.61268615722656</v>
+        <v>8.61268711090088</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G316" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G318" t="n">
-        <v>8.47751045227051</v>
+        <v>8.47750949859619</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G319" t="n">
-        <v>8.41957759857178</v>
+        <v>8.41957664489746</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G323" t="n">
-        <v>8.38095474243164</v>
+        <v>8.38095569610596</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G328" t="n">
-        <v>8.43888759613037</v>
+        <v>8.43888664245605</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>8.72855281829834</v>
+        <v>8.72855186462402</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G336" t="n">
-        <v>8.47751045227051</v>
+        <v>8.47750949859619</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>8.65130805969238</v>
+        <v>8.65130710601807</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G347" t="n">
-        <v>8.65130805969238</v>
+        <v>8.65130710601807</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G354" t="n">
-        <v>8.63199615478516</v>
+        <v>8.63199710845947</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G355" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G356" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>8.65130805969238</v>
+        <v>8.65130710601807</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G358" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G360" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G363" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G365" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G369" t="n">
-        <v>8.47751045227051</v>
+        <v>8.47750949859619</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G370" t="n">
-        <v>8.47751045227051</v>
+        <v>8.47750949859619</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G371" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G378" t="n">
-        <v>8.65484237670898</v>
+        <v>8.6548433303833</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G379" t="n">
-        <v>8.67433452606201</v>
+        <v>8.67433547973633</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G380" t="n">
-        <v>8.5573787689209</v>
+        <v>8.55737781524658</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>8.57687091827393</v>
+        <v>8.57687187194824</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G382" t="n">
-        <v>8.79129314422607</v>
+        <v>8.79129409790039</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G384" t="n">
-        <v>8.67433452606201</v>
+        <v>8.67433547973633</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G387" t="n">
-        <v>8.7133207321167</v>
+        <v>8.71332168579102</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G389" t="n">
-        <v>8.73281383514404</v>
+        <v>8.73281478881836</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>8.73281383514404</v>
+        <v>8.73281478881836</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G391" t="n">
-        <v>8.73281383514404</v>
+        <v>8.73281478881836</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>8.73281383514404</v>
+        <v>8.73281478881836</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>8.73281383514404</v>
+        <v>8.73281478881836</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G394" t="n">
-        <v>8.73281383514404</v>
+        <v>8.73281478881836</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G396" t="n">
-        <v>8.67433452606201</v>
+        <v>8.67433547973633</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G397" t="n">
-        <v>8.73281383514404</v>
+        <v>8.73281478881836</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G419" t="n">
-        <v>8.79129314422607</v>
+        <v>8.79129409790039</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G420" t="n">
-        <v>8.79129314422607</v>
+        <v>8.79129409790039</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G429" t="n">
-        <v>8.94723606109619</v>
+        <v>8.94723701477051</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>8.67433452606201</v>
+        <v>8.67433547973633</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G436" t="n">
-        <v>8.94723606109619</v>
+        <v>8.94723701477051</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G438" t="n">
-        <v>8.98622131347656</v>
+        <v>8.98622226715088</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G439" t="n">
-        <v>8.96672821044922</v>
+        <v>8.96672916412354</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>8.96672821044922</v>
+        <v>8.96672916412354</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>8.96672821044922</v>
+        <v>8.96672916412354</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G445" t="n">
-        <v>9.12267208099365</v>
+        <v>9.12267112731934</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G447" t="n">
-        <v>9.20064353942871</v>
+        <v>9.20064258575439</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G451" t="n">
-        <v>9.51253032684326</v>
+        <v>9.51252937316895</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G452" t="n">
-        <v>9.51253032684326</v>
+        <v>9.51252937316895</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G459" t="n">
-        <v>9.37607955932617</v>
+        <v>9.37607860565186</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G462" t="n">
-        <v>9.37607955932617</v>
+        <v>9.37607860565186</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G463" t="n">
-        <v>9.37607955932617</v>
+        <v>9.37607860565186</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>9.37607955932617</v>
+        <v>9.37607860565186</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G466" t="n">
-        <v>9.29810810089111</v>
+        <v>9.2981071472168</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G468" t="n">
-        <v>9.62948799133301</v>
+        <v>9.62948703765869</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G471" t="n">
-        <v>9.29810810089111</v>
+        <v>9.2981071472168</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>9.5</v>
       </c>
       <c r="G472" t="n">
-        <v>9.25912284851074</v>
+        <v>9.25912189483643</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>9.5</v>
       </c>
       <c r="G477" t="n">
-        <v>9.25912284851074</v>
+        <v>9.25912189483643</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>9.29810810089111</v>
+        <v>9.2981071472168</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G481" t="n">
-        <v>9.59050178527832</v>
+        <v>9.590500831604</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G483" t="n">
-        <v>10.0875701904297</v>
+        <v>10.087571144104</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G484" t="n">
-        <v>10.1850337982178</v>
+        <v>10.1850347518921</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G486" t="n">
-        <v>10.3312320709229</v>
+        <v>10.3312311172485</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G487" t="n">
-        <v>10.3312320709229</v>
+        <v>10.3312311172485</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>10.1850337982178</v>
+        <v>10.1850347518921</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G489" t="n">
-        <v>10.0388383865356</v>
+        <v>10.0388374328613</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>10.3312320709229</v>
+        <v>10.3312311172485</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G493" t="n">
-        <v>10.3312320709229</v>
+        <v>10.3312311172485</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>10.1363010406494</v>
+        <v>10.1363019943237</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>10.1363010406494</v>
+        <v>10.1363019943237</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G498" t="n">
-        <v>10.1363010406494</v>
+        <v>10.1363019943237</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G499" t="n">
-        <v>10.1850337982178</v>
+        <v>10.1850347518921</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>10.0388383865356</v>
+        <v>10.0388374328613</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G502" t="n">
-        <v>10.6723566055298</v>
+        <v>10.6723556518555</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G504" t="n">
-        <v>10.6723566055298</v>
+        <v>10.6723556518555</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G512" t="n">
-        <v>11.013482093811</v>
+        <v>11.0134830474854</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>11.25</v>
       </c>
       <c r="G513" t="n">
-        <v>10.964750289917</v>
+        <v>10.9647493362427</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G522" t="n">
-        <v>11.3058757781982</v>
+        <v>11.3058767318726</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>12</v>
       </c>
       <c r="G525" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>12.0368585586548</v>
+        <v>12.0368595123291</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>12</v>
       </c>
       <c r="G536" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G539" t="n">
-        <v>11.4033393859863</v>
+        <v>11.4033403396606</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G542" t="n">
-        <v>11.4033393859863</v>
+        <v>11.4033403396606</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G546" t="n">
-        <v>11.4033393859863</v>
+        <v>11.4033403396606</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G548" t="n">
-        <v>11.7931985855103</v>
+        <v>11.7931976318359</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>12</v>
       </c>
       <c r="G551" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>12</v>
       </c>
       <c r="G554" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G555" t="n">
-        <v>11.7931985855103</v>
+        <v>11.7931976318359</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>12</v>
       </c>
       <c r="G556" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G557" t="n">
-        <v>11.8906621932983</v>
+        <v>11.890661239624</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>11.7931985855103</v>
+        <v>11.7931976318359</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>12</v>
       </c>
       <c r="G561" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G562" t="n">
-        <v>11.6470003128052</v>
+        <v>11.6470012664795</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>12</v>
       </c>
       <c r="G563" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>11.7931985855103</v>
+        <v>11.7931976318359</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G565" t="n">
-        <v>11.6470003128052</v>
+        <v>11.6470012664795</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G567" t="n">
-        <v>11.7931985855103</v>
+        <v>11.7931976318359</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>11.7931985855103</v>
+        <v>11.7931976318359</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>12</v>
       </c>
       <c r="G572" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G577" t="n">
-        <v>11.8906621932983</v>
+        <v>11.890661239624</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G602" t="n">
-        <v>12.7093639373779</v>
+        <v>12.7093629837036</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G604" t="n">
-        <v>12.6898717880249</v>
+        <v>12.6898708343506</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G606" t="n">
-        <v>12.8653059005737</v>
+        <v>12.865306854248</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G611" t="n">
-        <v>13.3136425018311</v>
+        <v>13.3136434555054</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G616" t="n">
-        <v>13.4500942230225</v>
+        <v>13.4500932693481</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G619" t="n">
-        <v>13.3136425018311</v>
+        <v>13.3136434555054</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G620" t="n">
-        <v>13.3136425018311</v>
+        <v>13.3136434555054</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G622" t="n">
-        <v>13.6255283355713</v>
+        <v>13.6255292892456</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>14.5</v>
       </c>
       <c r="G626" t="n">
-        <v>14.1323442459106</v>
+        <v>14.132345199585</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -25592,6 +25592,32 @@
         <v>25.1000003814697</v>
       </c>
       <c r="H970" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B971" t="n">
+        <v>40205</v>
+      </c>
+      <c r="C971" t="n">
+        <v>25.2999992370605</v>
+      </c>
+      <c r="D971" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E971" t="n">
+        <v>25.2999992370605</v>
+      </c>
+      <c r="F971" t="n">
+        <v>24.6000003814697</v>
+      </c>
+      <c r="G971" t="n">
+        <v>24.6000003814697</v>
+      </c>
+      <c r="H971" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -25621,6 +25621,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="972">
+      <c r="A972" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B972" t="n">
+        <v>41266</v>
+      </c>
+      <c r="C972" t="n">
+        <v>25.6499996185303</v>
+      </c>
+      <c r="D972" t="n">
+        <v>24.6000003814697</v>
+      </c>
+      <c r="E972" t="n">
+        <v>24.6000003814697</v>
+      </c>
+      <c r="F972" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="G972" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="H972" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -25647,6 +25647,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="973">
+      <c r="A973" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B973" t="n">
+        <v>24119</v>
+      </c>
+      <c r="C973" t="n">
+        <v>25.7000007629395</v>
+      </c>
+      <c r="D973" t="n">
+        <v>25.1000003814697</v>
+      </c>
+      <c r="E973" t="n">
+        <v>25.1000003814697</v>
+      </c>
+      <c r="F973" t="n">
+        <v>25.4500007629395</v>
+      </c>
+      <c r="G973" t="n">
+        <v>25.4500007629395</v>
+      </c>
+      <c r="H973" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -473,7 +473,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G4" t="n">
-        <v>8.13956737518311</v>
+        <v>8.13956832885742</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G5" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G6" t="n">
-        <v>8.18784427642822</v>
+        <v>8.18784523010254</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G8" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G9" t="n">
-        <v>8.1009464263916</v>
+        <v>8.10094547271729</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G10" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G13" t="n">
-        <v>8.18784427642822</v>
+        <v>8.18784523010254</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G15" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G16" t="n">
-        <v>8.14922332763672</v>
+        <v>8.1492223739624</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G18" t="n">
-        <v>8.17819023132324</v>
+        <v>8.17818927764893</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G19" t="n">
-        <v>8.13956737518311</v>
+        <v>8.13956832885742</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G20" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G24" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G25" t="n">
-        <v>8.17819023132324</v>
+        <v>8.17818927764893</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G27" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>7.92714643478394</v>
+        <v>7.92714738845825</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G30" t="n">
-        <v>8.1009464263916</v>
+        <v>8.10094547271729</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G31" t="n">
-        <v>8.1009464263916</v>
+        <v>8.10094547271729</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G36" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G37" t="n">
-        <v>8.02370262145996</v>
+        <v>8.02370166778564</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G40" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G41" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G42" t="n">
-        <v>7.92714643478394</v>
+        <v>7.92714738845825</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G46" t="n">
-        <v>7.92714643478394</v>
+        <v>7.92714738845825</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G47" t="n">
-        <v>7.92714643478394</v>
+        <v>7.92714738845825</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G53" t="n">
-        <v>8.03335666656494</v>
+        <v>8.03335762023926</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G54" t="n">
-        <v>8.13956737518311</v>
+        <v>8.13956832885742</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G55" t="n">
-        <v>8.03335666656494</v>
+        <v>8.03335762023926</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>8.25543308258057</v>
+        <v>8.25543403625488</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G63" t="n">
-        <v>8.2650899887085</v>
+        <v>8.26508903503418</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G65" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G66" t="n">
-        <v>8.13956737518311</v>
+        <v>8.13956832885742</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G68" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G70" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G76" t="n">
-        <v>8.14922332763672</v>
+        <v>8.1492223739624</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G77" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G82" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G83" t="n">
-        <v>8.06232357025146</v>
+        <v>8.06232452392578</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G88" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G90" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G91" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G96" t="n">
-        <v>7.78231573104858</v>
+        <v>7.78231525421143</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G97" t="n">
-        <v>7.74369382858276</v>
+        <v>7.74369335174561</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8</v>
       </c>
       <c r="G105" t="n">
-        <v>7.72438192367554</v>
+        <v>7.7243824005127</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>8</v>
       </c>
       <c r="G106" t="n">
-        <v>7.72438192367554</v>
+        <v>7.7243824005127</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8</v>
       </c>
       <c r="G109" t="n">
-        <v>7.72438192367554</v>
+        <v>7.7243824005127</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>7.76300382614136</v>
+        <v>7.76300430297852</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G111" t="n">
-        <v>7.78231573104858</v>
+        <v>7.78231525421143</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G112" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G113" t="n">
-        <v>8.18784427642822</v>
+        <v>8.18784523010254</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G118" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G119" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G120" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G121" t="n">
-        <v>8.2650899887085</v>
+        <v>8.26508903503418</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>8.61268615722656</v>
+        <v>8.61268711090088</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G128" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G130" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G132" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>8.6513090133667</v>
+        <v>8.65130805969238</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G136" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G144" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G160" t="n">
-        <v>8.2650899887085</v>
+        <v>8.26508903503418</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G163" t="n">
-        <v>8.2650899887085</v>
+        <v>8.26508903503418</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G166" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G167" t="n">
-        <v>8.03335666656494</v>
+        <v>8.03335762023926</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G170" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G171" t="n">
-        <v>8.03335666656494</v>
+        <v>8.03335762023926</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G172" t="n">
-        <v>8.03335666656494</v>
+        <v>8.03335762023926</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G175" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G177" t="n">
-        <v>8.03335666656494</v>
+        <v>8.03335762023926</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G178" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G184" t="n">
-        <v>7.84024810791016</v>
+        <v>7.840247631073</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G187" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G193" t="n">
-        <v>7.80162572860718</v>
+        <v>7.80162620544434</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>7.80162572860718</v>
+        <v>7.80162620544434</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G200" t="n">
-        <v>7.84024810791016</v>
+        <v>7.840247631073</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G201" t="n">
-        <v>7.80162572860718</v>
+        <v>7.80162620544434</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>8</v>
       </c>
       <c r="G203" t="n">
-        <v>7.72438192367554</v>
+        <v>7.7243824005127</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G204" t="n">
-        <v>7.76300382614136</v>
+        <v>7.76300430297852</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G205" t="n">
-        <v>7.76300382614136</v>
+        <v>7.76300430297852</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G206" t="n">
-        <v>7.84024810791016</v>
+        <v>7.840247631073</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G207" t="n">
-        <v>7.84024810791016</v>
+        <v>7.840247631073</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G209" t="n">
-        <v>7.80162572860718</v>
+        <v>7.80162620544434</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G211" t="n">
-        <v>7.84024810791016</v>
+        <v>7.840247631073</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G214" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G215" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G216" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G217" t="n">
-        <v>8.18784427642822</v>
+        <v>8.18784523010254</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G219" t="n">
-        <v>8.14922332763672</v>
+        <v>8.1492223739624</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G220" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G222" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G223" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G224" t="n">
-        <v>8.14922332763672</v>
+        <v>8.1492223739624</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G226" t="n">
-        <v>8.18784427642822</v>
+        <v>8.18784523010254</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G230" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G231" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G234" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G236" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G237" t="n">
-        <v>8.03335666656494</v>
+        <v>8.03335762023926</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G240" t="n">
-        <v>7.84024810791016</v>
+        <v>7.840247631073</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G241" t="n">
-        <v>7.84024810791016</v>
+        <v>7.840247631073</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G242" t="n">
-        <v>7.80162572860718</v>
+        <v>7.80162620544434</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G244" t="n">
-        <v>7.80162572860718</v>
+        <v>7.80162620544434</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G245" t="n">
-        <v>7.78231573104858</v>
+        <v>7.78231525421143</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G246" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G247" t="n">
-        <v>8.03335666656494</v>
+        <v>8.03335762023926</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G249" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G250" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G257" t="n">
-        <v>8.03335666656494</v>
+        <v>8.03335762023926</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G258" t="n">
-        <v>8.03335666656494</v>
+        <v>8.03335762023926</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G260" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G262" t="n">
-        <v>8.03335666656494</v>
+        <v>8.03335762023926</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G264" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G265" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G266" t="n">
-        <v>7.76300382614136</v>
+        <v>7.76300430297852</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G267" t="n">
-        <v>7.74369382858276</v>
+        <v>7.74369335174561</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>7.80162572860718</v>
+        <v>7.80162620544434</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G270" t="n">
-        <v>7.74369382858276</v>
+        <v>7.74369335174561</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>8</v>
       </c>
       <c r="G271" t="n">
-        <v>7.72438192367554</v>
+        <v>7.7243824005127</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G274" t="n">
-        <v>7.84024810791016</v>
+        <v>7.840247631073</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G275" t="n">
-        <v>7.84024810791016</v>
+        <v>7.840247631073</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G277" t="n">
-        <v>7.74369382858276</v>
+        <v>7.74369335174561</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G279" t="n">
-        <v>7.76300382614136</v>
+        <v>7.76300430297852</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G280" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G282" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G284" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G285" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G288" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G291" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G292" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G297" t="n">
-        <v>8.2650899887085</v>
+        <v>8.26508903503418</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G300" t="n">
-        <v>8.61268615722656</v>
+        <v>8.61268711090088</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G301" t="n">
-        <v>8.57406520843506</v>
+        <v>8.57406425476074</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>8.6513090133667</v>
+        <v>8.65130805969238</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G307" t="n">
-        <v>8.6513090133667</v>
+        <v>8.65130805969238</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G310" t="n">
-        <v>8.92166137695312</v>
+        <v>8.92166233062744</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>8.61268615722656</v>
+        <v>8.61268711090088</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>8.6513090133667</v>
+        <v>8.65130805969238</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G347" t="n">
-        <v>8.6513090133667</v>
+        <v>8.65130805969238</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>8.6513090133667</v>
+        <v>8.65130805969238</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G360" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>8.57406520843506</v>
+        <v>8.57406425476074</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G371" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -25722,6 +25722,32 @@
         <v>25.3500003814697</v>
       </c>
       <c r="H975" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B976" t="n">
+        <v>21953</v>
+      </c>
+      <c r="C976" t="n">
+        <v>25.6000003814697</v>
+      </c>
+      <c r="D976" t="n">
+        <v>24.9500007629395</v>
+      </c>
+      <c r="E976" t="n">
+        <v>25.2000007629395</v>
+      </c>
+      <c r="F976" t="n">
+        <v>25</v>
+      </c>
+      <c r="G976" t="n">
+        <v>25</v>
+      </c>
+      <c r="H976" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -22882,8 +22882,31 @@
       <c r="E979" t="n">
         <v>23.2999992370605</v>
       </c>
-      <c r="F979"/>
+      <c r="F979" t="n">
+        <v>23.2999992370605</v>
+      </c>
       <c r="G979" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B980" t="n">
+        <v>35737</v>
+      </c>
+      <c r="C980" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="D980" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="E980" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="F980"/>
+      <c r="G980" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -22905,8 +22905,31 @@
       <c r="E980" t="n">
         <v>23.2000007629395</v>
       </c>
-      <c r="F980"/>
+      <c r="F980" t="n">
+        <v>24</v>
+      </c>
       <c r="G980" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B981" t="n">
+        <v>30777</v>
+      </c>
+      <c r="C981" t="n">
+        <v>24.2999992370605</v>
+      </c>
+      <c r="D981" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="E981" t="n">
+        <v>24.1499996185303</v>
+      </c>
+      <c r="F981"/>
+      <c r="G981" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -22928,8 +22928,31 @@
       <c r="E981" t="n">
         <v>24.1499996185303</v>
       </c>
-      <c r="F981"/>
+      <c r="F981" t="n">
+        <v>23.3999996185303</v>
+      </c>
       <c r="G981" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B982" t="n">
+        <v>39311</v>
+      </c>
+      <c r="C982" t="n">
+        <v>23.6499996185303</v>
+      </c>
+      <c r="D982" t="n">
+        <v>22.7000007629395</v>
+      </c>
+      <c r="E982" t="n">
+        <v>23.1000003814697</v>
+      </c>
+      <c r="F982"/>
+      <c r="G982" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -22951,8 +22951,31 @@
       <c r="E982" t="n">
         <v>23.1000003814697</v>
       </c>
-      <c r="F982"/>
+      <c r="F982" t="n">
+        <v>23.6499996185303</v>
+      </c>
       <c r="G982" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B983" t="n">
+        <v>36006</v>
+      </c>
+      <c r="C983" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="D983" t="n">
+        <v>23.3999996185303</v>
+      </c>
+      <c r="E983" t="n">
+        <v>23.3999996185303</v>
+      </c>
+      <c r="F983"/>
+      <c r="G983" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -22981,6 +22981,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="984">
+      <c r="A984" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B984" t="n">
+        <v>19102</v>
+      </c>
+      <c r="C984" t="n">
+        <v>24.0499992370605</v>
+      </c>
+      <c r="D984" t="n">
+        <v>23.7000007629395</v>
+      </c>
+      <c r="E984" t="n">
+        <v>24</v>
+      </c>
+      <c r="F984" t="n">
+        <v>23.9500007629395</v>
+      </c>
+      <c r="G984" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -421,7 +421,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G5" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G7" t="n">
-        <v>8.08163452148438</v>
+        <v>8.08163547515869</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G8" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G9" t="n">
-        <v>8.1009464263916</v>
+        <v>8.10094547271729</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G10" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G15" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G17" t="n">
-        <v>7.94645833969116</v>
+        <v>7.94645738601685</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G18" t="n">
-        <v>8.17819023132324</v>
+        <v>8.17818927764893</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G24" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G25" t="n">
-        <v>8.17819023132324</v>
+        <v>8.17818927764893</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G26" t="n">
-        <v>8.36164283752441</v>
+        <v>8.36164379119873</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G30" t="n">
-        <v>8.1009464263916</v>
+        <v>8.10094547271729</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G31" t="n">
-        <v>8.1009464263916</v>
+        <v>8.10094547271729</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G36" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G45" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85955858230591</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G61" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G67" t="n">
-        <v>8.1202564239502</v>
+        <v>8.12025547027588</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G68" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G69" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G70" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G78" t="n">
-        <v>8.1202564239502</v>
+        <v>8.12025547027588</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G84" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G85" t="n">
-        <v>8.08163452148438</v>
+        <v>8.08163547515869</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>8.08163452148438</v>
+        <v>8.08163547515869</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G91" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G92" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G93" t="n">
-        <v>7.85955858230591</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G94" t="n">
-        <v>7.85955858230591</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G95" t="n">
-        <v>7.8209376335144</v>
+        <v>7.82093715667725</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G107" t="n">
-        <v>7.53127336502075</v>
+        <v>7.53127288818359</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>7.62782764434814</v>
+        <v>7.6278281211853</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G112" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853332519531</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853332519531</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G118" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G119" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G120" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G122" t="n">
-        <v>8.41957664489746</v>
+        <v>8.41957759857178</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G123" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G124" t="n">
-        <v>8.67061996459961</v>
+        <v>8.67061901092529</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G126" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G131" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G135" t="n">
-        <v>8.47750949859619</v>
+        <v>8.47751045227051</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G137" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G141" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G142" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G143" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G145" t="n">
-        <v>8.36164283752441</v>
+        <v>8.36164379119873</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G150" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G156" t="n">
-        <v>8.41957664489746</v>
+        <v>8.41957759857178</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G157" t="n">
-        <v>8.41957664489746</v>
+        <v>8.41957759857178</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G166" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G175" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G185" t="n">
-        <v>7.8209376335144</v>
+        <v>7.82093715667725</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G187" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>7.8209376335144</v>
+        <v>7.82093715667725</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G189" t="n">
-        <v>7.85955858230591</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G190" t="n">
-        <v>7.85955858230591</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G191" t="n">
-        <v>7.8209376335144</v>
+        <v>7.82093715667725</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G192" t="n">
-        <v>7.8209376335144</v>
+        <v>7.82093715667725</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G194" t="n">
-        <v>7.8209376335144</v>
+        <v>7.82093715667725</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>7.8209376335144</v>
+        <v>7.82093715667725</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G197" t="n">
-        <v>7.85955858230591</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G202" t="n">
-        <v>7.85955858230591</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G208" t="n">
-        <v>7.85955858230591</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G210" t="n">
-        <v>7.85955858230591</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G212" t="n">
-        <v>7.85955858230591</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G214" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G215" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G216" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G218" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853332519531</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853332519531</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G223" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853332519531</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853332519531</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G234" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G243" t="n">
-        <v>7.85955858230591</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G249" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G250" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G265" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G273" t="n">
-        <v>7.85955858230591</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G280" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G282" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G284" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G286" t="n">
-        <v>7.85955858230591</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G287" t="n">
-        <v>7.85955858230591</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G291" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G293" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G296" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G299" t="n">
-        <v>8.43888664245605</v>
+        <v>8.43888759613037</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>9</v>
       </c>
       <c r="G302" t="n">
-        <v>8.68993091583252</v>
+        <v>8.6899299621582</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G304" t="n">
-        <v>8.74786376953125</v>
+        <v>8.74786281585693</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G310" t="n">
-        <v>8.92166137695312</v>
+        <v>8.92166042327881</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G316" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G318" t="n">
-        <v>8.47750949859619</v>
+        <v>8.47751045227051</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G319" t="n">
-        <v>8.41957664489746</v>
+        <v>8.41957759857178</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G328" t="n">
-        <v>8.43888664245605</v>
+        <v>8.43888759613037</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G333" t="n">
-        <v>8.67061996459961</v>
+        <v>8.67061901092529</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G336" t="n">
-        <v>8.47750949859619</v>
+        <v>8.47751045227051</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G337" t="n">
-        <v>8.74786376953125</v>
+        <v>8.74786281585693</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G342" t="n">
-        <v>8.74786376953125</v>
+        <v>8.74786281585693</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G343" t="n">
-        <v>8.74786376953125</v>
+        <v>8.74786281585693</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G344" t="n">
-        <v>8.74786376953125</v>
+        <v>8.74786281585693</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>9</v>
       </c>
       <c r="G345" t="n">
-        <v>8.68993091583252</v>
+        <v>8.6899299621582</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>9</v>
       </c>
       <c r="G346" t="n">
-        <v>8.68993091583252</v>
+        <v>8.6899299621582</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>9</v>
       </c>
       <c r="G350" t="n">
-        <v>8.68993091583252</v>
+        <v>8.6899299621582</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>9</v>
       </c>
       <c r="G351" t="n">
-        <v>8.68993091583252</v>
+        <v>8.6899299621582</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>9</v>
       </c>
       <c r="G352" t="n">
-        <v>8.68993091583252</v>
+        <v>8.6899299621582</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G353" t="n">
-        <v>8.67061996459961</v>
+        <v>8.67061901092529</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G355" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G356" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G358" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G363" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G365" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G369" t="n">
-        <v>8.47750949859619</v>
+        <v>8.47751045227051</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G370" t="n">
-        <v>8.47750949859619</v>
+        <v>8.47751045227051</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G372" t="n">
-        <v>8.74786376953125</v>
+        <v>8.74786281585693</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>9</v>
       </c>
       <c r="G373" t="n">
-        <v>8.68993091583252</v>
+        <v>8.6899299621582</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>9</v>
       </c>
       <c r="G374" t="n">
-        <v>8.68993091583252</v>
+        <v>8.6899299621582</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>9</v>
       </c>
       <c r="G375" t="n">
-        <v>8.68993091583252</v>
+        <v>8.6899299621582</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>9</v>
       </c>
       <c r="G376" t="n">
-        <v>8.68993091583252</v>
+        <v>8.6899299621582</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -26008,6 +26008,32 @@
         <v>24.2999992370605</v>
       </c>
       <c r="H986" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B987" t="n">
+        <v>32734</v>
+      </c>
+      <c r="C987" t="n">
+        <v>24.3999996185303</v>
+      </c>
+      <c r="D987" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="E987" t="n">
+        <v>24.1000003814697</v>
+      </c>
+      <c r="F987" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="G987" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="H987" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -473,7 +473,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G4" t="n">
-        <v>8.13956832885742</v>
+        <v>8.13956737518311</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G6" t="n">
-        <v>8.18784523010254</v>
+        <v>8.18784427642822</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G7" t="n">
-        <v>8.08163547515869</v>
+        <v>8.08163452148438</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G9" t="n">
-        <v>8.10094547271729</v>
+        <v>8.1009464263916</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G13" t="n">
-        <v>8.18784523010254</v>
+        <v>8.18784427642822</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G17" t="n">
-        <v>7.94645738601685</v>
+        <v>7.946457862854</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G18" t="n">
-        <v>8.17818927764893</v>
+        <v>8.17819023132324</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G19" t="n">
-        <v>8.13956832885742</v>
+        <v>8.13956737518311</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G20" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G21" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G23" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G25" t="n">
-        <v>8.17818927764893</v>
+        <v>8.17819023132324</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G27" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G30" t="n">
-        <v>8.10094547271729</v>
+        <v>8.1009464263916</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G31" t="n">
-        <v>8.10094547271729</v>
+        <v>8.1009464263916</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G44" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G45" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G48" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G51" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G52" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G54" t="n">
-        <v>8.13956832885742</v>
+        <v>8.13956737518311</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G56" t="n">
-        <v>7.98508071899414</v>
+        <v>7.9850811958313</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G59" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G60" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>8.25543403625488</v>
+        <v>8.25543308258057</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.5</v>
       </c>
       <c r="G64" t="n">
-        <v>8.20715618133545</v>
+        <v>8.20715522766113</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G65" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G66" t="n">
-        <v>8.13956832885742</v>
+        <v>8.13956737518311</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G67" t="n">
-        <v>8.12025547027588</v>
+        <v>8.1202564239502</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G69" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G71" t="n">
-        <v>8.12991237640381</v>
+        <v>8.12991142272949</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G73" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G74" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G75" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G78" t="n">
-        <v>8.12025547027588</v>
+        <v>8.1202564239502</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G80" t="n">
-        <v>7.98508071899414</v>
+        <v>7.9850811958313</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G84" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G85" t="n">
-        <v>8.08163547515869</v>
+        <v>8.08163452148438</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>8.08163547515869</v>
+        <v>8.08163452148438</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G87" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G88" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G89" t="n">
-        <v>7.98508071899414</v>
+        <v>7.9850811958313</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G90" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G92" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G93" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G94" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G98" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>7.70507097244263</v>
+        <v>7.70507144927979</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>7.70507097244263</v>
+        <v>7.70507144927979</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8</v>
       </c>
       <c r="G105" t="n">
-        <v>7.7243824005127</v>
+        <v>7.72438192367554</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>8</v>
       </c>
       <c r="G106" t="n">
-        <v>7.7243824005127</v>
+        <v>7.72438192367554</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>7.6278281211853</v>
+        <v>7.62782764434814</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8</v>
       </c>
       <c r="G109" t="n">
-        <v>7.7243824005127</v>
+        <v>7.72438192367554</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G113" t="n">
-        <v>8.18784523010254</v>
+        <v>8.18784427642822</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.5</v>
       </c>
       <c r="G116" t="n">
-        <v>8.20715618133545</v>
+        <v>8.20715522766113</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G126" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G137" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G141" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G142" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G143" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G152" t="n">
-        <v>8.38095569610596</v>
+        <v>8.38095474243164</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G161" t="n">
-        <v>8.22646713256836</v>
+        <v>8.22646808624268</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G162" t="n">
-        <v>8.22646713256836</v>
+        <v>8.22646808624268</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>8.5</v>
       </c>
       <c r="G164" t="n">
-        <v>8.20715618133545</v>
+        <v>8.20715522766113</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G170" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G173" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G174" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G176" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G181" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G183" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G189" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G190" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G197" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G198" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G199" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G202" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>8</v>
       </c>
       <c r="G203" t="n">
-        <v>7.7243824005127</v>
+        <v>7.72438192367554</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G208" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G210" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G212" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G217" t="n">
-        <v>8.18784523010254</v>
+        <v>8.18784427642822</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G218" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G220" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G222" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G226" t="n">
-        <v>8.18784523010254</v>
+        <v>8.18784427642822</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G229" t="n">
-        <v>8.12991237640381</v>
+        <v>8.12991142272949</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G230" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G231" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G236" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G238" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G239" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G243" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G246" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G251" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G252" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G255" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G261" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>8</v>
       </c>
       <c r="G271" t="n">
-        <v>7.7243824005127</v>
+        <v>7.72438192367554</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G273" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G278" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G283" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G285" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G286" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G287" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G289" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G293" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>8.5</v>
       </c>
       <c r="G294" t="n">
-        <v>8.20715618133545</v>
+        <v>8.20715522766113</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G304" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G306" t="n">
-        <v>8.38095569610596</v>
+        <v>8.38095474243164</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G308" t="n">
-        <v>8.70924186706543</v>
+        <v>8.70924091339111</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G310" t="n">
-        <v>8.92166042327881</v>
+        <v>8.92166137695312</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G313" t="n">
-        <v>8.70924186706543</v>
+        <v>8.70924091339111</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G316" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G323" t="n">
-        <v>8.38095569610596</v>
+        <v>8.38095474243164</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>8.72855186462402</v>
+        <v>8.72855281829834</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G337" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G342" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G343" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G344" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G348" t="n">
-        <v>8.76717472076416</v>
+        <v>8.76717376708984</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G349" t="n">
-        <v>8.70924186706543</v>
+        <v>8.70924091339111</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G355" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G356" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G358" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G363" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G365" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G372" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -26016,7 +26016,7 @@
         <v>46310.2916666667</v>
       </c>
       <c r="B987" t="n">
-        <v>32734</v>
+        <v>32959</v>
       </c>
       <c r="C987" t="n">
         <v>24.3999996185303</v>
@@ -26034,6 +26034,32 @@
         <v>24.25</v>
       </c>
       <c r="H987" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B988" t="n">
+        <v>23591</v>
+      </c>
+      <c r="C988" t="n">
+        <v>24.5499992370605</v>
+      </c>
+      <c r="D988" t="n">
+        <v>23.4500007629395</v>
+      </c>
+      <c r="E988" t="n">
+        <v>24.1000003814697</v>
+      </c>
+      <c r="F988" t="n">
+        <v>23.5499992370605</v>
+      </c>
+      <c r="G988" t="n">
+        <v>23.5499992370605</v>
+      </c>
+      <c r="H988" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H2" t="n">
         <v>4793</v>
@@ -485,7 +485,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G4" t="n">
-        <v>8.13956832885742</v>
+        <v>8.13956737518311</v>
       </c>
       <c r="H4" t="n">
         <v>6993</v>
@@ -514,7 +514,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G5" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H5" t="n">
         <v>15746</v>
@@ -601,7 +601,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G8" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H8" t="n">
         <v>3358</v>
@@ -659,7 +659,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G10" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H10" t="n">
         <v>6204</v>
@@ -804,7 +804,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G15" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H15" t="n">
         <v>32</v>
@@ -833,7 +833,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G16" t="n">
-        <v>8.1492223739624</v>
+        <v>8.14922332763672</v>
       </c>
       <c r="H16" t="n">
         <v>1934</v>
@@ -862,7 +862,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G17" t="n">
-        <v>7.94645881652832</v>
+        <v>7.946457862854</v>
       </c>
       <c r="H17" t="n">
         <v>2333</v>
@@ -920,7 +920,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G19" t="n">
-        <v>8.13956832885742</v>
+        <v>8.13956737518311</v>
       </c>
       <c r="H19" t="n">
         <v>505</v>
@@ -949,7 +949,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G20" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H20" t="n">
         <v>1660</v>
@@ -978,7 +978,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G21" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H21" t="n">
         <v>2849</v>
@@ -1036,7 +1036,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G23" t="n">
-        <v>7.95611429214478</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H23" t="n">
         <v>480</v>
@@ -1065,7 +1065,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G24" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H24" t="n">
         <v>8168</v>
@@ -1152,7 +1152,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G27" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H27" t="n">
         <v>15457</v>
@@ -1210,7 +1210,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>7.92714738845825</v>
+        <v>7.92714643478394</v>
       </c>
       <c r="H29" t="n">
         <v>5644</v>
@@ -1326,7 +1326,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H33" t="n">
         <v>3280</v>
@@ -1384,7 +1384,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H35" t="n">
         <v>8723</v>
@@ -1413,7 +1413,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G36" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H36" t="n">
         <v>411</v>
@@ -1471,7 +1471,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H38" t="n">
         <v>80</v>
@@ -1500,7 +1500,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H39" t="n">
         <v>559</v>
@@ -1529,7 +1529,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G40" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H40" t="n">
         <v>3659</v>
@@ -1558,7 +1558,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G41" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H41" t="n">
         <v>3082</v>
@@ -1587,7 +1587,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G42" t="n">
-        <v>7.92714738845825</v>
+        <v>7.92714643478394</v>
       </c>
       <c r="H42" t="n">
         <v>8130</v>
@@ -1645,7 +1645,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G44" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H44" t="n">
         <v>15725</v>
@@ -1674,7 +1674,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G45" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H45" t="n">
         <v>8898</v>
@@ -1703,7 +1703,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G46" t="n">
-        <v>7.92714738845825</v>
+        <v>7.92714643478394</v>
       </c>
       <c r="H46" t="n">
         <v>14594</v>
@@ -1732,7 +1732,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G47" t="n">
-        <v>7.92714738845825</v>
+        <v>7.92714643478394</v>
       </c>
       <c r="H47" t="n">
         <v>2940</v>
@@ -1819,7 +1819,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H50" t="n">
         <v>15331</v>
@@ -1848,7 +1848,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G51" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H51" t="n">
         <v>8900</v>
@@ -1906,7 +1906,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G53" t="n">
-        <v>8.03335762023926</v>
+        <v>8.03335666656494</v>
       </c>
       <c r="H53" t="n">
         <v>23431</v>
@@ -1935,7 +1935,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G54" t="n">
-        <v>8.13956832885742</v>
+        <v>8.13956737518311</v>
       </c>
       <c r="H54" t="n">
         <v>24286</v>
@@ -1964,7 +1964,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G55" t="n">
-        <v>8.03335762023926</v>
+        <v>8.03335666656494</v>
       </c>
       <c r="H55" t="n">
         <v>1335</v>
@@ -2022,7 +2022,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H57" t="n">
         <v>1380</v>
@@ -2051,7 +2051,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H58" t="n">
         <v>12623</v>
@@ -2080,7 +2080,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G59" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H59" t="n">
         <v>3310</v>
@@ -2109,7 +2109,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G60" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H60" t="n">
         <v>12417</v>
@@ -2138,7 +2138,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G61" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H61" t="n">
         <v>13315</v>
@@ -2167,7 +2167,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>8.25543403625488</v>
+        <v>8.25543308258057</v>
       </c>
       <c r="H62" t="n">
         <v>7660</v>
@@ -2196,7 +2196,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G63" t="n">
-        <v>8.26508903503418</v>
+        <v>8.2650899887085</v>
       </c>
       <c r="H63" t="n">
         <v>3625</v>
@@ -2225,7 +2225,7 @@
         <v>8.5</v>
       </c>
       <c r="G64" t="n">
-        <v>8.20715522766113</v>
+        <v>8.20715618133545</v>
       </c>
       <c r="H64" t="n">
         <v>659</v>
@@ -2254,7 +2254,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G65" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H65" t="n">
         <v>3106</v>
@@ -2283,7 +2283,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G66" t="n">
-        <v>8.13956832885742</v>
+        <v>8.13956737518311</v>
       </c>
       <c r="H66" t="n">
         <v>13</v>
@@ -2312,7 +2312,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G67" t="n">
-        <v>8.12025737762451</v>
+        <v>8.1202564239502</v>
       </c>
       <c r="H67" t="n">
         <v>969</v>
@@ -2341,7 +2341,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G68" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H68" t="n">
         <v>7666</v>
@@ -2370,7 +2370,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G69" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H69" t="n">
         <v>3050</v>
@@ -2399,7 +2399,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G70" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H70" t="n">
         <v>7975</v>
@@ -2457,7 +2457,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H72" t="n">
         <v>10401</v>
@@ -2486,7 +2486,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G73" t="n">
-        <v>7.95611429214478</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H73" t="n">
         <v>21359</v>
@@ -2515,7 +2515,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G74" t="n">
-        <v>7.95611429214478</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H74" t="n">
         <v>9297</v>
@@ -2544,7 +2544,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G75" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H75" t="n">
         <v>1884</v>
@@ -2573,7 +2573,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G76" t="n">
-        <v>8.1492223739624</v>
+        <v>8.14922332763672</v>
       </c>
       <c r="H76" t="n">
         <v>14438</v>
@@ -2602,7 +2602,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G77" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H77" t="n">
         <v>4665</v>
@@ -2631,7 +2631,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G78" t="n">
-        <v>8.12025737762451</v>
+        <v>8.1202564239502</v>
       </c>
       <c r="H78" t="n">
         <v>3676</v>
@@ -2718,7 +2718,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H81" t="n">
         <v>2117</v>
@@ -2747,7 +2747,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G82" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H82" t="n">
         <v>1745</v>
@@ -2776,7 +2776,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G83" t="n">
-        <v>8.06232452392578</v>
+        <v>8.06232357025146</v>
       </c>
       <c r="H83" t="n">
         <v>9150</v>
@@ -2805,7 +2805,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G84" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H84" t="n">
         <v>6600</v>
@@ -2892,7 +2892,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G87" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H87" t="n">
         <v>7121</v>
@@ -2921,7 +2921,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G88" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H88" t="n">
         <v>27333</v>
@@ -2979,7 +2979,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G90" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H90" t="n">
         <v>3277</v>
@@ -3008,7 +3008,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G91" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H91" t="n">
         <v>928</v>
@@ -3037,7 +3037,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G92" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H92" t="n">
         <v>4665</v>
@@ -3066,7 +3066,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G93" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H93" t="n">
         <v>17678</v>
@@ -3095,7 +3095,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G94" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H94" t="n">
         <v>3001</v>
@@ -3269,7 +3269,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>7.70507097244263</v>
+        <v>7.70507144927979</v>
       </c>
       <c r="H100" t="n">
         <v>2228</v>
@@ -3356,7 +3356,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>7.70507097244263</v>
+        <v>7.70507144927979</v>
       </c>
       <c r="H103" t="n">
         <v>238</v>
@@ -3414,7 +3414,7 @@
         <v>8</v>
       </c>
       <c r="G105" t="n">
-        <v>7.7243824005127</v>
+        <v>7.72438192367554</v>
       </c>
       <c r="H105" t="n">
         <v>2592</v>
@@ -3443,7 +3443,7 @@
         <v>8</v>
       </c>
       <c r="G106" t="n">
-        <v>7.7243824005127</v>
+        <v>7.72438192367554</v>
       </c>
       <c r="H106" t="n">
         <v>805</v>
@@ -3530,7 +3530,7 @@
         <v>8</v>
       </c>
       <c r="G109" t="n">
-        <v>7.7243824005127</v>
+        <v>7.72438192367554</v>
       </c>
       <c r="H109" t="n">
         <v>2584</v>
@@ -3559,7 +3559,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>7.76300430297852</v>
+        <v>7.76300382614136</v>
       </c>
       <c r="H110" t="n">
         <v>1005</v>
@@ -3675,7 +3675,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>8.16853523254395</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H114" t="n">
         <v>4325</v>
@@ -3704,7 +3704,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>8.16853523254395</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H115" t="n">
         <v>3981</v>
@@ -3733,7 +3733,7 @@
         <v>8.5</v>
       </c>
       <c r="G116" t="n">
-        <v>8.20715522766113</v>
+        <v>8.20715618133545</v>
       </c>
       <c r="H116" t="n">
         <v>3300</v>
@@ -3791,7 +3791,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G118" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H118" t="n">
         <v>4146</v>
@@ -3820,7 +3820,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G119" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H119" t="n">
         <v>2963</v>
@@ -3849,7 +3849,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G120" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H120" t="n">
         <v>40121</v>
@@ -3878,7 +3878,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G121" t="n">
-        <v>8.26508903503418</v>
+        <v>8.2650899887085</v>
       </c>
       <c r="H121" t="n">
         <v>9459</v>
@@ -3907,7 +3907,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G122" t="n">
-        <v>8.41957664489746</v>
+        <v>8.41957759857178</v>
       </c>
       <c r="H122" t="n">
         <v>12777</v>
@@ -3936,7 +3936,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G123" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H123" t="n">
         <v>8043</v>
@@ -3994,7 +3994,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H125" t="n">
         <v>42823</v>
@@ -4052,7 +4052,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>8.61268711090088</v>
+        <v>8.61268615722656</v>
       </c>
       <c r="H127" t="n">
         <v>14042</v>
@@ -4081,7 +4081,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G128" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H128" t="n">
         <v>4585</v>
@@ -4110,7 +4110,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G129" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H129" t="n">
         <v>6000</v>
@@ -4139,7 +4139,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G130" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H130" t="n">
         <v>19296</v>
@@ -4168,7 +4168,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G131" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H131" t="n">
         <v>40100</v>
@@ -4197,7 +4197,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G132" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H132" t="n">
         <v>3386</v>
@@ -4255,7 +4255,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>8.65130710601807</v>
+        <v>8.6513090133667</v>
       </c>
       <c r="H134" t="n">
         <v>4553</v>
@@ -4313,7 +4313,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G136" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H136" t="n">
         <v>1044</v>
@@ -4371,7 +4371,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H138" t="n">
         <v>475</v>
@@ -4400,7 +4400,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G139" t="n">
-        <v>8.5161304473877</v>
+        <v>8.51613140106201</v>
       </c>
       <c r="H139" t="n">
         <v>312</v>
@@ -4429,7 +4429,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H140" t="n">
         <v>1058</v>
@@ -4545,7 +4545,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G144" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H144" t="n">
         <v>1986</v>
@@ -4719,7 +4719,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G150" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H150" t="n">
         <v>4230</v>
@@ -4777,7 +4777,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G152" t="n">
-        <v>8.38095569610596</v>
+        <v>8.38095474243164</v>
       </c>
       <c r="H152" t="n">
         <v>7019</v>
@@ -4893,7 +4893,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G156" t="n">
-        <v>8.41957664489746</v>
+        <v>8.41957759857178</v>
       </c>
       <c r="H156" t="n">
         <v>9168</v>
@@ -4922,7 +4922,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G157" t="n">
-        <v>8.41957664489746</v>
+        <v>8.41957759857178</v>
       </c>
       <c r="H157" t="n">
         <v>10594</v>
@@ -5009,7 +5009,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G160" t="n">
-        <v>8.26508903503418</v>
+        <v>8.2650899887085</v>
       </c>
       <c r="H160" t="n">
         <v>1429</v>
@@ -5038,7 +5038,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G161" t="n">
-        <v>8.22646713256836</v>
+        <v>8.22646808624268</v>
       </c>
       <c r="H161" t="n">
         <v>18016</v>
@@ -5067,7 +5067,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G162" t="n">
-        <v>8.22646713256836</v>
+        <v>8.22646808624268</v>
       </c>
       <c r="H162" t="n">
         <v>257</v>
@@ -5096,7 +5096,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G163" t="n">
-        <v>8.26508903503418</v>
+        <v>8.2650899887085</v>
       </c>
       <c r="H163" t="n">
         <v>1104</v>
@@ -5125,7 +5125,7 @@
         <v>8.5</v>
       </c>
       <c r="G164" t="n">
-        <v>8.20715522766113</v>
+        <v>8.20715618133545</v>
       </c>
       <c r="H164" t="n">
         <v>18147</v>
@@ -5154,7 +5154,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H165" t="n">
         <v>1441</v>
@@ -5183,7 +5183,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G166" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H166" t="n">
         <v>9385</v>
@@ -5212,7 +5212,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G167" t="n">
-        <v>8.03335762023926</v>
+        <v>8.03335666656494</v>
       </c>
       <c r="H167" t="n">
         <v>3202</v>
@@ -5241,7 +5241,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H168" t="n">
         <v>4677</v>
@@ -5270,7 +5270,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H169" t="n">
         <v>670</v>
@@ -5299,7 +5299,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G170" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H170" t="n">
         <v>4833</v>
@@ -5328,7 +5328,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G171" t="n">
-        <v>8.03335762023926</v>
+        <v>8.03335666656494</v>
       </c>
       <c r="H171" t="n">
         <v>7897</v>
@@ -5357,7 +5357,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G172" t="n">
-        <v>8.03335762023926</v>
+        <v>8.03335666656494</v>
       </c>
       <c r="H172" t="n">
         <v>12746</v>
@@ -5386,7 +5386,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G173" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H173" t="n">
         <v>7608</v>
@@ -5415,7 +5415,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G174" t="n">
-        <v>7.95611429214478</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H174" t="n">
         <v>9388</v>
@@ -5444,7 +5444,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G175" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H175" t="n">
         <v>4377</v>
@@ -5502,7 +5502,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G177" t="n">
-        <v>8.03335762023926</v>
+        <v>8.03335666656494</v>
       </c>
       <c r="H177" t="n">
         <v>7669</v>
@@ -5531,7 +5531,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G178" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H178" t="n">
         <v>10600</v>
@@ -5560,7 +5560,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H179" t="n">
         <v>6577</v>
@@ -5618,7 +5618,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G181" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H181" t="n">
         <v>20346</v>
@@ -5705,7 +5705,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G184" t="n">
-        <v>7.840247631073</v>
+        <v>7.84024810791016</v>
       </c>
       <c r="H184" t="n">
         <v>1379</v>
@@ -5763,7 +5763,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H186" t="n">
         <v>3135</v>
@@ -5850,7 +5850,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G189" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H189" t="n">
         <v>5300</v>
@@ -5879,7 +5879,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G190" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H190" t="n">
         <v>3983</v>
@@ -5966,7 +5966,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G193" t="n">
-        <v>7.80162620544434</v>
+        <v>7.80162572860718</v>
       </c>
       <c r="H193" t="n">
         <v>4813</v>
@@ -6024,7 +6024,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>7.80162620544434</v>
+        <v>7.80162572860718</v>
       </c>
       <c r="H195" t="n">
         <v>30855</v>
@@ -6082,7 +6082,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G197" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H197" t="n">
         <v>21391</v>
@@ -6140,7 +6140,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G199" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H199" t="n">
         <v>20734</v>
@@ -6169,7 +6169,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G200" t="n">
-        <v>7.840247631073</v>
+        <v>7.84024810791016</v>
       </c>
       <c r="H200" t="n">
         <v>2702</v>
@@ -6198,7 +6198,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G201" t="n">
-        <v>7.80162620544434</v>
+        <v>7.80162572860718</v>
       </c>
       <c r="H201" t="n">
         <v>9261</v>
@@ -6227,7 +6227,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G202" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H202" t="n">
         <v>3347</v>
@@ -6256,7 +6256,7 @@
         <v>8</v>
       </c>
       <c r="G203" t="n">
-        <v>7.7243824005127</v>
+        <v>7.72438192367554</v>
       </c>
       <c r="H203" t="n">
         <v>14236</v>
@@ -6285,7 +6285,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G204" t="n">
-        <v>7.76300430297852</v>
+        <v>7.76300382614136</v>
       </c>
       <c r="H204" t="n">
         <v>924</v>
@@ -6314,7 +6314,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G205" t="n">
-        <v>7.76300430297852</v>
+        <v>7.76300382614136</v>
       </c>
       <c r="H205" t="n">
         <v>7017</v>
@@ -6343,7 +6343,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G206" t="n">
-        <v>7.840247631073</v>
+        <v>7.84024810791016</v>
       </c>
       <c r="H206" t="n">
         <v>11802</v>
@@ -6372,7 +6372,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G207" t="n">
-        <v>7.840247631073</v>
+        <v>7.84024810791016</v>
       </c>
       <c r="H207" t="n">
         <v>725</v>
@@ -6401,7 +6401,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G208" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H208" t="n">
         <v>1089</v>
@@ -6430,7 +6430,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G209" t="n">
-        <v>7.80162620544434</v>
+        <v>7.80162572860718</v>
       </c>
       <c r="H209" t="n">
         <v>12045</v>
@@ -6459,7 +6459,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G210" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H210" t="n">
         <v>1549</v>
@@ -6488,7 +6488,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G211" t="n">
-        <v>7.840247631073</v>
+        <v>7.84024810791016</v>
       </c>
       <c r="H211" t="n">
         <v>979</v>
@@ -6517,7 +6517,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G212" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H212" t="n">
         <v>12241</v>
@@ -6546,7 +6546,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H213" t="n">
         <v>55092</v>
@@ -6575,7 +6575,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G214" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H214" t="n">
         <v>8492</v>
@@ -6604,7 +6604,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G215" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H215" t="n">
         <v>4566</v>
@@ -6633,7 +6633,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G216" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H216" t="n">
         <v>16342</v>
@@ -6691,7 +6691,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G218" t="n">
-        <v>8.16853523254395</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H218" t="n">
         <v>1736</v>
@@ -6720,7 +6720,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G219" t="n">
-        <v>8.1492223739624</v>
+        <v>8.14922332763672</v>
       </c>
       <c r="H219" t="n">
         <v>13052</v>
@@ -6749,7 +6749,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G220" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H220" t="n">
         <v>8198</v>
@@ -6778,7 +6778,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>8.16853523254395</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H221" t="n">
         <v>7392</v>
@@ -6807,7 +6807,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G222" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H222" t="n">
         <v>5722</v>
@@ -6836,7 +6836,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G223" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H223" t="n">
         <v>5300</v>
@@ -6865,7 +6865,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G224" t="n">
-        <v>8.1492223739624</v>
+        <v>8.14922332763672</v>
       </c>
       <c r="H224" t="n">
         <v>15866</v>
@@ -6894,7 +6894,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>8.16853523254395</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H225" t="n">
         <v>1316</v>
@@ -7039,7 +7039,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G230" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H230" t="n">
         <v>2393</v>
@@ -7068,7 +7068,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G231" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H231" t="n">
         <v>7440</v>
@@ -7097,7 +7097,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H232" t="n">
         <v>11067</v>
@@ -7126,7 +7126,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>8.16853523254395</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H233" t="n">
         <v>6312</v>
@@ -7155,7 +7155,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G234" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H234" t="n">
         <v>826</v>
@@ -7184,7 +7184,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H235" t="n">
         <v>752</v>
@@ -7213,7 +7213,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G236" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H236" t="n">
         <v>8366</v>
@@ -7242,7 +7242,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G237" t="n">
-        <v>8.03335762023926</v>
+        <v>8.03335666656494</v>
       </c>
       <c r="H237" t="n">
         <v>963</v>
@@ -7271,7 +7271,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G238" t="n">
-        <v>7.95611429214478</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H238" t="n">
         <v>3477</v>
@@ -7300,7 +7300,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G239" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H239" t="n">
         <v>6101</v>
@@ -7329,7 +7329,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G240" t="n">
-        <v>7.840247631073</v>
+        <v>7.84024810791016</v>
       </c>
       <c r="H240" t="n">
         <v>1452</v>
@@ -7358,7 +7358,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G241" t="n">
-        <v>7.840247631073</v>
+        <v>7.84024810791016</v>
       </c>
       <c r="H241" t="n">
         <v>7526</v>
@@ -7387,7 +7387,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G242" t="n">
-        <v>7.80162620544434</v>
+        <v>7.80162572860718</v>
       </c>
       <c r="H242" t="n">
         <v>11501</v>
@@ -7416,7 +7416,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G243" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H243" t="n">
         <v>3669</v>
@@ -7445,7 +7445,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G244" t="n">
-        <v>7.80162620544434</v>
+        <v>7.80162572860718</v>
       </c>
       <c r="H244" t="n">
         <v>3415</v>
@@ -7503,7 +7503,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G246" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H246" t="n">
         <v>31120</v>
@@ -7532,7 +7532,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G247" t="n">
-        <v>8.03335762023926</v>
+        <v>8.03335666656494</v>
       </c>
       <c r="H247" t="n">
         <v>5954</v>
@@ -7648,7 +7648,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G251" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H251" t="n">
         <v>17702</v>
@@ -7677,7 +7677,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G252" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H252" t="n">
         <v>4458</v>
@@ -7764,7 +7764,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G255" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H255" t="n">
         <v>18125</v>
@@ -7822,7 +7822,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G257" t="n">
-        <v>8.03335762023926</v>
+        <v>8.03335666656494</v>
       </c>
       <c r="H257" t="n">
         <v>7880</v>
@@ -7851,7 +7851,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G258" t="n">
-        <v>8.03335762023926</v>
+        <v>8.03335666656494</v>
       </c>
       <c r="H258" t="n">
         <v>4353</v>
@@ -7880,7 +7880,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H259" t="n">
         <v>13726</v>
@@ -7909,7 +7909,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G260" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H260" t="n">
         <v>14869</v>
@@ -7938,7 +7938,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G261" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H261" t="n">
         <v>2653</v>
@@ -7967,7 +7967,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G262" t="n">
-        <v>8.03335762023926</v>
+        <v>8.03335666656494</v>
       </c>
       <c r="H262" t="n">
         <v>11900</v>
@@ -7996,7 +7996,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H263" t="n">
         <v>15803</v>
@@ -8025,7 +8025,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G264" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H264" t="n">
         <v>7199</v>
@@ -8083,7 +8083,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G266" t="n">
-        <v>7.76300430297852</v>
+        <v>7.76300382614136</v>
       </c>
       <c r="H266" t="n">
         <v>11333</v>
@@ -8141,7 +8141,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>7.80162620544434</v>
+        <v>7.80162572860718</v>
       </c>
       <c r="H268" t="n">
         <v>60509</v>
@@ -8228,7 +8228,7 @@
         <v>8</v>
       </c>
       <c r="G271" t="n">
-        <v>7.7243824005127</v>
+        <v>7.72438192367554</v>
       </c>
       <c r="H271" t="n">
         <v>11242</v>
@@ -8286,7 +8286,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G273" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H273" t="n">
         <v>7426</v>
@@ -8315,7 +8315,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G274" t="n">
-        <v>7.840247631073</v>
+        <v>7.84024810791016</v>
       </c>
       <c r="H274" t="n">
         <v>5092</v>
@@ -8344,7 +8344,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G275" t="n">
-        <v>7.840247631073</v>
+        <v>7.84024810791016</v>
       </c>
       <c r="H275" t="n">
         <v>4611</v>
@@ -8460,7 +8460,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G279" t="n">
-        <v>7.76300430297852</v>
+        <v>7.76300382614136</v>
       </c>
       <c r="H279" t="n">
         <v>16537</v>
@@ -8489,7 +8489,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G280" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H280" t="n">
         <v>7266</v>
@@ -8547,7 +8547,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G282" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H282" t="n">
         <v>2416</v>
@@ -8605,7 +8605,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G284" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H284" t="n">
         <v>12131</v>
@@ -8634,7 +8634,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G285" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H285" t="n">
         <v>2580</v>
@@ -8663,7 +8663,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G286" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H286" t="n">
         <v>2356</v>
@@ -8692,7 +8692,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G287" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H287" t="n">
         <v>14875</v>
@@ -8721,7 +8721,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G288" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H288" t="n">
         <v>4850</v>
@@ -8750,7 +8750,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G289" t="n">
-        <v>7.95611429214478</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H289" t="n">
         <v>6789</v>
@@ -8779,7 +8779,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H290" t="n">
         <v>1377</v>
@@ -8837,7 +8837,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G292" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H292" t="n">
         <v>2670</v>
@@ -8866,7 +8866,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G293" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H293" t="n">
         <v>11644</v>
@@ -8895,7 +8895,7 @@
         <v>8.5</v>
       </c>
       <c r="G294" t="n">
-        <v>8.20715522766113</v>
+        <v>8.20715618133545</v>
       </c>
       <c r="H294" t="n">
         <v>6062</v>
@@ -8953,7 +8953,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G296" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H296" t="n">
         <v>4509</v>
@@ -8982,7 +8982,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G297" t="n">
-        <v>8.26508903503418</v>
+        <v>8.2650899887085</v>
       </c>
       <c r="H297" t="n">
         <v>17816</v>
@@ -9040,7 +9040,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G299" t="n">
-        <v>8.43888664245605</v>
+        <v>8.43888759613037</v>
       </c>
       <c r="H299" t="n">
         <v>5531</v>
@@ -9069,7 +9069,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G300" t="n">
-        <v>8.61268711090088</v>
+        <v>8.61268615722656</v>
       </c>
       <c r="H300" t="n">
         <v>26734</v>
@@ -9098,7 +9098,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G301" t="n">
-        <v>8.57406425476074</v>
+        <v>8.57406520843506</v>
       </c>
       <c r="H301" t="n">
         <v>11499</v>
@@ -9214,7 +9214,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>8.65130710601807</v>
+        <v>8.6513090133667</v>
       </c>
       <c r="H305" t="n">
         <v>3325</v>
@@ -9243,7 +9243,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G306" t="n">
-        <v>8.38095569610596</v>
+        <v>8.38095474243164</v>
       </c>
       <c r="H306" t="n">
         <v>5373</v>
@@ -9272,7 +9272,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G307" t="n">
-        <v>8.65130710601807</v>
+        <v>8.6513090133667</v>
       </c>
       <c r="H307" t="n">
         <v>19782</v>
@@ -9301,7 +9301,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G308" t="n">
-        <v>8.70924091339111</v>
+        <v>8.70924186706543</v>
       </c>
       <c r="H308" t="n">
         <v>19262</v>
@@ -9446,7 +9446,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G313" t="n">
-        <v>8.70924091339111</v>
+        <v>8.70924186706543</v>
       </c>
       <c r="H313" t="n">
         <v>7173</v>
@@ -9475,7 +9475,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>8.61268711090088</v>
+        <v>8.61268615722656</v>
       </c>
       <c r="H314" t="n">
         <v>3755</v>
@@ -9504,7 +9504,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G315" t="n">
-        <v>8.5161304473877</v>
+        <v>8.51613140106201</v>
       </c>
       <c r="H315" t="n">
         <v>3379</v>
@@ -9562,7 +9562,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H317" t="n">
         <v>6105</v>
@@ -9620,7 +9620,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G319" t="n">
-        <v>8.41957664489746</v>
+        <v>8.41957759857178</v>
       </c>
       <c r="H319" t="n">
         <v>1746</v>
@@ -9649,7 +9649,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H320" t="n">
         <v>952</v>
@@ -9678,7 +9678,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H321" t="n">
         <v>1603</v>
@@ -9707,7 +9707,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G322" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H322" t="n">
         <v>14286</v>
@@ -9736,7 +9736,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G323" t="n">
-        <v>8.38095569610596</v>
+        <v>8.38095474243164</v>
       </c>
       <c r="H323" t="n">
         <v>27377</v>
@@ -9823,7 +9823,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G326" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H326" t="n">
         <v>3583</v>
@@ -9852,7 +9852,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H327" t="n">
         <v>1758</v>
@@ -9881,7 +9881,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G328" t="n">
-        <v>8.43888664245605</v>
+        <v>8.43888759613037</v>
       </c>
       <c r="H328" t="n">
         <v>4105</v>
@@ -9997,7 +9997,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G332" t="n">
-        <v>8.5161304473877</v>
+        <v>8.51613140106201</v>
       </c>
       <c r="H332" t="n">
         <v>28344</v>
@@ -10055,7 +10055,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>8.72855186462402</v>
+        <v>8.72855281829834</v>
       </c>
       <c r="H334" t="n">
         <v>10228</v>
@@ -10084,7 +10084,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G335" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H335" t="n">
         <v>18023</v>
@@ -10171,7 +10171,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>8.65130710601807</v>
+        <v>8.6513090133667</v>
       </c>
       <c r="H338" t="n">
         <v>20928</v>
@@ -10432,7 +10432,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G347" t="n">
-        <v>8.65130710601807</v>
+        <v>8.6513090133667</v>
       </c>
       <c r="H347" t="n">
         <v>3955</v>
@@ -10490,7 +10490,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G349" t="n">
-        <v>8.70924091339111</v>
+        <v>8.70924186706543</v>
       </c>
       <c r="H349" t="n">
         <v>20895</v>
@@ -10722,7 +10722,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>8.65130710601807</v>
+        <v>8.6513090133667</v>
       </c>
       <c r="H357" t="n">
         <v>2883</v>
@@ -10809,7 +10809,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G360" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H360" t="n">
         <v>1072</v>
@@ -10838,7 +10838,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H361" t="n">
         <v>299</v>
@@ -10867,7 +10867,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>8.57406425476074</v>
+        <v>8.57406520843506</v>
       </c>
       <c r="H362" t="n">
         <v>1231</v>
@@ -10925,7 +10925,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G364" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H364" t="n">
         <v>1993</v>
@@ -10983,7 +10983,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G366" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H366" t="n">
         <v>3879</v>
@@ -11012,7 +11012,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G367" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H367" t="n">
         <v>17028</v>
@@ -11128,7 +11128,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G371" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H371" t="n">
         <v>5429</v>
@@ -29027,6 +29027,64 @@
         <v>23591</v>
       </c>
       <c r="I988" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="s">
+        <v>9</v>
+      </c>
+      <c r="B989" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C989" t="n">
+        <v>23.8500003814697</v>
+      </c>
+      <c r="D989" t="n">
+        <v>23.8500003814697</v>
+      </c>
+      <c r="E989" t="n">
+        <v>22.4500007629395</v>
+      </c>
+      <c r="F989" t="n">
+        <v>22.6499996185303</v>
+      </c>
+      <c r="G989" t="n">
+        <v>22.6499996185303</v>
+      </c>
+      <c r="H989" t="n">
+        <v>32599</v>
+      </c>
+      <c r="I989" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="s">
+        <v>9</v>
+      </c>
+      <c r="B990" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C990" t="n">
+        <v>22.3500003814697</v>
+      </c>
+      <c r="D990" t="n">
+        <v>22.7000007629395</v>
+      </c>
+      <c r="E990" t="n">
+        <v>22</v>
+      </c>
+      <c r="F990" t="n">
+        <v>22.4500007629395</v>
+      </c>
+      <c r="G990" t="n">
+        <v>22.4500007629395</v>
+      </c>
+      <c r="H990" t="n">
+        <v>53790</v>
+      </c>
+      <c r="I990" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -29088,6 +29088,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="991">
+      <c r="A991" t="s">
+        <v>9</v>
+      </c>
+      <c r="B991" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C991" t="n">
+        <v>22.2999992370605</v>
+      </c>
+      <c r="D991" t="n">
+        <v>22.8500003814697</v>
+      </c>
+      <c r="E991" t="n">
+        <v>22.2999992370605</v>
+      </c>
+      <c r="F991" t="n">
+        <v>22.8500003814697</v>
+      </c>
+      <c r="G991" t="n">
+        <v>22.8500003814697</v>
+      </c>
+      <c r="H991" t="n">
+        <v>20861</v>
+      </c>
+      <c r="I991" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2" t="n">
-        <v>8.30371189117432</v>
+        <v>8.3037109375</v>
       </c>
       <c r="H2" t="n">
         <v>4793</v>
@@ -485,7 +485,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G4" t="n">
-        <v>8.13956737518311</v>
+        <v>8.13956832885742</v>
       </c>
       <c r="H4" t="n">
         <v>6993</v>
@@ -514,7 +514,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G5" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H5" t="n">
         <v>15746</v>
@@ -601,7 +601,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G8" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H8" t="n">
         <v>3358</v>
@@ -659,7 +659,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G10" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H10" t="n">
         <v>6204</v>
@@ -804,7 +804,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G15" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H15" t="n">
         <v>32</v>
@@ -833,7 +833,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G16" t="n">
-        <v>8.14922332763672</v>
+        <v>8.1492223739624</v>
       </c>
       <c r="H16" t="n">
         <v>1934</v>
@@ -862,7 +862,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G17" t="n">
-        <v>7.946457862854</v>
+        <v>7.94645881652832</v>
       </c>
       <c r="H17" t="n">
         <v>2333</v>
@@ -920,7 +920,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G19" t="n">
-        <v>8.13956737518311</v>
+        <v>8.13956832885742</v>
       </c>
       <c r="H19" t="n">
         <v>505</v>
@@ -949,7 +949,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G20" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H20" t="n">
         <v>1660</v>
@@ -978,7 +978,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G21" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H21" t="n">
         <v>2849</v>
@@ -1036,7 +1036,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G23" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611429214478</v>
       </c>
       <c r="H23" t="n">
         <v>480</v>
@@ -1065,7 +1065,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G24" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H24" t="n">
         <v>8168</v>
@@ -1152,7 +1152,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G27" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H27" t="n">
         <v>15457</v>
@@ -1210,7 +1210,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>7.92714643478394</v>
+        <v>7.92714738845825</v>
       </c>
       <c r="H29" t="n">
         <v>5644</v>
@@ -1326,7 +1326,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H33" t="n">
         <v>3280</v>
@@ -1384,7 +1384,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H35" t="n">
         <v>8723</v>
@@ -1413,7 +1413,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G36" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H36" t="n">
         <v>411</v>
@@ -1471,7 +1471,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H38" t="n">
         <v>80</v>
@@ -1500,7 +1500,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H39" t="n">
         <v>559</v>
@@ -1529,7 +1529,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G40" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H40" t="n">
         <v>3659</v>
@@ -1558,7 +1558,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G41" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H41" t="n">
         <v>3082</v>
@@ -1587,7 +1587,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G42" t="n">
-        <v>7.92714643478394</v>
+        <v>7.92714738845825</v>
       </c>
       <c r="H42" t="n">
         <v>8130</v>
@@ -1645,7 +1645,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G44" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H44" t="n">
         <v>15725</v>
@@ -1674,7 +1674,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G45" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H45" t="n">
         <v>8898</v>
@@ -1703,7 +1703,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G46" t="n">
-        <v>7.92714643478394</v>
+        <v>7.92714738845825</v>
       </c>
       <c r="H46" t="n">
         <v>14594</v>
@@ -1732,7 +1732,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G47" t="n">
-        <v>7.92714643478394</v>
+        <v>7.92714738845825</v>
       </c>
       <c r="H47" t="n">
         <v>2940</v>
@@ -1819,7 +1819,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H50" t="n">
         <v>15331</v>
@@ -1848,7 +1848,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G51" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H51" t="n">
         <v>8900</v>
@@ -1906,7 +1906,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G53" t="n">
-        <v>8.03335666656494</v>
+        <v>8.03335762023926</v>
       </c>
       <c r="H53" t="n">
         <v>23431</v>
@@ -1935,7 +1935,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G54" t="n">
-        <v>8.13956737518311</v>
+        <v>8.13956832885742</v>
       </c>
       <c r="H54" t="n">
         <v>24286</v>
@@ -1964,7 +1964,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G55" t="n">
-        <v>8.03335666656494</v>
+        <v>8.03335762023926</v>
       </c>
       <c r="H55" t="n">
         <v>1335</v>
@@ -2022,7 +2022,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H57" t="n">
         <v>1380</v>
@@ -2051,7 +2051,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H58" t="n">
         <v>12623</v>
@@ -2080,7 +2080,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G59" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H59" t="n">
         <v>3310</v>
@@ -2109,7 +2109,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G60" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H60" t="n">
         <v>12417</v>
@@ -2138,7 +2138,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G61" t="n">
-        <v>8.30371189117432</v>
+        <v>8.3037109375</v>
       </c>
       <c r="H61" t="n">
         <v>13315</v>
@@ -2167,7 +2167,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>8.25543308258057</v>
+        <v>8.25543403625488</v>
       </c>
       <c r="H62" t="n">
         <v>7660</v>
@@ -2196,7 +2196,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G63" t="n">
-        <v>8.2650899887085</v>
+        <v>8.26508903503418</v>
       </c>
       <c r="H63" t="n">
         <v>3625</v>
@@ -2225,7 +2225,7 @@
         <v>8.5</v>
       </c>
       <c r="G64" t="n">
-        <v>8.20715618133545</v>
+        <v>8.20715522766113</v>
       </c>
       <c r="H64" t="n">
         <v>659</v>
@@ -2254,7 +2254,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G65" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H65" t="n">
         <v>3106</v>
@@ -2283,7 +2283,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G66" t="n">
-        <v>8.13956737518311</v>
+        <v>8.13956832885742</v>
       </c>
       <c r="H66" t="n">
         <v>13</v>
@@ -2312,7 +2312,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G67" t="n">
-        <v>8.1202564239502</v>
+        <v>8.12025737762451</v>
       </c>
       <c r="H67" t="n">
         <v>969</v>
@@ -2341,7 +2341,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G68" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H68" t="n">
         <v>7666</v>
@@ -2370,7 +2370,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G69" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H69" t="n">
         <v>3050</v>
@@ -2399,7 +2399,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G70" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H70" t="n">
         <v>7975</v>
@@ -2457,7 +2457,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H72" t="n">
         <v>10401</v>
@@ -2486,7 +2486,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G73" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611429214478</v>
       </c>
       <c r="H73" t="n">
         <v>21359</v>
@@ -2515,7 +2515,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G74" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611429214478</v>
       </c>
       <c r="H74" t="n">
         <v>9297</v>
@@ -2544,7 +2544,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G75" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H75" t="n">
         <v>1884</v>
@@ -2573,7 +2573,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G76" t="n">
-        <v>8.14922332763672</v>
+        <v>8.1492223739624</v>
       </c>
       <c r="H76" t="n">
         <v>14438</v>
@@ -2602,7 +2602,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G77" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H77" t="n">
         <v>4665</v>
@@ -2631,7 +2631,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G78" t="n">
-        <v>8.1202564239502</v>
+        <v>8.12025737762451</v>
       </c>
       <c r="H78" t="n">
         <v>3676</v>
@@ -2718,7 +2718,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H81" t="n">
         <v>2117</v>
@@ -2747,7 +2747,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G82" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H82" t="n">
         <v>1745</v>
@@ -2776,7 +2776,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G83" t="n">
-        <v>8.06232357025146</v>
+        <v>8.06232452392578</v>
       </c>
       <c r="H83" t="n">
         <v>9150</v>
@@ -2805,7 +2805,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G84" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H84" t="n">
         <v>6600</v>
@@ -2892,7 +2892,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G87" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H87" t="n">
         <v>7121</v>
@@ -2921,7 +2921,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G88" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H88" t="n">
         <v>27333</v>
@@ -2979,7 +2979,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G90" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H90" t="n">
         <v>3277</v>
@@ -3008,7 +3008,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G91" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H91" t="n">
         <v>928</v>
@@ -3037,7 +3037,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G92" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H92" t="n">
         <v>4665</v>
@@ -3066,7 +3066,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G93" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H93" t="n">
         <v>17678</v>
@@ -3095,7 +3095,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G94" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H94" t="n">
         <v>3001</v>
@@ -3269,7 +3269,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>7.70507144927979</v>
+        <v>7.70507097244263</v>
       </c>
       <c r="H100" t="n">
         <v>2228</v>
@@ -3356,7 +3356,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>7.70507144927979</v>
+        <v>7.70507097244263</v>
       </c>
       <c r="H103" t="n">
         <v>238</v>
@@ -3414,7 +3414,7 @@
         <v>8</v>
       </c>
       <c r="G105" t="n">
-        <v>7.72438192367554</v>
+        <v>7.7243824005127</v>
       </c>
       <c r="H105" t="n">
         <v>2592</v>
@@ -3443,7 +3443,7 @@
         <v>8</v>
       </c>
       <c r="G106" t="n">
-        <v>7.72438192367554</v>
+        <v>7.7243824005127</v>
       </c>
       <c r="H106" t="n">
         <v>805</v>
@@ -3530,7 +3530,7 @@
         <v>8</v>
       </c>
       <c r="G109" t="n">
-        <v>7.72438192367554</v>
+        <v>7.7243824005127</v>
       </c>
       <c r="H109" t="n">
         <v>2584</v>
@@ -3559,7 +3559,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>7.76300382614136</v>
+        <v>7.76300430297852</v>
       </c>
       <c r="H110" t="n">
         <v>1005</v>
@@ -3675,7 +3675,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853523254395</v>
       </c>
       <c r="H114" t="n">
         <v>4325</v>
@@ -3704,7 +3704,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853523254395</v>
       </c>
       <c r="H115" t="n">
         <v>3981</v>
@@ -3733,7 +3733,7 @@
         <v>8.5</v>
       </c>
       <c r="G116" t="n">
-        <v>8.20715618133545</v>
+        <v>8.20715522766113</v>
       </c>
       <c r="H116" t="n">
         <v>3300</v>
@@ -3791,7 +3791,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G118" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H118" t="n">
         <v>4146</v>
@@ -3820,7 +3820,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G119" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H119" t="n">
         <v>2963</v>
@@ -3849,7 +3849,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G120" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H120" t="n">
         <v>40121</v>
@@ -3878,7 +3878,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G121" t="n">
-        <v>8.2650899887085</v>
+        <v>8.26508903503418</v>
       </c>
       <c r="H121" t="n">
         <v>9459</v>
@@ -3907,7 +3907,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G122" t="n">
-        <v>8.41957759857178</v>
+        <v>8.41957664489746</v>
       </c>
       <c r="H122" t="n">
         <v>12777</v>
@@ -3936,7 +3936,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G123" t="n">
-        <v>8.30371189117432</v>
+        <v>8.3037109375</v>
       </c>
       <c r="H123" t="n">
         <v>8043</v>
@@ -3994,7 +3994,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>8.49682140350342</v>
+        <v>8.4968204498291</v>
       </c>
       <c r="H125" t="n">
         <v>42823</v>
@@ -4052,7 +4052,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>8.61268615722656</v>
+        <v>8.61268711090088</v>
       </c>
       <c r="H127" t="n">
         <v>14042</v>
@@ -4081,7 +4081,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G128" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H128" t="n">
         <v>4585</v>
@@ -4110,7 +4110,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G129" t="n">
-        <v>8.49682140350342</v>
+        <v>8.4968204498291</v>
       </c>
       <c r="H129" t="n">
         <v>6000</v>
@@ -4139,7 +4139,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G130" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H130" t="n">
         <v>19296</v>
@@ -4168,7 +4168,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G131" t="n">
-        <v>8.30371189117432</v>
+        <v>8.3037109375</v>
       </c>
       <c r="H131" t="n">
         <v>40100</v>
@@ -4197,7 +4197,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G132" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H132" t="n">
         <v>3386</v>
@@ -4255,7 +4255,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>8.6513090133667</v>
+        <v>8.65130710601807</v>
       </c>
       <c r="H134" t="n">
         <v>4553</v>
@@ -4313,7 +4313,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G136" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H136" t="n">
         <v>1044</v>
@@ -4371,7 +4371,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H138" t="n">
         <v>475</v>
@@ -4400,7 +4400,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G139" t="n">
-        <v>8.51613140106201</v>
+        <v>8.5161304473877</v>
       </c>
       <c r="H139" t="n">
         <v>312</v>
@@ -4429,7 +4429,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H140" t="n">
         <v>1058</v>
@@ -4545,7 +4545,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G144" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H144" t="n">
         <v>1986</v>
@@ -4719,7 +4719,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G150" t="n">
-        <v>8.30371189117432</v>
+        <v>8.3037109375</v>
       </c>
       <c r="H150" t="n">
         <v>4230</v>
@@ -4777,7 +4777,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G152" t="n">
-        <v>8.38095474243164</v>
+        <v>8.38095569610596</v>
       </c>
       <c r="H152" t="n">
         <v>7019</v>
@@ -4893,7 +4893,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G156" t="n">
-        <v>8.41957759857178</v>
+        <v>8.41957664489746</v>
       </c>
       <c r="H156" t="n">
         <v>9168</v>
@@ -4922,7 +4922,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G157" t="n">
-        <v>8.41957759857178</v>
+        <v>8.41957664489746</v>
       </c>
       <c r="H157" t="n">
         <v>10594</v>
@@ -5009,7 +5009,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G160" t="n">
-        <v>8.2650899887085</v>
+        <v>8.26508903503418</v>
       </c>
       <c r="H160" t="n">
         <v>1429</v>
@@ -5038,7 +5038,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G161" t="n">
-        <v>8.22646808624268</v>
+        <v>8.22646713256836</v>
       </c>
       <c r="H161" t="n">
         <v>18016</v>
@@ -5067,7 +5067,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G162" t="n">
-        <v>8.22646808624268</v>
+        <v>8.22646713256836</v>
       </c>
       <c r="H162" t="n">
         <v>257</v>
@@ -5096,7 +5096,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G163" t="n">
-        <v>8.2650899887085</v>
+        <v>8.26508903503418</v>
       </c>
       <c r="H163" t="n">
         <v>1104</v>
@@ -5125,7 +5125,7 @@
         <v>8.5</v>
       </c>
       <c r="G164" t="n">
-        <v>8.20715618133545</v>
+        <v>8.20715522766113</v>
       </c>
       <c r="H164" t="n">
         <v>18147</v>
@@ -5154,7 +5154,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H165" t="n">
         <v>1441</v>
@@ -5183,7 +5183,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G166" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H166" t="n">
         <v>9385</v>
@@ -5212,7 +5212,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G167" t="n">
-        <v>8.03335666656494</v>
+        <v>8.03335762023926</v>
       </c>
       <c r="H167" t="n">
         <v>3202</v>
@@ -5241,7 +5241,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H168" t="n">
         <v>4677</v>
@@ -5270,7 +5270,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H169" t="n">
         <v>670</v>
@@ -5299,7 +5299,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G170" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H170" t="n">
         <v>4833</v>
@@ -5328,7 +5328,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G171" t="n">
-        <v>8.03335666656494</v>
+        <v>8.03335762023926</v>
       </c>
       <c r="H171" t="n">
         <v>7897</v>
@@ -5357,7 +5357,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G172" t="n">
-        <v>8.03335666656494</v>
+        <v>8.03335762023926</v>
       </c>
       <c r="H172" t="n">
         <v>12746</v>
@@ -5386,7 +5386,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G173" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H173" t="n">
         <v>7608</v>
@@ -5415,7 +5415,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G174" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611429214478</v>
       </c>
       <c r="H174" t="n">
         <v>9388</v>
@@ -5444,7 +5444,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G175" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H175" t="n">
         <v>4377</v>
@@ -5502,7 +5502,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G177" t="n">
-        <v>8.03335666656494</v>
+        <v>8.03335762023926</v>
       </c>
       <c r="H177" t="n">
         <v>7669</v>
@@ -5531,7 +5531,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G178" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H178" t="n">
         <v>10600</v>
@@ -5560,7 +5560,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H179" t="n">
         <v>6577</v>
@@ -5618,7 +5618,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G181" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H181" t="n">
         <v>20346</v>
@@ -5705,7 +5705,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G184" t="n">
-        <v>7.84024810791016</v>
+        <v>7.840247631073</v>
       </c>
       <c r="H184" t="n">
         <v>1379</v>
@@ -5763,7 +5763,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H186" t="n">
         <v>3135</v>
@@ -5850,7 +5850,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G189" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H189" t="n">
         <v>5300</v>
@@ -5879,7 +5879,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G190" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H190" t="n">
         <v>3983</v>
@@ -5966,7 +5966,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G193" t="n">
-        <v>7.80162572860718</v>
+        <v>7.80162620544434</v>
       </c>
       <c r="H193" t="n">
         <v>4813</v>
@@ -6024,7 +6024,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>7.80162572860718</v>
+        <v>7.80162620544434</v>
       </c>
       <c r="H195" t="n">
         <v>30855</v>
@@ -6082,7 +6082,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G197" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H197" t="n">
         <v>21391</v>
@@ -6140,7 +6140,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G199" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H199" t="n">
         <v>20734</v>
@@ -6169,7 +6169,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G200" t="n">
-        <v>7.84024810791016</v>
+        <v>7.840247631073</v>
       </c>
       <c r="H200" t="n">
         <v>2702</v>
@@ -6198,7 +6198,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G201" t="n">
-        <v>7.80162572860718</v>
+        <v>7.80162620544434</v>
       </c>
       <c r="H201" t="n">
         <v>9261</v>
@@ -6227,7 +6227,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G202" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H202" t="n">
         <v>3347</v>
@@ -6256,7 +6256,7 @@
         <v>8</v>
       </c>
       <c r="G203" t="n">
-        <v>7.72438192367554</v>
+        <v>7.7243824005127</v>
       </c>
       <c r="H203" t="n">
         <v>14236</v>
@@ -6285,7 +6285,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G204" t="n">
-        <v>7.76300382614136</v>
+        <v>7.76300430297852</v>
       </c>
       <c r="H204" t="n">
         <v>924</v>
@@ -6314,7 +6314,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G205" t="n">
-        <v>7.76300382614136</v>
+        <v>7.76300430297852</v>
       </c>
       <c r="H205" t="n">
         <v>7017</v>
@@ -6343,7 +6343,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G206" t="n">
-        <v>7.84024810791016</v>
+        <v>7.840247631073</v>
       </c>
       <c r="H206" t="n">
         <v>11802</v>
@@ -6372,7 +6372,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G207" t="n">
-        <v>7.84024810791016</v>
+        <v>7.840247631073</v>
       </c>
       <c r="H207" t="n">
         <v>725</v>
@@ -6401,7 +6401,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G208" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H208" t="n">
         <v>1089</v>
@@ -6430,7 +6430,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G209" t="n">
-        <v>7.80162572860718</v>
+        <v>7.80162620544434</v>
       </c>
       <c r="H209" t="n">
         <v>12045</v>
@@ -6459,7 +6459,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G210" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H210" t="n">
         <v>1549</v>
@@ -6488,7 +6488,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G211" t="n">
-        <v>7.84024810791016</v>
+        <v>7.840247631073</v>
       </c>
       <c r="H211" t="n">
         <v>979</v>
@@ -6517,7 +6517,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G212" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H212" t="n">
         <v>12241</v>
@@ -6546,7 +6546,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H213" t="n">
         <v>55092</v>
@@ -6575,7 +6575,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G214" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H214" t="n">
         <v>8492</v>
@@ -6604,7 +6604,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G215" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H215" t="n">
         <v>4566</v>
@@ -6633,7 +6633,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G216" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H216" t="n">
         <v>16342</v>
@@ -6691,7 +6691,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G218" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853523254395</v>
       </c>
       <c r="H218" t="n">
         <v>1736</v>
@@ -6720,7 +6720,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G219" t="n">
-        <v>8.14922332763672</v>
+        <v>8.1492223739624</v>
       </c>
       <c r="H219" t="n">
         <v>13052</v>
@@ -6749,7 +6749,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G220" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H220" t="n">
         <v>8198</v>
@@ -6778,7 +6778,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853523254395</v>
       </c>
       <c r="H221" t="n">
         <v>7392</v>
@@ -6807,7 +6807,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G222" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H222" t="n">
         <v>5722</v>
@@ -6836,7 +6836,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G223" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H223" t="n">
         <v>5300</v>
@@ -6865,7 +6865,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G224" t="n">
-        <v>8.14922332763672</v>
+        <v>8.1492223739624</v>
       </c>
       <c r="H224" t="n">
         <v>15866</v>
@@ -6894,7 +6894,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853523254395</v>
       </c>
       <c r="H225" t="n">
         <v>1316</v>
@@ -7039,7 +7039,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G230" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H230" t="n">
         <v>2393</v>
@@ -7068,7 +7068,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G231" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H231" t="n">
         <v>7440</v>
@@ -7097,7 +7097,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H232" t="n">
         <v>11067</v>
@@ -7126,7 +7126,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853523254395</v>
       </c>
       <c r="H233" t="n">
         <v>6312</v>
@@ -7155,7 +7155,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G234" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H234" t="n">
         <v>826</v>
@@ -7184,7 +7184,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H235" t="n">
         <v>752</v>
@@ -7213,7 +7213,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G236" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H236" t="n">
         <v>8366</v>
@@ -7242,7 +7242,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G237" t="n">
-        <v>8.03335666656494</v>
+        <v>8.03335762023926</v>
       </c>
       <c r="H237" t="n">
         <v>963</v>
@@ -7271,7 +7271,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G238" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611429214478</v>
       </c>
       <c r="H238" t="n">
         <v>3477</v>
@@ -7300,7 +7300,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G239" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H239" t="n">
         <v>6101</v>
@@ -7329,7 +7329,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G240" t="n">
-        <v>7.84024810791016</v>
+        <v>7.840247631073</v>
       </c>
       <c r="H240" t="n">
         <v>1452</v>
@@ -7358,7 +7358,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G241" t="n">
-        <v>7.84024810791016</v>
+        <v>7.840247631073</v>
       </c>
       <c r="H241" t="n">
         <v>7526</v>
@@ -7387,7 +7387,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G242" t="n">
-        <v>7.80162572860718</v>
+        <v>7.80162620544434</v>
       </c>
       <c r="H242" t="n">
         <v>11501</v>
@@ -7416,7 +7416,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G243" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H243" t="n">
         <v>3669</v>
@@ -7445,7 +7445,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G244" t="n">
-        <v>7.80162572860718</v>
+        <v>7.80162620544434</v>
       </c>
       <c r="H244" t="n">
         <v>3415</v>
@@ -7503,7 +7503,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G246" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H246" t="n">
         <v>31120</v>
@@ -7532,7 +7532,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G247" t="n">
-        <v>8.03335666656494</v>
+        <v>8.03335762023926</v>
       </c>
       <c r="H247" t="n">
         <v>5954</v>
@@ -7648,7 +7648,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G251" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H251" t="n">
         <v>17702</v>
@@ -7677,7 +7677,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G252" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H252" t="n">
         <v>4458</v>
@@ -7764,7 +7764,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G255" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H255" t="n">
         <v>18125</v>
@@ -7822,7 +7822,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G257" t="n">
-        <v>8.03335666656494</v>
+        <v>8.03335762023926</v>
       </c>
       <c r="H257" t="n">
         <v>7880</v>
@@ -7851,7 +7851,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G258" t="n">
-        <v>8.03335666656494</v>
+        <v>8.03335762023926</v>
       </c>
       <c r="H258" t="n">
         <v>4353</v>
@@ -7880,7 +7880,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H259" t="n">
         <v>13726</v>
@@ -7909,7 +7909,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G260" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H260" t="n">
         <v>14869</v>
@@ -7938,7 +7938,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G261" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H261" t="n">
         <v>2653</v>
@@ -7967,7 +7967,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G262" t="n">
-        <v>8.03335666656494</v>
+        <v>8.03335762023926</v>
       </c>
       <c r="H262" t="n">
         <v>11900</v>
@@ -7996,7 +7996,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H263" t="n">
         <v>15803</v>
@@ -8025,7 +8025,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G264" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H264" t="n">
         <v>7199</v>
@@ -8083,7 +8083,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G266" t="n">
-        <v>7.76300382614136</v>
+        <v>7.76300430297852</v>
       </c>
       <c r="H266" t="n">
         <v>11333</v>
@@ -8141,7 +8141,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>7.80162572860718</v>
+        <v>7.80162620544434</v>
       </c>
       <c r="H268" t="n">
         <v>60509</v>
@@ -8228,7 +8228,7 @@
         <v>8</v>
       </c>
       <c r="G271" t="n">
-        <v>7.72438192367554</v>
+        <v>7.7243824005127</v>
       </c>
       <c r="H271" t="n">
         <v>11242</v>
@@ -8286,7 +8286,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G273" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H273" t="n">
         <v>7426</v>
@@ -8315,7 +8315,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G274" t="n">
-        <v>7.84024810791016</v>
+        <v>7.840247631073</v>
       </c>
       <c r="H274" t="n">
         <v>5092</v>
@@ -8344,7 +8344,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G275" t="n">
-        <v>7.84024810791016</v>
+        <v>7.840247631073</v>
       </c>
       <c r="H275" t="n">
         <v>4611</v>
@@ -8460,7 +8460,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G279" t="n">
-        <v>7.76300382614136</v>
+        <v>7.76300430297852</v>
       </c>
       <c r="H279" t="n">
         <v>16537</v>
@@ -8489,7 +8489,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G280" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H280" t="n">
         <v>7266</v>
@@ -8547,7 +8547,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G282" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H282" t="n">
         <v>2416</v>
@@ -8605,7 +8605,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G284" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H284" t="n">
         <v>12131</v>
@@ -8634,7 +8634,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G285" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H285" t="n">
         <v>2580</v>
@@ -8663,7 +8663,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G286" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H286" t="n">
         <v>2356</v>
@@ -8692,7 +8692,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G287" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H287" t="n">
         <v>14875</v>
@@ -8721,7 +8721,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G288" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H288" t="n">
         <v>4850</v>
@@ -8750,7 +8750,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G289" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611429214478</v>
       </c>
       <c r="H289" t="n">
         <v>6789</v>
@@ -8779,7 +8779,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H290" t="n">
         <v>1377</v>
@@ -8837,7 +8837,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G292" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H292" t="n">
         <v>2670</v>
@@ -8866,7 +8866,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G293" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H293" t="n">
         <v>11644</v>
@@ -8895,7 +8895,7 @@
         <v>8.5</v>
       </c>
       <c r="G294" t="n">
-        <v>8.20715618133545</v>
+        <v>8.20715522766113</v>
       </c>
       <c r="H294" t="n">
         <v>6062</v>
@@ -8953,7 +8953,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G296" t="n">
-        <v>8.30371189117432</v>
+        <v>8.3037109375</v>
       </c>
       <c r="H296" t="n">
         <v>4509</v>
@@ -8982,7 +8982,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G297" t="n">
-        <v>8.2650899887085</v>
+        <v>8.26508903503418</v>
       </c>
       <c r="H297" t="n">
         <v>17816</v>
@@ -9040,7 +9040,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G299" t="n">
-        <v>8.43888759613037</v>
+        <v>8.43888664245605</v>
       </c>
       <c r="H299" t="n">
         <v>5531</v>
@@ -9069,7 +9069,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G300" t="n">
-        <v>8.61268615722656</v>
+        <v>8.61268711090088</v>
       </c>
       <c r="H300" t="n">
         <v>26734</v>
@@ -9098,7 +9098,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G301" t="n">
-        <v>8.57406520843506</v>
+        <v>8.57406425476074</v>
       </c>
       <c r="H301" t="n">
         <v>11499</v>
@@ -9214,7 +9214,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>8.6513090133667</v>
+        <v>8.65130710601807</v>
       </c>
       <c r="H305" t="n">
         <v>3325</v>
@@ -9243,7 +9243,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G306" t="n">
-        <v>8.38095474243164</v>
+        <v>8.38095569610596</v>
       </c>
       <c r="H306" t="n">
         <v>5373</v>
@@ -9272,7 +9272,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G307" t="n">
-        <v>8.6513090133667</v>
+        <v>8.65130710601807</v>
       </c>
       <c r="H307" t="n">
         <v>19782</v>
@@ -9301,7 +9301,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G308" t="n">
-        <v>8.70924186706543</v>
+        <v>8.70924091339111</v>
       </c>
       <c r="H308" t="n">
         <v>19262</v>
@@ -9446,7 +9446,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G313" t="n">
-        <v>8.70924186706543</v>
+        <v>8.70924091339111</v>
       </c>
       <c r="H313" t="n">
         <v>7173</v>
@@ -9475,7 +9475,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>8.61268615722656</v>
+        <v>8.61268711090088</v>
       </c>
       <c r="H314" t="n">
         <v>3755</v>
@@ -9504,7 +9504,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G315" t="n">
-        <v>8.51613140106201</v>
+        <v>8.5161304473877</v>
       </c>
       <c r="H315" t="n">
         <v>3379</v>
@@ -9562,7 +9562,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H317" t="n">
         <v>6105</v>
@@ -9620,7 +9620,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G319" t="n">
-        <v>8.41957759857178</v>
+        <v>8.41957664489746</v>
       </c>
       <c r="H319" t="n">
         <v>1746</v>
@@ -9649,7 +9649,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>8.49682140350342</v>
+        <v>8.4968204498291</v>
       </c>
       <c r="H320" t="n">
         <v>952</v>
@@ -9678,7 +9678,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>8.49682140350342</v>
+        <v>8.4968204498291</v>
       </c>
       <c r="H321" t="n">
         <v>1603</v>
@@ -9707,7 +9707,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G322" t="n">
-        <v>8.49682140350342</v>
+        <v>8.4968204498291</v>
       </c>
       <c r="H322" t="n">
         <v>14286</v>
@@ -9736,7 +9736,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G323" t="n">
-        <v>8.38095474243164</v>
+        <v>8.38095569610596</v>
       </c>
       <c r="H323" t="n">
         <v>27377</v>
@@ -9823,7 +9823,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G326" t="n">
-        <v>8.49682140350342</v>
+        <v>8.4968204498291</v>
       </c>
       <c r="H326" t="n">
         <v>3583</v>
@@ -9852,7 +9852,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>8.49682140350342</v>
+        <v>8.4968204498291</v>
       </c>
       <c r="H327" t="n">
         <v>1758</v>
@@ -9881,7 +9881,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G328" t="n">
-        <v>8.43888759613037</v>
+        <v>8.43888664245605</v>
       </c>
       <c r="H328" t="n">
         <v>4105</v>
@@ -9997,7 +9997,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G332" t="n">
-        <v>8.51613140106201</v>
+        <v>8.5161304473877</v>
       </c>
       <c r="H332" t="n">
         <v>28344</v>
@@ -10055,7 +10055,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>8.72855281829834</v>
+        <v>8.72855186462402</v>
       </c>
       <c r="H334" t="n">
         <v>10228</v>
@@ -10084,7 +10084,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G335" t="n">
-        <v>8.49682140350342</v>
+        <v>8.4968204498291</v>
       </c>
       <c r="H335" t="n">
         <v>18023</v>
@@ -10171,7 +10171,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>8.6513090133667</v>
+        <v>8.65130710601807</v>
       </c>
       <c r="H338" t="n">
         <v>20928</v>
@@ -10432,7 +10432,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G347" t="n">
-        <v>8.6513090133667</v>
+        <v>8.65130710601807</v>
       </c>
       <c r="H347" t="n">
         <v>3955</v>
@@ -10490,7 +10490,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G349" t="n">
-        <v>8.70924186706543</v>
+        <v>8.70924091339111</v>
       </c>
       <c r="H349" t="n">
         <v>20895</v>
@@ -10722,7 +10722,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>8.6513090133667</v>
+        <v>8.65130710601807</v>
       </c>
       <c r="H357" t="n">
         <v>2883</v>
@@ -10809,7 +10809,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G360" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H360" t="n">
         <v>1072</v>
@@ -10838,7 +10838,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H361" t="n">
         <v>299</v>
@@ -10867,7 +10867,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>8.57406520843506</v>
+        <v>8.57406425476074</v>
       </c>
       <c r="H362" t="n">
         <v>1231</v>
@@ -10925,7 +10925,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G364" t="n">
-        <v>8.49682140350342</v>
+        <v>8.4968204498291</v>
       </c>
       <c r="H364" t="n">
         <v>1993</v>
@@ -10983,7 +10983,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G366" t="n">
-        <v>8.49682140350342</v>
+        <v>8.4968204498291</v>
       </c>
       <c r="H366" t="n">
         <v>3879</v>
@@ -11012,7 +11012,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G367" t="n">
-        <v>8.49682140350342</v>
+        <v>8.4968204498291</v>
       </c>
       <c r="H367" t="n">
         <v>17028</v>
@@ -11128,7 +11128,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G371" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H371" t="n">
         <v>5429</v>
@@ -29114,6 +29114,35 @@
         <v>20861</v>
       </c>
       <c r="I991" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="s">
+        <v>9</v>
+      </c>
+      <c r="B992" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C992" t="n">
+        <v>23.1000003814697</v>
+      </c>
+      <c r="D992" t="n">
+        <v>23.1000003814697</v>
+      </c>
+      <c r="E992" t="n">
+        <v>21.9500007629395</v>
+      </c>
+      <c r="F992" t="n">
+        <v>22.1000003814697</v>
+      </c>
+      <c r="G992" t="n">
+        <v>22.1000003814697</v>
+      </c>
+      <c r="H992" t="n">
+        <v>29749</v>
+      </c>
+      <c r="I992" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H2" t="n">
         <v>4793</v>
@@ -543,7 +543,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G6" t="n">
-        <v>8.18784427642822</v>
+        <v>8.18784523010254</v>
       </c>
       <c r="H6" t="n">
         <v>2771</v>
@@ -630,7 +630,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G9" t="n">
-        <v>8.1009464263916</v>
+        <v>8.10094547271729</v>
       </c>
       <c r="H9" t="n">
         <v>1320</v>
@@ -746,7 +746,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G13" t="n">
-        <v>8.18784427642822</v>
+        <v>8.18784523010254</v>
       </c>
       <c r="H13" t="n">
         <v>4230</v>
@@ -862,7 +862,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G17" t="n">
-        <v>7.94645881652832</v>
+        <v>7.946457862854</v>
       </c>
       <c r="H17" t="n">
         <v>2333</v>
@@ -891,7 +891,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G18" t="n">
-        <v>8.17819023132324</v>
+        <v>8.17818927764893</v>
       </c>
       <c r="H18" t="n">
         <v>980</v>
@@ -978,7 +978,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G21" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H21" t="n">
         <v>2849</v>
@@ -1036,7 +1036,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G23" t="n">
-        <v>7.95611429214478</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H23" t="n">
         <v>480</v>
@@ -1094,7 +1094,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G25" t="n">
-        <v>8.17819023132324</v>
+        <v>8.17818927764893</v>
       </c>
       <c r="H25" t="n">
         <v>384</v>
@@ -1239,7 +1239,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G30" t="n">
-        <v>8.1009464263916</v>
+        <v>8.10094547271729</v>
       </c>
       <c r="H30" t="n">
         <v>578</v>
@@ -1268,7 +1268,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G31" t="n">
-        <v>8.1009464263916</v>
+        <v>8.10094547271729</v>
       </c>
       <c r="H31" t="n">
         <v>332</v>
@@ -1326,7 +1326,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H33" t="n">
         <v>3280</v>
@@ -1384,7 +1384,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H35" t="n">
         <v>8723</v>
@@ -1442,7 +1442,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G37" t="n">
-        <v>8.02370262145996</v>
+        <v>8.02370166778564</v>
       </c>
       <c r="H37" t="n">
         <v>4958</v>
@@ -1645,7 +1645,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G44" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H44" t="n">
         <v>15725</v>
@@ -1674,7 +1674,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G45" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H45" t="n">
         <v>8898</v>
@@ -1819,7 +1819,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H50" t="n">
         <v>15331</v>
@@ -1848,7 +1848,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G51" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H51" t="n">
         <v>8900</v>
@@ -2022,7 +2022,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H57" t="n">
         <v>1380</v>
@@ -2051,7 +2051,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H58" t="n">
         <v>12623</v>
@@ -2080,7 +2080,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G59" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H59" t="n">
         <v>3310</v>
@@ -2109,7 +2109,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G60" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H60" t="n">
         <v>12417</v>
@@ -2138,7 +2138,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G61" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H61" t="n">
         <v>13315</v>
@@ -2225,7 +2225,7 @@
         <v>8.5</v>
       </c>
       <c r="G64" t="n">
-        <v>8.20715522766113</v>
+        <v>8.20715618133545</v>
       </c>
       <c r="H64" t="n">
         <v>659</v>
@@ -2312,7 +2312,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G67" t="n">
-        <v>8.12025737762451</v>
+        <v>8.1202564239502</v>
       </c>
       <c r="H67" t="n">
         <v>969</v>
@@ -2370,7 +2370,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G69" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H69" t="n">
         <v>3050</v>
@@ -2457,7 +2457,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H72" t="n">
         <v>10401</v>
@@ -2486,7 +2486,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G73" t="n">
-        <v>7.95611429214478</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H73" t="n">
         <v>21359</v>
@@ -2515,7 +2515,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G74" t="n">
-        <v>7.95611429214478</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H74" t="n">
         <v>9297</v>
@@ -2544,7 +2544,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G75" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H75" t="n">
         <v>1884</v>
@@ -2631,7 +2631,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G78" t="n">
-        <v>8.12025737762451</v>
+        <v>8.1202564239502</v>
       </c>
       <c r="H78" t="n">
         <v>3676</v>
@@ -2718,7 +2718,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H81" t="n">
         <v>2117</v>
@@ -2805,7 +2805,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G84" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H84" t="n">
         <v>6600</v>
@@ -2892,7 +2892,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G87" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H87" t="n">
         <v>7121</v>
@@ -3037,7 +3037,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G92" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H92" t="n">
         <v>4665</v>
@@ -3066,7 +3066,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G93" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H93" t="n">
         <v>17678</v>
@@ -3095,7 +3095,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G94" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H94" t="n">
         <v>3001</v>
@@ -3153,7 +3153,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G96" t="n">
-        <v>7.78231573104858</v>
+        <v>7.78231525421143</v>
       </c>
       <c r="H96" t="n">
         <v>15390</v>
@@ -3182,7 +3182,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G97" t="n">
-        <v>7.74369382858276</v>
+        <v>7.74369335174561</v>
       </c>
       <c r="H97" t="n">
         <v>25102</v>
@@ -3269,7 +3269,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>7.70507097244263</v>
+        <v>7.70507144927979</v>
       </c>
       <c r="H100" t="n">
         <v>2228</v>
@@ -3356,7 +3356,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>7.70507097244263</v>
+        <v>7.70507144927979</v>
       </c>
       <c r="H103" t="n">
         <v>238</v>
@@ -3588,7 +3588,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G111" t="n">
-        <v>7.78231573104858</v>
+        <v>7.78231525421143</v>
       </c>
       <c r="H111" t="n">
         <v>40906</v>
@@ -3617,7 +3617,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G112" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H112" t="n">
         <v>364</v>
@@ -3646,7 +3646,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G113" t="n">
-        <v>8.18784427642822</v>
+        <v>8.18784523010254</v>
       </c>
       <c r="H113" t="n">
         <v>4328</v>
@@ -3675,7 +3675,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>8.16853523254395</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H114" t="n">
         <v>4325</v>
@@ -3704,7 +3704,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>8.16853523254395</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H115" t="n">
         <v>3981</v>
@@ -3733,7 +3733,7 @@
         <v>8.5</v>
       </c>
       <c r="G116" t="n">
-        <v>8.20715522766113</v>
+        <v>8.20715618133545</v>
       </c>
       <c r="H116" t="n">
         <v>3300</v>
@@ -3907,7 +3907,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G122" t="n">
-        <v>8.41957664489746</v>
+        <v>8.41957759857178</v>
       </c>
       <c r="H122" t="n">
         <v>12777</v>
@@ -3936,7 +3936,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G123" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H123" t="n">
         <v>8043</v>
@@ -3994,7 +3994,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H125" t="n">
         <v>42823</v>
@@ -4110,7 +4110,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G129" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H129" t="n">
         <v>6000</v>
@@ -4168,7 +4168,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G131" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H131" t="n">
         <v>40100</v>
@@ -4255,7 +4255,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>8.65130710601807</v>
+        <v>8.65130805969238</v>
       </c>
       <c r="H134" t="n">
         <v>4553</v>
@@ -4400,7 +4400,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G139" t="n">
-        <v>8.5161304473877</v>
+        <v>8.51613140106201</v>
       </c>
       <c r="H139" t="n">
         <v>312</v>
@@ -4719,7 +4719,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G150" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H150" t="n">
         <v>4230</v>
@@ -4777,7 +4777,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G152" t="n">
-        <v>8.38095569610596</v>
+        <v>8.38095474243164</v>
       </c>
       <c r="H152" t="n">
         <v>7019</v>
@@ -4893,7 +4893,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G156" t="n">
-        <v>8.41957664489746</v>
+        <v>8.41957759857178</v>
       </c>
       <c r="H156" t="n">
         <v>9168</v>
@@ -4922,7 +4922,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G157" t="n">
-        <v>8.41957664489746</v>
+        <v>8.41957759857178</v>
       </c>
       <c r="H157" t="n">
         <v>10594</v>
@@ -5038,7 +5038,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G161" t="n">
-        <v>8.22646713256836</v>
+        <v>8.22646808624268</v>
       </c>
       <c r="H161" t="n">
         <v>18016</v>
@@ -5067,7 +5067,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G162" t="n">
-        <v>8.22646713256836</v>
+        <v>8.22646808624268</v>
       </c>
       <c r="H162" t="n">
         <v>257</v>
@@ -5125,7 +5125,7 @@
         <v>8.5</v>
       </c>
       <c r="G164" t="n">
-        <v>8.20715522766113</v>
+        <v>8.20715618133545</v>
       </c>
       <c r="H164" t="n">
         <v>18147</v>
@@ -5386,7 +5386,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G173" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H173" t="n">
         <v>7608</v>
@@ -5415,7 +5415,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G174" t="n">
-        <v>7.95611429214478</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H174" t="n">
         <v>9388</v>
@@ -5618,7 +5618,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G181" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H181" t="n">
         <v>20346</v>
@@ -5763,7 +5763,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H186" t="n">
         <v>3135</v>
@@ -5792,7 +5792,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G187" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H187" t="n">
         <v>2250</v>
@@ -5850,7 +5850,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G189" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H189" t="n">
         <v>5300</v>
@@ -5879,7 +5879,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G190" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H190" t="n">
         <v>3983</v>
@@ -6082,7 +6082,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G197" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H197" t="n">
         <v>21391</v>
@@ -6140,7 +6140,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G199" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H199" t="n">
         <v>20734</v>
@@ -6227,7 +6227,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G202" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H202" t="n">
         <v>3347</v>
@@ -6401,7 +6401,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G208" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H208" t="n">
         <v>1089</v>
@@ -6459,7 +6459,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G210" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H210" t="n">
         <v>1549</v>
@@ -6517,7 +6517,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G212" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H212" t="n">
         <v>12241</v>
@@ -6546,7 +6546,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H213" t="n">
         <v>55092</v>
@@ -6662,7 +6662,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G217" t="n">
-        <v>8.18784427642822</v>
+        <v>8.18784523010254</v>
       </c>
       <c r="H217" t="n">
         <v>3476</v>
@@ -6691,7 +6691,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G218" t="n">
-        <v>8.16853523254395</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H218" t="n">
         <v>1736</v>
@@ -6778,7 +6778,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>8.16853523254395</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H221" t="n">
         <v>7392</v>
@@ -6894,7 +6894,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>8.16853523254395</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H225" t="n">
         <v>1316</v>
@@ -6923,7 +6923,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G226" t="n">
-        <v>8.18784427642822</v>
+        <v>8.18784523010254</v>
       </c>
       <c r="H226" t="n">
         <v>1388</v>
@@ -7097,7 +7097,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H232" t="n">
         <v>11067</v>
@@ -7126,7 +7126,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>8.16853523254395</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H233" t="n">
         <v>6312</v>
@@ -7271,7 +7271,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G238" t="n">
-        <v>7.95611429214478</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H238" t="n">
         <v>3477</v>
@@ -7300,7 +7300,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G239" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H239" t="n">
         <v>6101</v>
@@ -7416,7 +7416,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G243" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H243" t="n">
         <v>3669</v>
@@ -7474,7 +7474,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G245" t="n">
-        <v>7.78231573104858</v>
+        <v>7.78231525421143</v>
       </c>
       <c r="H245" t="n">
         <v>2691</v>
@@ -7590,7 +7590,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G249" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H249" t="n">
         <v>1405</v>
@@ -7619,7 +7619,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G250" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H250" t="n">
         <v>4624</v>
@@ -7648,7 +7648,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G251" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H251" t="n">
         <v>17702</v>
@@ -7677,7 +7677,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G252" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H252" t="n">
         <v>4458</v>
@@ -7764,7 +7764,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G255" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H255" t="n">
         <v>18125</v>
@@ -7880,7 +7880,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H259" t="n">
         <v>13726</v>
@@ -7938,7 +7938,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G261" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H261" t="n">
         <v>2653</v>
@@ -7996,7 +7996,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H263" t="n">
         <v>15803</v>
@@ -8054,7 +8054,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G265" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H265" t="n">
         <v>18960</v>
@@ -8112,7 +8112,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G267" t="n">
-        <v>7.74369382858276</v>
+        <v>7.74369335174561</v>
       </c>
       <c r="H267" t="n">
         <v>16020</v>
@@ -8199,7 +8199,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G270" t="n">
-        <v>7.74369382858276</v>
+        <v>7.74369335174561</v>
       </c>
       <c r="H270" t="n">
         <v>40748</v>
@@ -8286,7 +8286,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G273" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H273" t="n">
         <v>7426</v>
@@ -8402,7 +8402,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G277" t="n">
-        <v>7.74369382858276</v>
+        <v>7.74369335174561</v>
       </c>
       <c r="H277" t="n">
         <v>3373</v>
@@ -8663,7 +8663,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G286" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H286" t="n">
         <v>2356</v>
@@ -8692,7 +8692,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G287" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H287" t="n">
         <v>14875</v>
@@ -8750,7 +8750,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G289" t="n">
-        <v>7.95611429214478</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H289" t="n">
         <v>6789</v>
@@ -8808,7 +8808,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G291" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H291" t="n">
         <v>6109</v>
@@ -8866,7 +8866,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G293" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H293" t="n">
         <v>11644</v>
@@ -8895,7 +8895,7 @@
         <v>8.5</v>
       </c>
       <c r="G294" t="n">
-        <v>8.20715522766113</v>
+        <v>8.20715618133545</v>
       </c>
       <c r="H294" t="n">
         <v>6062</v>
@@ -8953,7 +8953,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G296" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H296" t="n">
         <v>4509</v>
@@ -9040,7 +9040,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G299" t="n">
-        <v>8.43888664245605</v>
+        <v>8.43888759613037</v>
       </c>
       <c r="H299" t="n">
         <v>5531</v>
@@ -9214,7 +9214,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>8.65130710601807</v>
+        <v>8.65130805969238</v>
       </c>
       <c r="H305" t="n">
         <v>3325</v>
@@ -9243,7 +9243,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G306" t="n">
-        <v>8.38095569610596</v>
+        <v>8.38095474243164</v>
       </c>
       <c r="H306" t="n">
         <v>5373</v>
@@ -9272,7 +9272,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G307" t="n">
-        <v>8.65130710601807</v>
+        <v>8.65130805969238</v>
       </c>
       <c r="H307" t="n">
         <v>19782</v>
@@ -9301,7 +9301,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G308" t="n">
-        <v>8.70924091339111</v>
+        <v>8.70924186706543</v>
       </c>
       <c r="H308" t="n">
         <v>19262</v>
@@ -9359,7 +9359,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G310" t="n">
-        <v>8.92166137695312</v>
+        <v>8.92166233062744</v>
       </c>
       <c r="H310" t="n">
         <v>29147</v>
@@ -9446,7 +9446,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G313" t="n">
-        <v>8.70924091339111</v>
+        <v>8.70924186706543</v>
       </c>
       <c r="H313" t="n">
         <v>7173</v>
@@ -9504,7 +9504,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G315" t="n">
-        <v>8.5161304473877</v>
+        <v>8.51613140106201</v>
       </c>
       <c r="H315" t="n">
         <v>3379</v>
@@ -9620,7 +9620,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G319" t="n">
-        <v>8.41957664489746</v>
+        <v>8.41957759857178</v>
       </c>
       <c r="H319" t="n">
         <v>1746</v>
@@ -9649,7 +9649,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H320" t="n">
         <v>952</v>
@@ -9678,7 +9678,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H321" t="n">
         <v>1603</v>
@@ -9707,7 +9707,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G322" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H322" t="n">
         <v>14286</v>
@@ -9736,7 +9736,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G323" t="n">
-        <v>8.38095569610596</v>
+        <v>8.38095474243164</v>
       </c>
       <c r="H323" t="n">
         <v>27377</v>
@@ -9823,7 +9823,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G326" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H326" t="n">
         <v>3583</v>
@@ -9852,7 +9852,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H327" t="n">
         <v>1758</v>
@@ -9881,7 +9881,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G328" t="n">
-        <v>8.43888664245605</v>
+        <v>8.43888759613037</v>
       </c>
       <c r="H328" t="n">
         <v>4105</v>
@@ -9997,7 +9997,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G332" t="n">
-        <v>8.5161304473877</v>
+        <v>8.51613140106201</v>
       </c>
       <c r="H332" t="n">
         <v>28344</v>
@@ -10055,7 +10055,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>8.72855186462402</v>
+        <v>8.72855281829834</v>
       </c>
       <c r="H334" t="n">
         <v>10228</v>
@@ -10084,7 +10084,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G335" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H335" t="n">
         <v>18023</v>
@@ -10171,7 +10171,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>8.65130710601807</v>
+        <v>8.65130805969238</v>
       </c>
       <c r="H338" t="n">
         <v>20928</v>
@@ -10432,7 +10432,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G347" t="n">
-        <v>8.65130710601807</v>
+        <v>8.65130805969238</v>
       </c>
       <c r="H347" t="n">
         <v>3955</v>
@@ -10490,7 +10490,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G349" t="n">
-        <v>8.70924091339111</v>
+        <v>8.70924186706543</v>
       </c>
       <c r="H349" t="n">
         <v>20895</v>
@@ -10722,7 +10722,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>8.65130710601807</v>
+        <v>8.65130805969238</v>
       </c>
       <c r="H357" t="n">
         <v>2883</v>
@@ -10925,7 +10925,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G364" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H364" t="n">
         <v>1993</v>
@@ -10983,7 +10983,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G366" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H366" t="n">
         <v>3879</v>
@@ -11012,7 +11012,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G367" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H367" t="n">
         <v>17028</v>
@@ -29143,6 +29143,35 @@
         <v>29749</v>
       </c>
       <c r="I992" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="s">
+        <v>9</v>
+      </c>
+      <c r="B993" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C993" t="n">
+        <v>21.9500007629395</v>
+      </c>
+      <c r="D993" t="n">
+        <v>22.6000003814697</v>
+      </c>
+      <c r="E993" t="n">
+        <v>21.7000007629395</v>
+      </c>
+      <c r="F993" t="n">
+        <v>22</v>
+      </c>
+      <c r="G993" t="n">
+        <v>22</v>
+      </c>
+      <c r="H993" t="n">
+        <v>91116</v>
+      </c>
+      <c r="I993" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -514,7 +514,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G5" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H5" t="n">
         <v>15746</v>
@@ -572,7 +572,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G7" t="n">
-        <v>8.08163452148438</v>
+        <v>8.08163547515869</v>
       </c>
       <c r="H7" t="n">
         <v>2650</v>
@@ -601,7 +601,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G8" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H8" t="n">
         <v>3358</v>
@@ -659,7 +659,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G10" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H10" t="n">
         <v>6204</v>
@@ -688,7 +688,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G11" t="n">
-        <v>8.04301261901855</v>
+        <v>8.04301357269287</v>
       </c>
       <c r="H11" t="n">
         <v>66</v>
@@ -717,7 +717,7 @@
         <v>8.25</v>
       </c>
       <c r="G12" t="n">
-        <v>7.96576881408691</v>
+        <v>7.96576976776123</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
@@ -804,7 +804,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G15" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H15" t="n">
         <v>32</v>
@@ -862,7 +862,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G17" t="n">
-        <v>7.946457862854</v>
+        <v>7.94645738601685</v>
       </c>
       <c r="H17" t="n">
         <v>2333</v>
@@ -978,7 +978,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G21" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473524093628</v>
       </c>
       <c r="H21" t="n">
         <v>2849</v>
@@ -1007,7 +1007,7 @@
         <v>8.25</v>
       </c>
       <c r="G22" t="n">
-        <v>7.96576881408691</v>
+        <v>7.96576976776123</v>
       </c>
       <c r="H22" t="n">
         <v>1800</v>
@@ -1036,7 +1036,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G23" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611381530762</v>
       </c>
       <c r="H23" t="n">
         <v>480</v>
@@ -1065,7 +1065,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G24" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H24" t="n">
         <v>8168</v>
@@ -1297,7 +1297,7 @@
         <v>8.25</v>
       </c>
       <c r="G32" t="n">
-        <v>7.96576881408691</v>
+        <v>7.96576976776123</v>
       </c>
       <c r="H32" t="n">
         <v>10305</v>
@@ -1326,7 +1326,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H33" t="n">
         <v>3280</v>
@@ -1384,7 +1384,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H35" t="n">
         <v>8723</v>
@@ -1413,7 +1413,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G36" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H36" t="n">
         <v>411</v>
@@ -1442,7 +1442,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G37" t="n">
-        <v>8.02370166778564</v>
+        <v>8.02370262145996</v>
       </c>
       <c r="H37" t="n">
         <v>4958</v>
@@ -1471,7 +1471,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H38" t="n">
         <v>80</v>
@@ -1529,7 +1529,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G40" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H40" t="n">
         <v>3659</v>
@@ -1558,7 +1558,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G41" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H41" t="n">
         <v>3082</v>
@@ -1645,7 +1645,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G44" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H44" t="n">
         <v>15725</v>
@@ -1674,7 +1674,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G45" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H45" t="n">
         <v>8898</v>
@@ -1790,7 +1790,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G49" t="n">
-        <v>7.90783548355103</v>
+        <v>7.90783596038818</v>
       </c>
       <c r="H49" t="n">
         <v>9413</v>
@@ -1819,7 +1819,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H50" t="n">
         <v>15331</v>
@@ -1848,7 +1848,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G51" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H51" t="n">
         <v>8900</v>
@@ -1993,7 +1993,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G56" t="n">
-        <v>7.98508024215698</v>
+        <v>7.98508071899414</v>
       </c>
       <c r="H56" t="n">
         <v>8601</v>
@@ -2022,7 +2022,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H57" t="n">
         <v>1380</v>
@@ -2051,7 +2051,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H58" t="n">
         <v>12623</v>
@@ -2080,7 +2080,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G59" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473524093628</v>
       </c>
       <c r="H59" t="n">
         <v>3310</v>
@@ -2109,7 +2109,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G60" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473524093628</v>
       </c>
       <c r="H60" t="n">
         <v>12417</v>
@@ -2312,7 +2312,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G67" t="n">
-        <v>8.1202564239502</v>
+        <v>8.12025547027588</v>
       </c>
       <c r="H67" t="n">
         <v>969</v>
@@ -2341,7 +2341,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G68" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H68" t="n">
         <v>7666</v>
@@ -2370,7 +2370,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G69" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H69" t="n">
         <v>3050</v>
@@ -2399,7 +2399,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G70" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H70" t="n">
         <v>7975</v>
@@ -2457,7 +2457,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H72" t="n">
         <v>10401</v>
@@ -2486,7 +2486,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G73" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611381530762</v>
       </c>
       <c r="H73" t="n">
         <v>21359</v>
@@ -2515,7 +2515,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G74" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611381530762</v>
       </c>
       <c r="H74" t="n">
         <v>9297</v>
@@ -2544,7 +2544,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G75" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473524093628</v>
       </c>
       <c r="H75" t="n">
         <v>1884</v>
@@ -2602,7 +2602,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G77" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H77" t="n">
         <v>4665</v>
@@ -2631,7 +2631,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G78" t="n">
-        <v>8.1202564239502</v>
+        <v>8.12025547027588</v>
       </c>
       <c r="H78" t="n">
         <v>3676</v>
@@ -2660,7 +2660,7 @@
         <v>8.25</v>
       </c>
       <c r="G79" t="n">
-        <v>7.96576881408691</v>
+        <v>7.96576976776123</v>
       </c>
       <c r="H79" t="n">
         <v>3004</v>
@@ -2689,7 +2689,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G80" t="n">
-        <v>7.98508024215698</v>
+        <v>7.98508071899414</v>
       </c>
       <c r="H80" t="n">
         <v>2183</v>
@@ -2718,7 +2718,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H81" t="n">
         <v>2117</v>
@@ -2747,7 +2747,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G82" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H82" t="n">
         <v>1745</v>
@@ -2805,7 +2805,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G84" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H84" t="n">
         <v>6600</v>
@@ -2834,7 +2834,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G85" t="n">
-        <v>8.08163452148438</v>
+        <v>8.08163547515869</v>
       </c>
       <c r="H85" t="n">
         <v>3150</v>
@@ -2863,7 +2863,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>8.08163452148438</v>
+        <v>8.08163547515869</v>
       </c>
       <c r="H86" t="n">
         <v>500</v>
@@ -2892,7 +2892,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G87" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473524093628</v>
       </c>
       <c r="H87" t="n">
         <v>7121</v>
@@ -2950,7 +2950,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G89" t="n">
-        <v>7.98508024215698</v>
+        <v>7.98508071899414</v>
       </c>
       <c r="H89" t="n">
         <v>14762</v>
@@ -3008,7 +3008,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G91" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H91" t="n">
         <v>928</v>
@@ -3037,7 +3037,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G92" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H92" t="n">
         <v>4665</v>
@@ -3066,7 +3066,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G93" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H93" t="n">
         <v>17678</v>
@@ -3095,7 +3095,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G94" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H94" t="n">
         <v>3001</v>
@@ -3124,7 +3124,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G95" t="n">
-        <v>7.8209376335144</v>
+        <v>7.82093715667725</v>
       </c>
       <c r="H95" t="n">
         <v>33055</v>
@@ -3153,7 +3153,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G96" t="n">
-        <v>7.78231525421143</v>
+        <v>7.78231573104858</v>
       </c>
       <c r="H96" t="n">
         <v>15390</v>
@@ -3182,7 +3182,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G97" t="n">
-        <v>7.74369335174561</v>
+        <v>7.74369382858276</v>
       </c>
       <c r="H97" t="n">
         <v>25102</v>
@@ -3211,7 +3211,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G98" t="n">
-        <v>7.68576002120972</v>
+        <v>7.68576049804688</v>
       </c>
       <c r="H98" t="n">
         <v>27915</v>
@@ -3240,7 +3240,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>7.68576002120972</v>
+        <v>7.68576049804688</v>
       </c>
       <c r="H99" t="n">
         <v>6541</v>
@@ -3269,7 +3269,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>7.70507144927979</v>
+        <v>7.70507097244263</v>
       </c>
       <c r="H100" t="n">
         <v>2228</v>
@@ -3356,7 +3356,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>7.70507144927979</v>
+        <v>7.70507097244263</v>
       </c>
       <c r="H103" t="n">
         <v>238</v>
@@ -3385,7 +3385,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>7.68576002120972</v>
+        <v>7.68576049804688</v>
       </c>
       <c r="H104" t="n">
         <v>4845</v>
@@ -3501,7 +3501,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>7.62782764434814</v>
+        <v>7.6278281211853</v>
       </c>
       <c r="H108" t="n">
         <v>3757</v>
@@ -3588,7 +3588,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G111" t="n">
-        <v>7.78231525421143</v>
+        <v>7.78231573104858</v>
       </c>
       <c r="H111" t="n">
         <v>40906</v>
@@ -3675,7 +3675,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853332519531</v>
       </c>
       <c r="H114" t="n">
         <v>4325</v>
@@ -3704,7 +3704,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853332519531</v>
       </c>
       <c r="H115" t="n">
         <v>3981</v>
@@ -3791,7 +3791,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G118" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H118" t="n">
         <v>4146</v>
@@ -3820,7 +3820,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G119" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H119" t="n">
         <v>2963</v>
@@ -3849,7 +3849,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G120" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H120" t="n">
         <v>40121</v>
@@ -3994,7 +3994,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>8.49682140350342</v>
+        <v>8.4968204498291</v>
       </c>
       <c r="H125" t="n">
         <v>42823</v>
@@ -4052,7 +4052,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>8.61268711090088</v>
+        <v>8.61268615722656</v>
       </c>
       <c r="H127" t="n">
         <v>14042</v>
@@ -4081,7 +4081,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G128" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H128" t="n">
         <v>4585</v>
@@ -4110,7 +4110,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G129" t="n">
-        <v>8.49682140350342</v>
+        <v>8.4968204498291</v>
       </c>
       <c r="H129" t="n">
         <v>6000</v>
@@ -4139,7 +4139,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G130" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H130" t="n">
         <v>19296</v>
@@ -4197,7 +4197,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G132" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H132" t="n">
         <v>3386</v>
@@ -4284,7 +4284,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G135" t="n">
-        <v>8.47750949859619</v>
+        <v>8.47751045227051</v>
       </c>
       <c r="H135" t="n">
         <v>2684</v>
@@ -4313,7 +4313,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G136" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H136" t="n">
         <v>1044</v>
@@ -4371,7 +4371,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H138" t="n">
         <v>475</v>
@@ -4400,7 +4400,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G139" t="n">
-        <v>8.51613140106201</v>
+        <v>8.5161304473877</v>
       </c>
       <c r="H139" t="n">
         <v>312</v>
@@ -4429,7 +4429,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H140" t="n">
         <v>1058</v>
@@ -4545,7 +4545,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G144" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H144" t="n">
         <v>1986</v>
@@ -4603,7 +4603,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G146" t="n">
-        <v>8.34233379364014</v>
+        <v>8.34233283996582</v>
       </c>
       <c r="H146" t="n">
         <v>13733</v>
@@ -4748,7 +4748,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G151" t="n">
-        <v>8.34233379364014</v>
+        <v>8.34233283996582</v>
       </c>
       <c r="H151" t="n">
         <v>4010</v>
@@ -4777,7 +4777,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G152" t="n">
-        <v>8.38095474243164</v>
+        <v>8.38095569610596</v>
       </c>
       <c r="H152" t="n">
         <v>7019</v>
@@ -4806,7 +4806,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G153" t="n">
-        <v>8.34233379364014</v>
+        <v>8.34233283996582</v>
       </c>
       <c r="H153" t="n">
         <v>16815</v>
@@ -5038,7 +5038,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G161" t="n">
-        <v>8.22646808624268</v>
+        <v>8.22646713256836</v>
       </c>
       <c r="H161" t="n">
         <v>18016</v>
@@ -5067,7 +5067,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G162" t="n">
-        <v>8.22646808624268</v>
+        <v>8.22646713256836</v>
       </c>
       <c r="H162" t="n">
         <v>257</v>
@@ -5183,7 +5183,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G166" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H166" t="n">
         <v>9385</v>
@@ -5386,7 +5386,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G173" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473524093628</v>
       </c>
       <c r="H173" t="n">
         <v>7608</v>
@@ -5415,7 +5415,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G174" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611381530762</v>
       </c>
       <c r="H174" t="n">
         <v>9388</v>
@@ -5444,7 +5444,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G175" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H175" t="n">
         <v>4377</v>
@@ -5531,7 +5531,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G178" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H178" t="n">
         <v>10600</v>
@@ -5618,7 +5618,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G181" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H181" t="n">
         <v>20346</v>
@@ -5734,7 +5734,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G185" t="n">
-        <v>7.8209376335144</v>
+        <v>7.82093715667725</v>
       </c>
       <c r="H185" t="n">
         <v>4523</v>
@@ -5763,7 +5763,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H186" t="n">
         <v>3135</v>
@@ -5821,7 +5821,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>7.8209376335144</v>
+        <v>7.82093715667725</v>
       </c>
       <c r="H188" t="n">
         <v>271</v>
@@ -5850,7 +5850,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G189" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H189" t="n">
         <v>5300</v>
@@ -5879,7 +5879,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G190" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H190" t="n">
         <v>3983</v>
@@ -5908,7 +5908,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G191" t="n">
-        <v>7.8209376335144</v>
+        <v>7.82093715667725</v>
       </c>
       <c r="H191" t="n">
         <v>8096</v>
@@ -5937,7 +5937,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G192" t="n">
-        <v>7.8209376335144</v>
+        <v>7.82093715667725</v>
       </c>
       <c r="H192" t="n">
         <v>9675</v>
@@ -5995,7 +5995,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G194" t="n">
-        <v>7.8209376335144</v>
+        <v>7.82093715667725</v>
       </c>
       <c r="H194" t="n">
         <v>25407</v>
@@ -6053,7 +6053,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>7.8209376335144</v>
+        <v>7.82093715667725</v>
       </c>
       <c r="H196" t="n">
         <v>9084</v>
@@ -6082,7 +6082,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G197" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H197" t="n">
         <v>21391</v>
@@ -6140,7 +6140,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G199" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H199" t="n">
         <v>20734</v>
@@ -6227,7 +6227,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G202" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H202" t="n">
         <v>3347</v>
@@ -6401,7 +6401,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G208" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H208" t="n">
         <v>1089</v>
@@ -6459,7 +6459,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G210" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H210" t="n">
         <v>1549</v>
@@ -6517,7 +6517,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G212" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H212" t="n">
         <v>12241</v>
@@ -6546,7 +6546,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H213" t="n">
         <v>55092</v>
@@ -6575,7 +6575,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G214" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H214" t="n">
         <v>8492</v>
@@ -6604,7 +6604,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G215" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H215" t="n">
         <v>4566</v>
@@ -6633,7 +6633,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G216" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H216" t="n">
         <v>16342</v>
@@ -6691,7 +6691,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G218" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853332519531</v>
       </c>
       <c r="H218" t="n">
         <v>1736</v>
@@ -6778,7 +6778,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853332519531</v>
       </c>
       <c r="H221" t="n">
         <v>7392</v>
@@ -6836,7 +6836,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G223" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H223" t="n">
         <v>5300</v>
@@ -6894,7 +6894,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853332519531</v>
       </c>
       <c r="H225" t="n">
         <v>1316</v>
@@ -7097,7 +7097,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H232" t="n">
         <v>11067</v>
@@ -7126,7 +7126,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853332519531</v>
       </c>
       <c r="H233" t="n">
         <v>6312</v>
@@ -7155,7 +7155,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G234" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H234" t="n">
         <v>826</v>
@@ -7184,7 +7184,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H235" t="n">
         <v>752</v>
@@ -7271,7 +7271,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G238" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611381530762</v>
       </c>
       <c r="H238" t="n">
         <v>3477</v>
@@ -7300,7 +7300,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G239" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H239" t="n">
         <v>6101</v>
@@ -7416,7 +7416,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G243" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H243" t="n">
         <v>3669</v>
@@ -7474,7 +7474,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G245" t="n">
-        <v>7.78231525421143</v>
+        <v>7.78231573104858</v>
       </c>
       <c r="H245" t="n">
         <v>2691</v>
@@ -7648,7 +7648,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G251" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473524093628</v>
       </c>
       <c r="H251" t="n">
         <v>17702</v>
@@ -7677,7 +7677,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G252" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473524093628</v>
       </c>
       <c r="H252" t="n">
         <v>4458</v>
@@ -7764,7 +7764,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G255" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473524093628</v>
       </c>
       <c r="H255" t="n">
         <v>18125</v>
@@ -7880,7 +7880,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H259" t="n">
         <v>13726</v>
@@ -7909,7 +7909,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G260" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H260" t="n">
         <v>14869</v>
@@ -7938,7 +7938,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G261" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473524093628</v>
       </c>
       <c r="H261" t="n">
         <v>2653</v>
@@ -7996,7 +7996,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H263" t="n">
         <v>15803</v>
@@ -8025,7 +8025,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G264" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H264" t="n">
         <v>7199</v>
@@ -8112,7 +8112,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G267" t="n">
-        <v>7.74369335174561</v>
+        <v>7.74369382858276</v>
       </c>
       <c r="H267" t="n">
         <v>16020</v>
@@ -8170,7 +8170,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>7.68576002120972</v>
+        <v>7.68576049804688</v>
       </c>
       <c r="H269" t="n">
         <v>22886</v>
@@ -8199,7 +8199,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G270" t="n">
-        <v>7.74369335174561</v>
+        <v>7.74369382858276</v>
       </c>
       <c r="H270" t="n">
         <v>40748</v>
@@ -8257,7 +8257,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>7.68576002120972</v>
+        <v>7.68576049804688</v>
       </c>
       <c r="H272" t="n">
         <v>12707</v>
@@ -8286,7 +8286,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G273" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H273" t="n">
         <v>7426</v>
@@ -8373,7 +8373,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>7.68576002120972</v>
+        <v>7.68576049804688</v>
       </c>
       <c r="H276" t="n">
         <v>22466</v>
@@ -8402,7 +8402,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G277" t="n">
-        <v>7.74369335174561</v>
+        <v>7.74369382858276</v>
       </c>
       <c r="H277" t="n">
         <v>3373</v>
@@ -8431,7 +8431,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G278" t="n">
-        <v>7.68576002120972</v>
+        <v>7.68576049804688</v>
       </c>
       <c r="H278" t="n">
         <v>7771</v>
@@ -8489,7 +8489,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G280" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H280" t="n">
         <v>7266</v>
@@ -8547,7 +8547,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G282" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H282" t="n">
         <v>2416</v>
@@ -8605,7 +8605,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G284" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H284" t="n">
         <v>12131</v>
@@ -8663,7 +8663,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G286" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H286" t="n">
         <v>2356</v>
@@ -8692,7 +8692,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G287" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H287" t="n">
         <v>14875</v>
@@ -8721,7 +8721,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G288" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H288" t="n">
         <v>4850</v>
@@ -8750,7 +8750,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G289" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611381530762</v>
       </c>
       <c r="H289" t="n">
         <v>6789</v>
@@ -8837,7 +8837,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G292" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H292" t="n">
         <v>2670</v>
@@ -8866,7 +8866,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G293" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H293" t="n">
         <v>11644</v>
@@ -9069,7 +9069,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G300" t="n">
-        <v>8.61268711090088</v>
+        <v>8.61268615722656</v>
       </c>
       <c r="H300" t="n">
         <v>26734</v>
@@ -9156,7 +9156,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G303" t="n">
-        <v>8.63199710845947</v>
+        <v>8.63199615478516</v>
       </c>
       <c r="H303" t="n">
         <v>22705</v>
@@ -9185,7 +9185,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G304" t="n">
-        <v>8.74786376953125</v>
+        <v>8.74786281585693</v>
       </c>
       <c r="H304" t="n">
         <v>26905</v>
@@ -9243,7 +9243,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G306" t="n">
-        <v>8.38095474243164</v>
+        <v>8.38095569610596</v>
       </c>
       <c r="H306" t="n">
         <v>5373</v>
@@ -9359,7 +9359,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G310" t="n">
-        <v>8.92166233062744</v>
+        <v>8.92166042327881</v>
       </c>
       <c r="H310" t="n">
         <v>29147</v>
@@ -9475,7 +9475,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>8.61268711090088</v>
+        <v>8.61268615722656</v>
       </c>
       <c r="H314" t="n">
         <v>3755</v>
@@ -9504,7 +9504,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G315" t="n">
-        <v>8.51613140106201</v>
+        <v>8.5161304473877</v>
       </c>
       <c r="H315" t="n">
         <v>3379</v>
@@ -9562,7 +9562,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H317" t="n">
         <v>6105</v>
@@ -9591,7 +9591,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G318" t="n">
-        <v>8.47750949859619</v>
+        <v>8.47751045227051</v>
       </c>
       <c r="H318" t="n">
         <v>3095</v>
@@ -9649,7 +9649,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>8.49682140350342</v>
+        <v>8.4968204498291</v>
       </c>
       <c r="H320" t="n">
         <v>952</v>
@@ -9678,7 +9678,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>8.49682140350342</v>
+        <v>8.4968204498291</v>
       </c>
       <c r="H321" t="n">
         <v>1603</v>
@@ -9707,7 +9707,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G322" t="n">
-        <v>8.49682140350342</v>
+        <v>8.4968204498291</v>
       </c>
       <c r="H322" t="n">
         <v>14286</v>
@@ -9736,7 +9736,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G323" t="n">
-        <v>8.38095474243164</v>
+        <v>8.38095569610596</v>
       </c>
       <c r="H323" t="n">
         <v>27377</v>
@@ -9823,7 +9823,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G326" t="n">
-        <v>8.49682140350342</v>
+        <v>8.4968204498291</v>
       </c>
       <c r="H326" t="n">
         <v>3583</v>
@@ -9852,7 +9852,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>8.49682140350342</v>
+        <v>8.4968204498291</v>
       </c>
       <c r="H327" t="n">
         <v>1758</v>
@@ -9997,7 +9997,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G332" t="n">
-        <v>8.51613140106201</v>
+        <v>8.5161304473877</v>
       </c>
       <c r="H332" t="n">
         <v>28344</v>
@@ -10055,7 +10055,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>8.72855281829834</v>
+        <v>8.72855186462402</v>
       </c>
       <c r="H334" t="n">
         <v>10228</v>
@@ -10084,7 +10084,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G335" t="n">
-        <v>8.49682140350342</v>
+        <v>8.4968204498291</v>
       </c>
       <c r="H335" t="n">
         <v>18023</v>
@@ -10113,7 +10113,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G336" t="n">
-        <v>8.47750949859619</v>
+        <v>8.47751045227051</v>
       </c>
       <c r="H336" t="n">
         <v>12212</v>
@@ -10142,7 +10142,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G337" t="n">
-        <v>8.74786376953125</v>
+        <v>8.74786281585693</v>
       </c>
       <c r="H337" t="n">
         <v>26896</v>
@@ -10287,7 +10287,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G342" t="n">
-        <v>8.74786376953125</v>
+        <v>8.74786281585693</v>
       </c>
       <c r="H342" t="n">
         <v>36062</v>
@@ -10316,7 +10316,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G343" t="n">
-        <v>8.74786376953125</v>
+        <v>8.74786281585693</v>
       </c>
       <c r="H343" t="n">
         <v>59646</v>
@@ -10345,7 +10345,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G344" t="n">
-        <v>8.74786376953125</v>
+        <v>8.74786281585693</v>
       </c>
       <c r="H344" t="n">
         <v>998</v>
@@ -10461,7 +10461,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G348" t="n">
-        <v>8.76717376708984</v>
+        <v>8.76717472076416</v>
       </c>
       <c r="H348" t="n">
         <v>8969</v>
@@ -10635,7 +10635,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G354" t="n">
-        <v>8.63199710845947</v>
+        <v>8.63199615478516</v>
       </c>
       <c r="H354" t="n">
         <v>746</v>
@@ -10809,7 +10809,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G360" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H360" t="n">
         <v>1072</v>
@@ -10838,7 +10838,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H361" t="n">
         <v>299</v>
@@ -10925,7 +10925,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G364" t="n">
-        <v>8.49682140350342</v>
+        <v>8.4968204498291</v>
       </c>
       <c r="H364" t="n">
         <v>1993</v>
@@ -10983,7 +10983,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G366" t="n">
-        <v>8.49682140350342</v>
+        <v>8.4968204498291</v>
       </c>
       <c r="H366" t="n">
         <v>3879</v>
@@ -11012,7 +11012,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G367" t="n">
-        <v>8.49682140350342</v>
+        <v>8.4968204498291</v>
       </c>
       <c r="H367" t="n">
         <v>17028</v>
@@ -11070,7 +11070,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G369" t="n">
-        <v>8.47750949859619</v>
+        <v>8.47751045227051</v>
       </c>
       <c r="H369" t="n">
         <v>1997</v>
@@ -11099,7 +11099,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G370" t="n">
-        <v>8.47750949859619</v>
+        <v>8.47751045227051</v>
       </c>
       <c r="H370" t="n">
         <v>3224</v>
@@ -11128,7 +11128,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G371" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H371" t="n">
         <v>5429</v>
@@ -11157,7 +11157,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G372" t="n">
-        <v>8.74786376953125</v>
+        <v>8.74786281585693</v>
       </c>
       <c r="H372" t="n">
         <v>8776</v>
@@ -11331,7 +11331,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G378" t="n">
-        <v>8.6548433303833</v>
+        <v>8.65484237670898</v>
       </c>
       <c r="H378" t="n">
         <v>4178</v>
@@ -11360,7 +11360,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G379" t="n">
-        <v>8.67433547973633</v>
+        <v>8.67433452606201</v>
       </c>
       <c r="H379" t="n">
         <v>8702</v>
@@ -11389,7 +11389,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G380" t="n">
-        <v>8.55737781524658</v>
+        <v>8.5573787689209</v>
       </c>
       <c r="H380" t="n">
         <v>3988</v>
@@ -11418,7 +11418,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>8.57687187194824</v>
+        <v>8.57687091827393</v>
       </c>
       <c r="H381" t="n">
         <v>581</v>
@@ -11447,7 +11447,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G382" t="n">
-        <v>8.79129409790039</v>
+        <v>8.79129314422607</v>
       </c>
       <c r="H382" t="n">
         <v>10780</v>
@@ -11505,7 +11505,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G384" t="n">
-        <v>8.67433547973633</v>
+        <v>8.67433452606201</v>
       </c>
       <c r="H384" t="n">
         <v>2635</v>
@@ -11592,7 +11592,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G387" t="n">
-        <v>8.71332168579102</v>
+        <v>8.7133207321167</v>
       </c>
       <c r="H387" t="n">
         <v>13870</v>
@@ -11650,7 +11650,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G389" t="n">
-        <v>8.73281478881836</v>
+        <v>8.73281383514404</v>
       </c>
       <c r="H389" t="n">
         <v>7250</v>
@@ -11679,7 +11679,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>8.73281478881836</v>
+        <v>8.73281383514404</v>
       </c>
       <c r="H390" t="n">
         <v>8078</v>
@@ -11708,7 +11708,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G391" t="n">
-        <v>8.73281478881836</v>
+        <v>8.73281383514404</v>
       </c>
       <c r="H391" t="n">
         <v>16733</v>
@@ -11737,7 +11737,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>8.73281478881836</v>
+        <v>8.73281383514404</v>
       </c>
       <c r="H392" t="n">
         <v>4956</v>
@@ -11766,7 +11766,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>8.73281478881836</v>
+        <v>8.73281383514404</v>
       </c>
       <c r="H393" t="n">
         <v>6859</v>
@@ -11795,7 +11795,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G394" t="n">
-        <v>8.73281478881836</v>
+        <v>8.73281383514404</v>
       </c>
       <c r="H394" t="n">
         <v>8968</v>
@@ -11853,7 +11853,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G396" t="n">
-        <v>8.67433547973633</v>
+        <v>8.67433452606201</v>
       </c>
       <c r="H396" t="n">
         <v>11489</v>
@@ -11882,7 +11882,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G397" t="n">
-        <v>8.73281478881836</v>
+        <v>8.73281383514404</v>
       </c>
       <c r="H397" t="n">
         <v>15733</v>
@@ -12520,7 +12520,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G419" t="n">
-        <v>8.79129409790039</v>
+        <v>8.79129314422607</v>
       </c>
       <c r="H419" t="n">
         <v>8156</v>
@@ -12549,7 +12549,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G420" t="n">
-        <v>8.79129409790039</v>
+        <v>8.79129314422607</v>
       </c>
       <c r="H420" t="n">
         <v>1912</v>
@@ -12810,7 +12810,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G429" t="n">
-        <v>8.94723701477051</v>
+        <v>8.94723606109619</v>
       </c>
       <c r="H429" t="n">
         <v>9874</v>
@@ -12897,7 +12897,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>8.67433547973633</v>
+        <v>8.67433452606201</v>
       </c>
       <c r="H432" t="n">
         <v>20846</v>
@@ -13013,7 +13013,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G436" t="n">
-        <v>8.94723701477051</v>
+        <v>8.94723606109619</v>
       </c>
       <c r="H436" t="n">
         <v>14343</v>
@@ -13071,7 +13071,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G438" t="n">
-        <v>8.98622226715088</v>
+        <v>8.98622131347656</v>
       </c>
       <c r="H438" t="n">
         <v>5816</v>
@@ -13100,7 +13100,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G439" t="n">
-        <v>8.96672916412354</v>
+        <v>8.96672821044922</v>
       </c>
       <c r="H439" t="n">
         <v>2547</v>
@@ -13129,7 +13129,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>8.96672916412354</v>
+        <v>8.96672821044922</v>
       </c>
       <c r="H440" t="n">
         <v>1343</v>
@@ -13158,7 +13158,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>8.96672916412354</v>
+        <v>8.96672821044922</v>
       </c>
       <c r="H441" t="n">
         <v>3058</v>
@@ -13274,7 +13274,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G445" t="n">
-        <v>9.12267112731934</v>
+        <v>9.12267208099365</v>
       </c>
       <c r="H445" t="n">
         <v>3603</v>
@@ -13332,7 +13332,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G447" t="n">
-        <v>9.20064258575439</v>
+        <v>9.20064353942871</v>
       </c>
       <c r="H447" t="n">
         <v>17365</v>
@@ -13448,7 +13448,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G451" t="n">
-        <v>9.51252937316895</v>
+        <v>9.51253032684326</v>
       </c>
       <c r="H451" t="n">
         <v>22601</v>
@@ -13477,7 +13477,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G452" t="n">
-        <v>9.51252937316895</v>
+        <v>9.51253032684326</v>
       </c>
       <c r="H452" t="n">
         <v>18345</v>
@@ -13680,7 +13680,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G459" t="n">
-        <v>9.37607860565186</v>
+        <v>9.37607955932617</v>
       </c>
       <c r="H459" t="n">
         <v>12381</v>
@@ -13767,7 +13767,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G462" t="n">
-        <v>9.37607860565186</v>
+        <v>9.37607955932617</v>
       </c>
       <c r="H462" t="n">
         <v>47114</v>
@@ -13796,7 +13796,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G463" t="n">
-        <v>9.37607860565186</v>
+        <v>9.37607955932617</v>
       </c>
       <c r="H463" t="n">
         <v>28654</v>
@@ -13825,7 +13825,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>9.37607860565186</v>
+        <v>9.37607955932617</v>
       </c>
       <c r="H464" t="n">
         <v>44888</v>
@@ -13883,7 +13883,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G466" t="n">
-        <v>9.2981071472168</v>
+        <v>9.29810810089111</v>
       </c>
       <c r="H466" t="n">
         <v>34817</v>
@@ -13941,7 +13941,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G468" t="n">
-        <v>9.62948703765869</v>
+        <v>9.62948799133301</v>
       </c>
       <c r="H468" t="n">
         <v>49815</v>
@@ -14028,7 +14028,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G471" t="n">
-        <v>9.2981071472168</v>
+        <v>9.29810810089111</v>
       </c>
       <c r="H471" t="n">
         <v>103158</v>
@@ -14057,7 +14057,7 @@
         <v>9.5</v>
       </c>
       <c r="G472" t="n">
-        <v>9.25912189483643</v>
+        <v>9.25912284851074</v>
       </c>
       <c r="H472" t="n">
         <v>75426</v>
@@ -14202,7 +14202,7 @@
         <v>9.5</v>
       </c>
       <c r="G477" t="n">
-        <v>9.25912189483643</v>
+        <v>9.25912284851074</v>
       </c>
       <c r="H477" t="n">
         <v>24059</v>
@@ -14231,7 +14231,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>9.2981071472168</v>
+        <v>9.29810810089111</v>
       </c>
       <c r="H478" t="n">
         <v>8181</v>
@@ -14318,7 +14318,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G481" t="n">
-        <v>9.590500831604</v>
+        <v>9.59050178527832</v>
       </c>
       <c r="H481" t="n">
         <v>27152</v>
@@ -14376,7 +14376,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G483" t="n">
-        <v>10.087571144104</v>
+        <v>10.0875701904297</v>
       </c>
       <c r="H483" t="n">
         <v>99460</v>
@@ -14405,7 +14405,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G484" t="n">
-        <v>10.1850347518921</v>
+        <v>10.1850337982178</v>
       </c>
       <c r="H484" t="n">
         <v>42643</v>
@@ -14463,7 +14463,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G486" t="n">
-        <v>10.3312311172485</v>
+        <v>10.3312320709229</v>
       </c>
       <c r="H486" t="n">
         <v>14224</v>
@@ -14492,7 +14492,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G487" t="n">
-        <v>10.3312311172485</v>
+        <v>10.3312320709229</v>
       </c>
       <c r="H487" t="n">
         <v>40436</v>
@@ -14521,7 +14521,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>10.1850347518921</v>
+        <v>10.1850337982178</v>
       </c>
       <c r="H488" t="n">
         <v>58963</v>
@@ -14550,7 +14550,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G489" t="n">
-        <v>10.0388374328613</v>
+        <v>10.0388383865356</v>
       </c>
       <c r="H489" t="n">
         <v>31431</v>
@@ -14608,7 +14608,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>10.3312311172485</v>
+        <v>10.3312320709229</v>
       </c>
       <c r="H491" t="n">
         <v>7253</v>
@@ -14666,7 +14666,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G493" t="n">
-        <v>10.3312311172485</v>
+        <v>10.3312320709229</v>
       </c>
       <c r="H493" t="n">
         <v>9014</v>
@@ -14753,7 +14753,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>10.1363019943237</v>
+        <v>10.1363010406494</v>
       </c>
       <c r="H496" t="n">
         <v>7452</v>
@@ -14782,7 +14782,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>10.1363019943237</v>
+        <v>10.1363010406494</v>
       </c>
       <c r="H497" t="n">
         <v>21636</v>
@@ -14811,7 +14811,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G498" t="n">
-        <v>10.1363019943237</v>
+        <v>10.1363010406494</v>
       </c>
       <c r="H498" t="n">
         <v>34176</v>
@@ -14840,7 +14840,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G499" t="n">
-        <v>10.1850347518921</v>
+        <v>10.1850337982178</v>
       </c>
       <c r="H499" t="n">
         <v>73943</v>
@@ -14869,7 +14869,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>10.0388374328613</v>
+        <v>10.0388383865356</v>
       </c>
       <c r="H500" t="n">
         <v>53170</v>
@@ -14927,7 +14927,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G502" t="n">
-        <v>10.6723556518555</v>
+        <v>10.6723566055298</v>
       </c>
       <c r="H502" t="n">
         <v>93835</v>
@@ -14985,7 +14985,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G504" t="n">
-        <v>10.6723556518555</v>
+        <v>10.6723566055298</v>
       </c>
       <c r="H504" t="n">
         <v>42791</v>
@@ -15217,7 +15217,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G512" t="n">
-        <v>11.0134830474854</v>
+        <v>11.013482093811</v>
       </c>
       <c r="H512" t="n">
         <v>81844</v>
@@ -15246,7 +15246,7 @@
         <v>11.25</v>
       </c>
       <c r="G513" t="n">
-        <v>10.9647493362427</v>
+        <v>10.964750289917</v>
       </c>
       <c r="H513" t="n">
         <v>65236</v>
@@ -15507,7 +15507,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G522" t="n">
-        <v>11.3058767318726</v>
+        <v>11.3058757781982</v>
       </c>
       <c r="H522" t="n">
         <v>74151</v>
@@ -15594,7 +15594,7 @@
         <v>12</v>
       </c>
       <c r="G525" t="n">
-        <v>11.6957340240479</v>
+        <v>11.6957330703735</v>
       </c>
       <c r="H525" t="n">
         <v>165830</v>
@@ -15681,7 +15681,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>12.0368595123291</v>
+        <v>12.0368585586548</v>
       </c>
       <c r="H528" t="n">
         <v>204255</v>
@@ -15913,7 +15913,7 @@
         <v>12</v>
       </c>
       <c r="G536" t="n">
-        <v>11.6957340240479</v>
+        <v>11.6957330703735</v>
       </c>
       <c r="H536" t="n">
         <v>25535</v>
@@ -16000,7 +16000,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G539" t="n">
-        <v>11.4033403396606</v>
+        <v>11.4033393859863</v>
       </c>
       <c r="H539" t="n">
         <v>20898</v>
@@ -16087,7 +16087,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G542" t="n">
-        <v>11.4033403396606</v>
+        <v>11.4033393859863</v>
       </c>
       <c r="H542" t="n">
         <v>25345</v>
@@ -16203,7 +16203,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G546" t="n">
-        <v>11.4033403396606</v>
+        <v>11.4033393859863</v>
       </c>
       <c r="H546" t="n">
         <v>47534</v>
@@ -16261,7 +16261,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G548" t="n">
-        <v>11.7931976318359</v>
+        <v>11.7931985855103</v>
       </c>
       <c r="H548" t="n">
         <v>47029</v>
@@ -16348,7 +16348,7 @@
         <v>12</v>
       </c>
       <c r="G551" t="n">
-        <v>11.6957340240479</v>
+        <v>11.6957330703735</v>
       </c>
       <c r="H551" t="n">
         <v>30358</v>
@@ -16435,7 +16435,7 @@
         <v>12</v>
       </c>
       <c r="G554" t="n">
-        <v>11.6957340240479</v>
+        <v>11.6957330703735</v>
       </c>
       <c r="H554" t="n">
         <v>8761</v>
@@ -16464,7 +16464,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G555" t="n">
-        <v>11.7931976318359</v>
+        <v>11.7931985855103</v>
       </c>
       <c r="H555" t="n">
         <v>13533</v>
@@ -16493,7 +16493,7 @@
         <v>12</v>
       </c>
       <c r="G556" t="n">
-        <v>11.6957340240479</v>
+        <v>11.6957330703735</v>
       </c>
       <c r="H556" t="n">
         <v>5809</v>
@@ -16522,7 +16522,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G557" t="n">
-        <v>11.890661239624</v>
+        <v>11.8906621932983</v>
       </c>
       <c r="H557" t="n">
         <v>10698</v>
@@ -16609,7 +16609,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>11.7931976318359</v>
+        <v>11.7931985855103</v>
       </c>
       <c r="H560" t="n">
         <v>93481</v>
@@ -16638,7 +16638,7 @@
         <v>12</v>
       </c>
       <c r="G561" t="n">
-        <v>11.6957340240479</v>
+        <v>11.6957330703735</v>
       </c>
       <c r="H561" t="n">
         <v>34950</v>
@@ -16667,7 +16667,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G562" t="n">
-        <v>11.6470012664795</v>
+        <v>11.6470003128052</v>
       </c>
       <c r="H562" t="n">
         <v>15367</v>
@@ -16696,7 +16696,7 @@
         <v>12</v>
       </c>
       <c r="G563" t="n">
-        <v>11.6957340240479</v>
+        <v>11.6957330703735</v>
       </c>
       <c r="H563" t="n">
         <v>39064</v>
@@ -16725,7 +16725,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>11.7931976318359</v>
+        <v>11.7931985855103</v>
       </c>
       <c r="H564" t="n">
         <v>22959</v>
@@ -16754,7 +16754,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G565" t="n">
-        <v>11.6470012664795</v>
+        <v>11.6470003128052</v>
       </c>
       <c r="H565" t="n">
         <v>14206</v>
@@ -16812,7 +16812,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G567" t="n">
-        <v>11.7931976318359</v>
+        <v>11.7931985855103</v>
       </c>
       <c r="H567" t="n">
         <v>56931</v>
@@ -16841,7 +16841,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>11.7931976318359</v>
+        <v>11.7931985855103</v>
       </c>
       <c r="H568" t="n">
         <v>12168</v>
@@ -16957,7 +16957,7 @@
         <v>12</v>
       </c>
       <c r="G572" t="n">
-        <v>11.6957340240479</v>
+        <v>11.6957330703735</v>
       </c>
       <c r="H572" t="n">
         <v>50297</v>
@@ -17102,7 +17102,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G577" t="n">
-        <v>11.890661239624</v>
+        <v>11.8906621932983</v>
       </c>
       <c r="H577" t="n">
         <v>8377</v>
@@ -17827,7 +17827,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G602" t="n">
-        <v>12.7093629837036</v>
+        <v>12.7093639373779</v>
       </c>
       <c r="H602" t="n">
         <v>70858</v>
@@ -17885,7 +17885,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G604" t="n">
-        <v>12.6898708343506</v>
+        <v>12.6898717880249</v>
       </c>
       <c r="H604" t="n">
         <v>57453</v>
@@ -17943,7 +17943,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G606" t="n">
-        <v>12.865306854248</v>
+        <v>12.8653059005737</v>
       </c>
       <c r="H606" t="n">
         <v>71717</v>
@@ -18088,7 +18088,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G611" t="n">
-        <v>13.3136434555054</v>
+        <v>13.3136425018311</v>
       </c>
       <c r="H611" t="n">
         <v>69440</v>
@@ -18233,7 +18233,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G616" t="n">
-        <v>13.4500932693481</v>
+        <v>13.4500942230225</v>
       </c>
       <c r="H616" t="n">
         <v>45178</v>
@@ -18320,7 +18320,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G619" t="n">
-        <v>13.3136434555054</v>
+        <v>13.3136425018311</v>
       </c>
       <c r="H619" t="n">
         <v>22500</v>
@@ -18349,7 +18349,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G620" t="n">
-        <v>13.3136434555054</v>
+        <v>13.3136425018311</v>
       </c>
       <c r="H620" t="n">
         <v>23712</v>
@@ -18407,7 +18407,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G622" t="n">
-        <v>13.6255292892456</v>
+        <v>13.6255283355713</v>
       </c>
       <c r="H622" t="n">
         <v>54015</v>
@@ -18523,7 +18523,7 @@
         <v>14.5</v>
       </c>
       <c r="G626" t="n">
-        <v>14.132345199585</v>
+        <v>14.1323442459106</v>
       </c>
       <c r="H626" t="n">
         <v>143325</v>
@@ -29172,6 +29172,35 @@
         <v>91116</v>
       </c>
       <c r="I993" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="s">
+        <v>9</v>
+      </c>
+      <c r="B994" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C994" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="D994" t="n">
+        <v>22.4500007629395</v>
+      </c>
+      <c r="E994" t="n">
+        <v>22.1499996185303</v>
+      </c>
+      <c r="F994" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="G994" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="H994" t="n">
+        <v>28947</v>
+      </c>
+      <c r="I994" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -485,7 +485,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G4" t="n">
-        <v>8.13956832885742</v>
+        <v>8.13956737518311</v>
       </c>
       <c r="H4" t="n">
         <v>6993</v>
@@ -543,7 +543,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G6" t="n">
-        <v>8.18784523010254</v>
+        <v>8.18784427642822</v>
       </c>
       <c r="H6" t="n">
         <v>2771</v>
@@ -572,7 +572,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G7" t="n">
-        <v>8.08163547515869</v>
+        <v>8.08163452148438</v>
       </c>
       <c r="H7" t="n">
         <v>2650</v>
@@ -630,7 +630,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G9" t="n">
-        <v>8.10094547271729</v>
+        <v>8.1009464263916</v>
       </c>
       <c r="H9" t="n">
         <v>1320</v>
@@ -746,7 +746,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G13" t="n">
-        <v>8.18784523010254</v>
+        <v>8.18784427642822</v>
       </c>
       <c r="H13" t="n">
         <v>4230</v>
@@ -862,7 +862,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G17" t="n">
-        <v>7.94645738601685</v>
+        <v>7.946457862854</v>
       </c>
       <c r="H17" t="n">
         <v>2333</v>
@@ -891,7 +891,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G18" t="n">
-        <v>8.17818927764893</v>
+        <v>8.17819023132324</v>
       </c>
       <c r="H18" t="n">
         <v>980</v>
@@ -920,7 +920,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G19" t="n">
-        <v>8.13956832885742</v>
+        <v>8.13956737518311</v>
       </c>
       <c r="H19" t="n">
         <v>505</v>
@@ -949,7 +949,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G20" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H20" t="n">
         <v>1660</v>
@@ -978,7 +978,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G21" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H21" t="n">
         <v>2849</v>
@@ -1036,7 +1036,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G23" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H23" t="n">
         <v>480</v>
@@ -1094,7 +1094,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G25" t="n">
-        <v>8.17818927764893</v>
+        <v>8.17819023132324</v>
       </c>
       <c r="H25" t="n">
         <v>384</v>
@@ -1152,7 +1152,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G27" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H27" t="n">
         <v>15457</v>
@@ -1239,7 +1239,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G30" t="n">
-        <v>8.10094547271729</v>
+        <v>8.1009464263916</v>
       </c>
       <c r="H30" t="n">
         <v>578</v>
@@ -1268,7 +1268,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G31" t="n">
-        <v>8.10094547271729</v>
+        <v>8.1009464263916</v>
       </c>
       <c r="H31" t="n">
         <v>332</v>
@@ -1326,7 +1326,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H33" t="n">
         <v>3280</v>
@@ -1384,7 +1384,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H35" t="n">
         <v>8723</v>
@@ -1500,7 +1500,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H39" t="n">
         <v>559</v>
@@ -1645,7 +1645,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G44" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H44" t="n">
         <v>15725</v>
@@ -1674,7 +1674,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G45" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H45" t="n">
         <v>8898</v>
@@ -1761,7 +1761,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G48" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H48" t="n">
         <v>13323</v>
@@ -1819,7 +1819,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H50" t="n">
         <v>15331</v>
@@ -1848,7 +1848,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G51" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H51" t="n">
         <v>8900</v>
@@ -1877,7 +1877,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G52" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H52" t="n">
         <v>11521</v>
@@ -1935,7 +1935,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G54" t="n">
-        <v>8.13956832885742</v>
+        <v>8.13956737518311</v>
       </c>
       <c r="H54" t="n">
         <v>24286</v>
@@ -1993,7 +1993,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G56" t="n">
-        <v>7.98508071899414</v>
+        <v>7.9850811958313</v>
       </c>
       <c r="H56" t="n">
         <v>8601</v>
@@ -2022,7 +2022,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H57" t="n">
         <v>1380</v>
@@ -2051,7 +2051,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H58" t="n">
         <v>12623</v>
@@ -2080,7 +2080,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G59" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H59" t="n">
         <v>3310</v>
@@ -2109,7 +2109,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G60" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H60" t="n">
         <v>12417</v>
@@ -2167,7 +2167,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>8.25543403625488</v>
+        <v>8.25543308258057</v>
       </c>
       <c r="H62" t="n">
         <v>7660</v>
@@ -2225,7 +2225,7 @@
         <v>8.5</v>
       </c>
       <c r="G64" t="n">
-        <v>8.20715618133545</v>
+        <v>8.20715522766113</v>
       </c>
       <c r="H64" t="n">
         <v>659</v>
@@ -2254,7 +2254,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G65" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H65" t="n">
         <v>3106</v>
@@ -2283,7 +2283,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G66" t="n">
-        <v>8.13956832885742</v>
+        <v>8.13956737518311</v>
       </c>
       <c r="H66" t="n">
         <v>13</v>
@@ -2312,7 +2312,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G67" t="n">
-        <v>8.12025547027588</v>
+        <v>8.1202564239502</v>
       </c>
       <c r="H67" t="n">
         <v>969</v>
@@ -2370,7 +2370,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G69" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H69" t="n">
         <v>3050</v>
@@ -2428,7 +2428,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G71" t="n">
-        <v>8.12991237640381</v>
+        <v>8.12991142272949</v>
       </c>
       <c r="H71" t="n">
         <v>2651</v>
@@ -2457,7 +2457,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H72" t="n">
         <v>10401</v>
@@ -2486,7 +2486,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G73" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H73" t="n">
         <v>21359</v>
@@ -2515,7 +2515,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G74" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H74" t="n">
         <v>9297</v>
@@ -2544,7 +2544,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G75" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H75" t="n">
         <v>1884</v>
@@ -2631,7 +2631,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G78" t="n">
-        <v>8.12025547027588</v>
+        <v>8.1202564239502</v>
       </c>
       <c r="H78" t="n">
         <v>3676</v>
@@ -2689,7 +2689,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G80" t="n">
-        <v>7.98508071899414</v>
+        <v>7.9850811958313</v>
       </c>
       <c r="H80" t="n">
         <v>2183</v>
@@ -2718,7 +2718,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H81" t="n">
         <v>2117</v>
@@ -2805,7 +2805,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G84" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H84" t="n">
         <v>6600</v>
@@ -2834,7 +2834,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G85" t="n">
-        <v>8.08163547515869</v>
+        <v>8.08163452148438</v>
       </c>
       <c r="H85" t="n">
         <v>3150</v>
@@ -2863,7 +2863,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>8.08163547515869</v>
+        <v>8.08163452148438</v>
       </c>
       <c r="H86" t="n">
         <v>500</v>
@@ -2892,7 +2892,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G87" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H87" t="n">
         <v>7121</v>
@@ -2921,7 +2921,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G88" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H88" t="n">
         <v>27333</v>
@@ -2950,7 +2950,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G89" t="n">
-        <v>7.98508071899414</v>
+        <v>7.9850811958313</v>
       </c>
       <c r="H89" t="n">
         <v>14762</v>
@@ -2979,7 +2979,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G90" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H90" t="n">
         <v>3277</v>
@@ -3037,7 +3037,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G92" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H92" t="n">
         <v>4665</v>
@@ -3066,7 +3066,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G93" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H93" t="n">
         <v>17678</v>
@@ -3095,7 +3095,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G94" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H94" t="n">
         <v>3001</v>
@@ -3211,7 +3211,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G98" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H98" t="n">
         <v>27915</v>
@@ -3240,7 +3240,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H99" t="n">
         <v>6541</v>
@@ -3269,7 +3269,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>7.70507097244263</v>
+        <v>7.70507144927979</v>
       </c>
       <c r="H100" t="n">
         <v>2228</v>
@@ -3356,7 +3356,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>7.70507097244263</v>
+        <v>7.70507144927979</v>
       </c>
       <c r="H103" t="n">
         <v>238</v>
@@ -3385,7 +3385,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H104" t="n">
         <v>4845</v>
@@ -3414,7 +3414,7 @@
         <v>8</v>
       </c>
       <c r="G105" t="n">
-        <v>7.7243824005127</v>
+        <v>7.72438192367554</v>
       </c>
       <c r="H105" t="n">
         <v>2592</v>
@@ -3443,7 +3443,7 @@
         <v>8</v>
       </c>
       <c r="G106" t="n">
-        <v>7.7243824005127</v>
+        <v>7.72438192367554</v>
       </c>
       <c r="H106" t="n">
         <v>805</v>
@@ -3501,7 +3501,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>7.6278281211853</v>
+        <v>7.62782764434814</v>
       </c>
       <c r="H108" t="n">
         <v>3757</v>
@@ -3530,7 +3530,7 @@
         <v>8</v>
       </c>
       <c r="G109" t="n">
-        <v>7.7243824005127</v>
+        <v>7.72438192367554</v>
       </c>
       <c r="H109" t="n">
         <v>2584</v>
@@ -3646,7 +3646,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G113" t="n">
-        <v>8.18784523010254</v>
+        <v>8.18784427642822</v>
       </c>
       <c r="H113" t="n">
         <v>4328</v>
@@ -3675,7 +3675,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H114" t="n">
         <v>4325</v>
@@ -3704,7 +3704,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H115" t="n">
         <v>3981</v>
@@ -3733,7 +3733,7 @@
         <v>8.5</v>
       </c>
       <c r="G116" t="n">
-        <v>8.20715618133545</v>
+        <v>8.20715522766113</v>
       </c>
       <c r="H116" t="n">
         <v>3300</v>
@@ -4023,7 +4023,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G126" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H126" t="n">
         <v>6006</v>
@@ -4342,7 +4342,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G137" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H137" t="n">
         <v>2700</v>
@@ -4458,7 +4458,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G141" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H141" t="n">
         <v>2149</v>
@@ -4487,7 +4487,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G142" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H142" t="n">
         <v>1962</v>
@@ -4516,7 +4516,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G143" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H143" t="n">
         <v>3502</v>
@@ -4777,7 +4777,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G152" t="n">
-        <v>8.38095569610596</v>
+        <v>8.38095474243164</v>
       </c>
       <c r="H152" t="n">
         <v>7019</v>
@@ -5038,7 +5038,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G161" t="n">
-        <v>8.22646713256836</v>
+        <v>8.22646808624268</v>
       </c>
       <c r="H161" t="n">
         <v>18016</v>
@@ -5067,7 +5067,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G162" t="n">
-        <v>8.22646713256836</v>
+        <v>8.22646808624268</v>
       </c>
       <c r="H162" t="n">
         <v>257</v>
@@ -5125,7 +5125,7 @@
         <v>8.5</v>
       </c>
       <c r="G164" t="n">
-        <v>8.20715618133545</v>
+        <v>8.20715522766113</v>
       </c>
       <c r="H164" t="n">
         <v>18147</v>
@@ -5154,7 +5154,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H165" t="n">
         <v>1441</v>
@@ -5241,7 +5241,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H168" t="n">
         <v>4677</v>
@@ -5270,7 +5270,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H169" t="n">
         <v>670</v>
@@ -5299,7 +5299,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G170" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H170" t="n">
         <v>4833</v>
@@ -5386,7 +5386,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G173" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H173" t="n">
         <v>7608</v>
@@ -5415,7 +5415,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G174" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H174" t="n">
         <v>9388</v>
@@ -5473,7 +5473,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G176" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H176" t="n">
         <v>21179</v>
@@ -5560,7 +5560,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H179" t="n">
         <v>6577</v>
@@ -5589,7 +5589,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H180" t="n">
         <v>14463</v>
@@ -5618,7 +5618,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G181" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H181" t="n">
         <v>20346</v>
@@ -5647,7 +5647,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H182" t="n">
         <v>35125</v>
@@ -5676,7 +5676,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G183" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H183" t="n">
         <v>3370</v>
@@ -5763,7 +5763,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H186" t="n">
         <v>3135</v>
@@ -5850,7 +5850,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G189" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H189" t="n">
         <v>5300</v>
@@ -5879,7 +5879,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G190" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H190" t="n">
         <v>3983</v>
@@ -6082,7 +6082,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G197" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H197" t="n">
         <v>21391</v>
@@ -6111,7 +6111,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G198" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H198" t="n">
         <v>6073</v>
@@ -6140,7 +6140,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G199" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H199" t="n">
         <v>20734</v>
@@ -6227,7 +6227,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G202" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H202" t="n">
         <v>3347</v>
@@ -6256,7 +6256,7 @@
         <v>8</v>
       </c>
       <c r="G203" t="n">
-        <v>7.7243824005127</v>
+        <v>7.72438192367554</v>
       </c>
       <c r="H203" t="n">
         <v>14236</v>
@@ -6401,7 +6401,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G208" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H208" t="n">
         <v>1089</v>
@@ -6459,7 +6459,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G210" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H210" t="n">
         <v>1549</v>
@@ -6517,7 +6517,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G212" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H212" t="n">
         <v>12241</v>
@@ -6546,7 +6546,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H213" t="n">
         <v>55092</v>
@@ -6662,7 +6662,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G217" t="n">
-        <v>8.18784523010254</v>
+        <v>8.18784427642822</v>
       </c>
       <c r="H217" t="n">
         <v>3476</v>
@@ -6691,7 +6691,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G218" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H218" t="n">
         <v>1736</v>
@@ -6749,7 +6749,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G220" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H220" t="n">
         <v>8198</v>
@@ -6778,7 +6778,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H221" t="n">
         <v>7392</v>
@@ -6807,7 +6807,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G222" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H222" t="n">
         <v>5722</v>
@@ -6894,7 +6894,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H225" t="n">
         <v>1316</v>
@@ -6923,7 +6923,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G226" t="n">
-        <v>8.18784523010254</v>
+        <v>8.18784427642822</v>
       </c>
       <c r="H226" t="n">
         <v>1388</v>
@@ -7010,7 +7010,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G229" t="n">
-        <v>8.12991237640381</v>
+        <v>8.12991142272949</v>
       </c>
       <c r="H229" t="n">
         <v>20282</v>
@@ -7039,7 +7039,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G230" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H230" t="n">
         <v>2393</v>
@@ -7068,7 +7068,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G231" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H231" t="n">
         <v>7440</v>
@@ -7097,7 +7097,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H232" t="n">
         <v>11067</v>
@@ -7126,7 +7126,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H233" t="n">
         <v>6312</v>
@@ -7213,7 +7213,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G236" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H236" t="n">
         <v>8366</v>
@@ -7271,7 +7271,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G238" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H238" t="n">
         <v>3477</v>
@@ -7300,7 +7300,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G239" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H239" t="n">
         <v>6101</v>
@@ -7416,7 +7416,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G243" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H243" t="n">
         <v>3669</v>
@@ -7503,7 +7503,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G246" t="n">
-        <v>8.0912914276123</v>
+        <v>8.09129047393799</v>
       </c>
       <c r="H246" t="n">
         <v>31120</v>
@@ -7648,7 +7648,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G251" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H251" t="n">
         <v>17702</v>
@@ -7677,7 +7677,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G252" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H252" t="n">
         <v>4458</v>
@@ -7735,7 +7735,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H254" t="n">
         <v>10600</v>
@@ -7764,7 +7764,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G255" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H255" t="n">
         <v>18125</v>
@@ -7880,7 +7880,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H259" t="n">
         <v>13726</v>
@@ -7938,7 +7938,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G261" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H261" t="n">
         <v>2653</v>
@@ -7996,7 +7996,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H263" t="n">
         <v>15803</v>
@@ -8170,7 +8170,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H269" t="n">
         <v>22886</v>
@@ -8228,7 +8228,7 @@
         <v>8</v>
       </c>
       <c r="G271" t="n">
-        <v>7.7243824005127</v>
+        <v>7.72438192367554</v>
       </c>
       <c r="H271" t="n">
         <v>11242</v>
@@ -8257,7 +8257,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H272" t="n">
         <v>12707</v>
@@ -8286,7 +8286,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G273" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H273" t="n">
         <v>7426</v>
@@ -8373,7 +8373,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H276" t="n">
         <v>22466</v>
@@ -8431,7 +8431,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G278" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H278" t="n">
         <v>7771</v>
@@ -8576,7 +8576,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G283" t="n">
-        <v>7.9174919128418</v>
+        <v>7.91749143600464</v>
       </c>
       <c r="H283" t="n">
         <v>1082</v>
@@ -8634,7 +8634,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G285" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H285" t="n">
         <v>2580</v>
@@ -8663,7 +8663,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G286" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H286" t="n">
         <v>2356</v>
@@ -8692,7 +8692,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G287" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H287" t="n">
         <v>14875</v>
@@ -8750,7 +8750,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G289" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H289" t="n">
         <v>6789</v>
@@ -8779,7 +8779,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>8.05266857147217</v>
+        <v>8.05266952514648</v>
       </c>
       <c r="H290" t="n">
         <v>1377</v>
@@ -8866,7 +8866,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G293" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H293" t="n">
         <v>11644</v>
@@ -8895,7 +8895,7 @@
         <v>8.5</v>
       </c>
       <c r="G294" t="n">
-        <v>8.20715618133545</v>
+        <v>8.20715522766113</v>
       </c>
       <c r="H294" t="n">
         <v>6062</v>
@@ -9185,7 +9185,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G304" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H304" t="n">
         <v>26905</v>
@@ -9243,7 +9243,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G306" t="n">
-        <v>8.38095569610596</v>
+        <v>8.38095474243164</v>
       </c>
       <c r="H306" t="n">
         <v>5373</v>
@@ -9301,7 +9301,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G308" t="n">
-        <v>8.70924186706543</v>
+        <v>8.70924091339111</v>
       </c>
       <c r="H308" t="n">
         <v>19262</v>
@@ -9359,7 +9359,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G310" t="n">
-        <v>8.92166042327881</v>
+        <v>8.92166137695312</v>
       </c>
       <c r="H310" t="n">
         <v>29147</v>
@@ -9446,7 +9446,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G313" t="n">
-        <v>8.70924186706543</v>
+        <v>8.70924091339111</v>
       </c>
       <c r="H313" t="n">
         <v>7173</v>
@@ -9533,7 +9533,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G316" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H316" t="n">
         <v>20275</v>
@@ -9736,7 +9736,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G323" t="n">
-        <v>8.38095569610596</v>
+        <v>8.38095474243164</v>
       </c>
       <c r="H323" t="n">
         <v>27377</v>
@@ -10055,7 +10055,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>8.72855186462402</v>
+        <v>8.72855281829834</v>
       </c>
       <c r="H334" t="n">
         <v>10228</v>
@@ -10142,7 +10142,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G337" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H337" t="n">
         <v>26896</v>
@@ -10287,7 +10287,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G342" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H342" t="n">
         <v>36062</v>
@@ -10316,7 +10316,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G343" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H343" t="n">
         <v>59646</v>
@@ -10345,7 +10345,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G344" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H344" t="n">
         <v>998</v>
@@ -10461,7 +10461,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G348" t="n">
-        <v>8.76717472076416</v>
+        <v>8.76717376708984</v>
       </c>
       <c r="H348" t="n">
         <v>8969</v>
@@ -10490,7 +10490,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G349" t="n">
-        <v>8.70924186706543</v>
+        <v>8.70924091339111</v>
       </c>
       <c r="H349" t="n">
         <v>20895</v>
@@ -10664,7 +10664,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G355" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H355" t="n">
         <v>649</v>
@@ -10693,7 +10693,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G356" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H356" t="n">
         <v>1221</v>
@@ -10751,7 +10751,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G358" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H358" t="n">
         <v>55213</v>
@@ -10780,7 +10780,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H359" t="n">
         <v>1434</v>
@@ -10896,7 +10896,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G363" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H363" t="n">
         <v>1804</v>
@@ -10954,7 +10954,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G365" t="n">
-        <v>8.59337520599365</v>
+        <v>8.59337425231934</v>
       </c>
       <c r="H365" t="n">
         <v>6093</v>
@@ -11157,7 +11157,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G372" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H372" t="n">
         <v>8776</v>
@@ -29201,6 +29201,35 @@
         <v>28947</v>
       </c>
       <c r="I994" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="s">
+        <v>9</v>
+      </c>
+      <c r="B995" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C995" t="n">
+        <v>22.3500003814697</v>
+      </c>
+      <c r="D995" t="n">
+        <v>22.3500003814697</v>
+      </c>
+      <c r="E995" t="n">
+        <v>22.1000003814697</v>
+      </c>
+      <c r="F995" t="n">
+        <v>22.2999992370605</v>
+      </c>
+      <c r="G995" t="n">
+        <v>22.2999992370605</v>
+      </c>
+      <c r="H995" t="n">
+        <v>6273</v>
+      </c>
+      <c r="I995" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2" t="n">
-        <v>8.30371189117432</v>
+        <v>8.3037109375</v>
       </c>
       <c r="H2" t="n">
         <v>4793</v>
@@ -485,7 +485,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G4" t="n">
-        <v>8.13956737518311</v>
+        <v>8.13956832885742</v>
       </c>
       <c r="H4" t="n">
         <v>6993</v>
@@ -514,7 +514,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G5" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H5" t="n">
         <v>15746</v>
@@ -601,7 +601,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G8" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H8" t="n">
         <v>3358</v>
@@ -659,7 +659,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G10" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H10" t="n">
         <v>6204</v>
@@ -688,7 +688,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G11" t="n">
-        <v>8.04301357269287</v>
+        <v>8.04301261901855</v>
       </c>
       <c r="H11" t="n">
         <v>66</v>
@@ -717,7 +717,7 @@
         <v>8.25</v>
       </c>
       <c r="G12" t="n">
-        <v>7.96576976776123</v>
+        <v>7.96576881408691</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
@@ -804,7 +804,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G15" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H15" t="n">
         <v>32</v>
@@ -862,7 +862,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G17" t="n">
-        <v>7.946457862854</v>
+        <v>7.94645881652832</v>
       </c>
       <c r="H17" t="n">
         <v>2333</v>
@@ -920,7 +920,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G19" t="n">
-        <v>8.13956737518311</v>
+        <v>8.13956832885742</v>
       </c>
       <c r="H19" t="n">
         <v>505</v>
@@ -949,7 +949,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G20" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H20" t="n">
         <v>1660</v>
@@ -978,7 +978,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G21" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H21" t="n">
         <v>2849</v>
@@ -1007,7 +1007,7 @@
         <v>8.25</v>
       </c>
       <c r="G22" t="n">
-        <v>7.96576976776123</v>
+        <v>7.96576881408691</v>
       </c>
       <c r="H22" t="n">
         <v>1800</v>
@@ -1036,7 +1036,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G23" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611429214478</v>
       </c>
       <c r="H23" t="n">
         <v>480</v>
@@ -1065,7 +1065,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G24" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H24" t="n">
         <v>8168</v>
@@ -1152,7 +1152,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G27" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H27" t="n">
         <v>15457</v>
@@ -1297,7 +1297,7 @@
         <v>8.25</v>
       </c>
       <c r="G32" t="n">
-        <v>7.96576976776123</v>
+        <v>7.96576881408691</v>
       </c>
       <c r="H32" t="n">
         <v>10305</v>
@@ -1326,7 +1326,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H33" t="n">
         <v>3280</v>
@@ -1384,7 +1384,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H35" t="n">
         <v>8723</v>
@@ -1413,7 +1413,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G36" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H36" t="n">
         <v>411</v>
@@ -1471,7 +1471,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H38" t="n">
         <v>80</v>
@@ -1500,7 +1500,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H39" t="n">
         <v>559</v>
@@ -1529,7 +1529,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G40" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H40" t="n">
         <v>3659</v>
@@ -1558,7 +1558,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G41" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H41" t="n">
         <v>3082</v>
@@ -1645,7 +1645,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G44" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H44" t="n">
         <v>15725</v>
@@ -1674,7 +1674,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G45" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H45" t="n">
         <v>8898</v>
@@ -1761,7 +1761,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G48" t="n">
-        <v>7.91749143600464</v>
+        <v>7.9174919128418</v>
       </c>
       <c r="H48" t="n">
         <v>13323</v>
@@ -1790,7 +1790,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G49" t="n">
-        <v>7.90783596038818</v>
+        <v>7.90783548355103</v>
       </c>
       <c r="H49" t="n">
         <v>9413</v>
@@ -1819,7 +1819,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H50" t="n">
         <v>15331</v>
@@ -1848,7 +1848,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G51" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H51" t="n">
         <v>8900</v>
@@ -1877,7 +1877,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G52" t="n">
-        <v>7.91749143600464</v>
+        <v>7.9174919128418</v>
       </c>
       <c r="H52" t="n">
         <v>11521</v>
@@ -1935,7 +1935,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G54" t="n">
-        <v>8.13956737518311</v>
+        <v>8.13956832885742</v>
       </c>
       <c r="H54" t="n">
         <v>24286</v>
@@ -1993,7 +1993,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G56" t="n">
-        <v>7.9850811958313</v>
+        <v>7.98508024215698</v>
       </c>
       <c r="H56" t="n">
         <v>8601</v>
@@ -2022,7 +2022,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H57" t="n">
         <v>1380</v>
@@ -2051,7 +2051,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H58" t="n">
         <v>12623</v>
@@ -2080,7 +2080,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G59" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H59" t="n">
         <v>3310</v>
@@ -2109,7 +2109,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G60" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H60" t="n">
         <v>12417</v>
@@ -2138,7 +2138,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G61" t="n">
-        <v>8.30371189117432</v>
+        <v>8.3037109375</v>
       </c>
       <c r="H61" t="n">
         <v>13315</v>
@@ -2167,7 +2167,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>8.25543308258057</v>
+        <v>8.25543403625488</v>
       </c>
       <c r="H62" t="n">
         <v>7660</v>
@@ -2254,7 +2254,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G65" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H65" t="n">
         <v>3106</v>
@@ -2283,7 +2283,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G66" t="n">
-        <v>8.13956737518311</v>
+        <v>8.13956832885742</v>
       </c>
       <c r="H66" t="n">
         <v>13</v>
@@ -2312,7 +2312,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G67" t="n">
-        <v>8.1202564239502</v>
+        <v>8.12025737762451</v>
       </c>
       <c r="H67" t="n">
         <v>969</v>
@@ -2341,7 +2341,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G68" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H68" t="n">
         <v>7666</v>
@@ -2370,7 +2370,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G69" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H69" t="n">
         <v>3050</v>
@@ -2399,7 +2399,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G70" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H70" t="n">
         <v>7975</v>
@@ -2428,7 +2428,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G71" t="n">
-        <v>8.12991142272949</v>
+        <v>8.12991237640381</v>
       </c>
       <c r="H71" t="n">
         <v>2651</v>
@@ -2457,7 +2457,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H72" t="n">
         <v>10401</v>
@@ -2486,7 +2486,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G73" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611429214478</v>
       </c>
       <c r="H73" t="n">
         <v>21359</v>
@@ -2515,7 +2515,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G74" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611429214478</v>
       </c>
       <c r="H74" t="n">
         <v>9297</v>
@@ -2544,7 +2544,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G75" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H75" t="n">
         <v>1884</v>
@@ -2602,7 +2602,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G77" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H77" t="n">
         <v>4665</v>
@@ -2631,7 +2631,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G78" t="n">
-        <v>8.1202564239502</v>
+        <v>8.12025737762451</v>
       </c>
       <c r="H78" t="n">
         <v>3676</v>
@@ -2660,7 +2660,7 @@
         <v>8.25</v>
       </c>
       <c r="G79" t="n">
-        <v>7.96576976776123</v>
+        <v>7.96576881408691</v>
       </c>
       <c r="H79" t="n">
         <v>3004</v>
@@ -2689,7 +2689,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G80" t="n">
-        <v>7.9850811958313</v>
+        <v>7.98508024215698</v>
       </c>
       <c r="H80" t="n">
         <v>2183</v>
@@ -2718,7 +2718,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H81" t="n">
         <v>2117</v>
@@ -2747,7 +2747,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G82" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H82" t="n">
         <v>1745</v>
@@ -2805,7 +2805,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G84" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H84" t="n">
         <v>6600</v>
@@ -2892,7 +2892,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G87" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H87" t="n">
         <v>7121</v>
@@ -2921,7 +2921,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G88" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H88" t="n">
         <v>27333</v>
@@ -2950,7 +2950,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G89" t="n">
-        <v>7.9850811958313</v>
+        <v>7.98508024215698</v>
       </c>
       <c r="H89" t="n">
         <v>14762</v>
@@ -2979,7 +2979,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G90" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H90" t="n">
         <v>3277</v>
@@ -3008,7 +3008,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G91" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H91" t="n">
         <v>928</v>
@@ -3037,7 +3037,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G92" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H92" t="n">
         <v>4665</v>
@@ -3066,7 +3066,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G93" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H93" t="n">
         <v>17678</v>
@@ -3095,7 +3095,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G94" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H94" t="n">
         <v>3001</v>
@@ -3124,7 +3124,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G95" t="n">
-        <v>7.82093715667725</v>
+        <v>7.8209376335144</v>
       </c>
       <c r="H95" t="n">
         <v>33055</v>
@@ -3269,7 +3269,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>7.70507144927979</v>
+        <v>7.70507097244263</v>
       </c>
       <c r="H100" t="n">
         <v>2228</v>
@@ -3356,7 +3356,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>7.70507144927979</v>
+        <v>7.70507097244263</v>
       </c>
       <c r="H103" t="n">
         <v>238</v>
@@ -3414,7 +3414,7 @@
         <v>8</v>
       </c>
       <c r="G105" t="n">
-        <v>7.72438192367554</v>
+        <v>7.7243824005127</v>
       </c>
       <c r="H105" t="n">
         <v>2592</v>
@@ -3443,7 +3443,7 @@
         <v>8</v>
       </c>
       <c r="G106" t="n">
-        <v>7.72438192367554</v>
+        <v>7.7243824005127</v>
       </c>
       <c r="H106" t="n">
         <v>805</v>
@@ -3530,7 +3530,7 @@
         <v>8</v>
       </c>
       <c r="G109" t="n">
-        <v>7.72438192367554</v>
+        <v>7.7243824005127</v>
       </c>
       <c r="H109" t="n">
         <v>2584</v>
@@ -3617,7 +3617,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G112" t="n">
-        <v>7.87886953353882</v>
+        <v>7.87887001037598</v>
       </c>
       <c r="H112" t="n">
         <v>364</v>
@@ -3675,7 +3675,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853523254395</v>
       </c>
       <c r="H114" t="n">
         <v>4325</v>
@@ -3704,7 +3704,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853523254395</v>
       </c>
       <c r="H115" t="n">
         <v>3981</v>
@@ -3791,7 +3791,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G118" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H118" t="n">
         <v>4146</v>
@@ -3820,7 +3820,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G119" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H119" t="n">
         <v>2963</v>
@@ -3849,7 +3849,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G120" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H120" t="n">
         <v>40121</v>
@@ -3907,7 +3907,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G122" t="n">
-        <v>8.41957759857178</v>
+        <v>8.41957664489746</v>
       </c>
       <c r="H122" t="n">
         <v>12777</v>
@@ -3936,7 +3936,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G123" t="n">
-        <v>8.30371189117432</v>
+        <v>8.3037109375</v>
       </c>
       <c r="H123" t="n">
         <v>8043</v>
@@ -4023,7 +4023,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G126" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H126" t="n">
         <v>6006</v>
@@ -4052,7 +4052,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>8.61268615722656</v>
+        <v>8.61268711090088</v>
       </c>
       <c r="H127" t="n">
         <v>14042</v>
@@ -4081,7 +4081,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G128" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H128" t="n">
         <v>4585</v>
@@ -4139,7 +4139,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G130" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H130" t="n">
         <v>19296</v>
@@ -4168,7 +4168,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G131" t="n">
-        <v>8.30371189117432</v>
+        <v>8.3037109375</v>
       </c>
       <c r="H131" t="n">
         <v>40100</v>
@@ -4197,7 +4197,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G132" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H132" t="n">
         <v>3386</v>
@@ -4255,7 +4255,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>8.65130805969238</v>
+        <v>8.65130710601807</v>
       </c>
       <c r="H134" t="n">
         <v>4553</v>
@@ -4284,7 +4284,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G135" t="n">
-        <v>8.47751045227051</v>
+        <v>8.47750949859619</v>
       </c>
       <c r="H135" t="n">
         <v>2684</v>
@@ -4313,7 +4313,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G136" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H136" t="n">
         <v>1044</v>
@@ -4342,7 +4342,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G137" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H137" t="n">
         <v>2700</v>
@@ -4371,7 +4371,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H138" t="n">
         <v>475</v>
@@ -4429,7 +4429,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H140" t="n">
         <v>1058</v>
@@ -4458,7 +4458,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G141" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H141" t="n">
         <v>2149</v>
@@ -4487,7 +4487,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G142" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H142" t="n">
         <v>1962</v>
@@ -4516,7 +4516,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G143" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H143" t="n">
         <v>3502</v>
@@ -4545,7 +4545,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G144" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H144" t="n">
         <v>1986</v>
@@ -4603,7 +4603,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G146" t="n">
-        <v>8.34233283996582</v>
+        <v>8.34233379364014</v>
       </c>
       <c r="H146" t="n">
         <v>13733</v>
@@ -4719,7 +4719,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G150" t="n">
-        <v>8.30371189117432</v>
+        <v>8.3037109375</v>
       </c>
       <c r="H150" t="n">
         <v>4230</v>
@@ -4748,7 +4748,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G151" t="n">
-        <v>8.34233283996582</v>
+        <v>8.34233379364014</v>
       </c>
       <c r="H151" t="n">
         <v>4010</v>
@@ -4777,7 +4777,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G152" t="n">
-        <v>8.38095474243164</v>
+        <v>8.38095569610596</v>
       </c>
       <c r="H152" t="n">
         <v>7019</v>
@@ -4806,7 +4806,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G153" t="n">
-        <v>8.34233283996582</v>
+        <v>8.34233379364014</v>
       </c>
       <c r="H153" t="n">
         <v>16815</v>
@@ -4893,7 +4893,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G156" t="n">
-        <v>8.41957759857178</v>
+        <v>8.41957664489746</v>
       </c>
       <c r="H156" t="n">
         <v>9168</v>
@@ -4922,7 +4922,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G157" t="n">
-        <v>8.41957759857178</v>
+        <v>8.41957664489746</v>
       </c>
       <c r="H157" t="n">
         <v>10594</v>
@@ -5038,7 +5038,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G161" t="n">
-        <v>8.22646808624268</v>
+        <v>8.22646713256836</v>
       </c>
       <c r="H161" t="n">
         <v>18016</v>
@@ -5067,7 +5067,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G162" t="n">
-        <v>8.22646808624268</v>
+        <v>8.22646713256836</v>
       </c>
       <c r="H162" t="n">
         <v>257</v>
@@ -5154,7 +5154,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H165" t="n">
         <v>1441</v>
@@ -5183,7 +5183,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G166" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H166" t="n">
         <v>9385</v>
@@ -5241,7 +5241,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H168" t="n">
         <v>4677</v>
@@ -5270,7 +5270,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H169" t="n">
         <v>670</v>
@@ -5299,7 +5299,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G170" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H170" t="n">
         <v>4833</v>
@@ -5386,7 +5386,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G173" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H173" t="n">
         <v>7608</v>
@@ -5415,7 +5415,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G174" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611429214478</v>
       </c>
       <c r="H174" t="n">
         <v>9388</v>
@@ -5444,7 +5444,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G175" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H175" t="n">
         <v>4377</v>
@@ -5473,7 +5473,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G176" t="n">
-        <v>7.91749143600464</v>
+        <v>7.9174919128418</v>
       </c>
       <c r="H176" t="n">
         <v>21179</v>
@@ -5531,7 +5531,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G178" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H178" t="n">
         <v>10600</v>
@@ -5560,7 +5560,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H179" t="n">
         <v>6577</v>
@@ -5589,7 +5589,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>7.91749143600464</v>
+        <v>7.9174919128418</v>
       </c>
       <c r="H180" t="n">
         <v>14463</v>
@@ -5618,7 +5618,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G181" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H181" t="n">
         <v>20346</v>
@@ -5647,7 +5647,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>7.91749143600464</v>
+        <v>7.9174919128418</v>
       </c>
       <c r="H182" t="n">
         <v>35125</v>
@@ -5676,7 +5676,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G183" t="n">
-        <v>7.91749143600464</v>
+        <v>7.9174919128418</v>
       </c>
       <c r="H183" t="n">
         <v>3370</v>
@@ -5734,7 +5734,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G185" t="n">
-        <v>7.82093715667725</v>
+        <v>7.8209376335144</v>
       </c>
       <c r="H185" t="n">
         <v>4523</v>
@@ -5763,7 +5763,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H186" t="n">
         <v>3135</v>
@@ -5792,7 +5792,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G187" t="n">
-        <v>7.87886953353882</v>
+        <v>7.87887001037598</v>
       </c>
       <c r="H187" t="n">
         <v>2250</v>
@@ -5821,7 +5821,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>7.82093715667725</v>
+        <v>7.8209376335144</v>
       </c>
       <c r="H188" t="n">
         <v>271</v>
@@ -5850,7 +5850,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G189" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H189" t="n">
         <v>5300</v>
@@ -5879,7 +5879,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G190" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H190" t="n">
         <v>3983</v>
@@ -5908,7 +5908,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G191" t="n">
-        <v>7.82093715667725</v>
+        <v>7.8209376335144</v>
       </c>
       <c r="H191" t="n">
         <v>8096</v>
@@ -5937,7 +5937,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G192" t="n">
-        <v>7.82093715667725</v>
+        <v>7.8209376335144</v>
       </c>
       <c r="H192" t="n">
         <v>9675</v>
@@ -5995,7 +5995,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G194" t="n">
-        <v>7.82093715667725</v>
+        <v>7.8209376335144</v>
       </c>
       <c r="H194" t="n">
         <v>25407</v>
@@ -6053,7 +6053,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>7.82093715667725</v>
+        <v>7.8209376335144</v>
       </c>
       <c r="H196" t="n">
         <v>9084</v>
@@ -6082,7 +6082,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G197" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H197" t="n">
         <v>21391</v>
@@ -6111,7 +6111,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G198" t="n">
-        <v>7.91749143600464</v>
+        <v>7.9174919128418</v>
       </c>
       <c r="H198" t="n">
         <v>6073</v>
@@ -6140,7 +6140,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G199" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H199" t="n">
         <v>20734</v>
@@ -6227,7 +6227,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G202" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H202" t="n">
         <v>3347</v>
@@ -6256,7 +6256,7 @@
         <v>8</v>
       </c>
       <c r="G203" t="n">
-        <v>7.72438192367554</v>
+        <v>7.7243824005127</v>
       </c>
       <c r="H203" t="n">
         <v>14236</v>
@@ -6401,7 +6401,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G208" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H208" t="n">
         <v>1089</v>
@@ -6459,7 +6459,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G210" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H210" t="n">
         <v>1549</v>
@@ -6517,7 +6517,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G212" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H212" t="n">
         <v>12241</v>
@@ -6546,7 +6546,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H213" t="n">
         <v>55092</v>
@@ -6575,7 +6575,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G214" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H214" t="n">
         <v>8492</v>
@@ -6604,7 +6604,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G215" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H215" t="n">
         <v>4566</v>
@@ -6633,7 +6633,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G216" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H216" t="n">
         <v>16342</v>
@@ -6691,7 +6691,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G218" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853523254395</v>
       </c>
       <c r="H218" t="n">
         <v>1736</v>
@@ -6749,7 +6749,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G220" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H220" t="n">
         <v>8198</v>
@@ -6778,7 +6778,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853523254395</v>
       </c>
       <c r="H221" t="n">
         <v>7392</v>
@@ -6807,7 +6807,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G222" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H222" t="n">
         <v>5722</v>
@@ -6836,7 +6836,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G223" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H223" t="n">
         <v>5300</v>
@@ -6894,7 +6894,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853523254395</v>
       </c>
       <c r="H225" t="n">
         <v>1316</v>
@@ -7010,7 +7010,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G229" t="n">
-        <v>8.12991142272949</v>
+        <v>8.12991237640381</v>
       </c>
       <c r="H229" t="n">
         <v>20282</v>
@@ -7039,7 +7039,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G230" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H230" t="n">
         <v>2393</v>
@@ -7068,7 +7068,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G231" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H231" t="n">
         <v>7440</v>
@@ -7097,7 +7097,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H232" t="n">
         <v>11067</v>
@@ -7126,7 +7126,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>8.16853427886963</v>
+        <v>8.16853523254395</v>
       </c>
       <c r="H233" t="n">
         <v>6312</v>
@@ -7155,7 +7155,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G234" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H234" t="n">
         <v>826</v>
@@ -7184,7 +7184,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H235" t="n">
         <v>752</v>
@@ -7213,7 +7213,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G236" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H236" t="n">
         <v>8366</v>
@@ -7271,7 +7271,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G238" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611429214478</v>
       </c>
       <c r="H238" t="n">
         <v>3477</v>
@@ -7300,7 +7300,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G239" t="n">
-        <v>7.89818096160889</v>
+        <v>7.89818143844604</v>
       </c>
       <c r="H239" t="n">
         <v>6101</v>
@@ -7416,7 +7416,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G243" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H243" t="n">
         <v>3669</v>
@@ -7503,7 +7503,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G246" t="n">
-        <v>8.09129047393799</v>
+        <v>8.0912914276123</v>
       </c>
       <c r="H246" t="n">
         <v>31120</v>
@@ -7590,7 +7590,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G249" t="n">
-        <v>7.87886953353882</v>
+        <v>7.87887001037598</v>
       </c>
       <c r="H249" t="n">
         <v>1405</v>
@@ -7619,7 +7619,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G250" t="n">
-        <v>7.87886953353882</v>
+        <v>7.87887001037598</v>
       </c>
       <c r="H250" t="n">
         <v>4624</v>
@@ -7648,7 +7648,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G251" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H251" t="n">
         <v>17702</v>
@@ -7677,7 +7677,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G252" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H252" t="n">
         <v>4458</v>
@@ -7735,7 +7735,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>7.91749143600464</v>
+        <v>7.9174919128418</v>
       </c>
       <c r="H254" t="n">
         <v>10600</v>
@@ -7764,7 +7764,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G255" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H255" t="n">
         <v>18125</v>
@@ -7880,7 +7880,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H259" t="n">
         <v>13726</v>
@@ -7909,7 +7909,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G260" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H260" t="n">
         <v>14869</v>
@@ -7938,7 +7938,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G261" t="n">
-        <v>7.99473571777344</v>
+        <v>7.99473476409912</v>
       </c>
       <c r="H261" t="n">
         <v>2653</v>
@@ -7996,7 +7996,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H263" t="n">
         <v>15803</v>
@@ -8025,7 +8025,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G264" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H264" t="n">
         <v>7199</v>
@@ -8054,7 +8054,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G265" t="n">
-        <v>7.87886953353882</v>
+        <v>7.87887001037598</v>
       </c>
       <c r="H265" t="n">
         <v>18960</v>
@@ -8228,7 +8228,7 @@
         <v>8</v>
       </c>
       <c r="G271" t="n">
-        <v>7.72438192367554</v>
+        <v>7.7243824005127</v>
       </c>
       <c r="H271" t="n">
         <v>11242</v>
@@ -8286,7 +8286,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G273" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H273" t="n">
         <v>7426</v>
@@ -8489,7 +8489,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G280" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H280" t="n">
         <v>7266</v>
@@ -8547,7 +8547,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G282" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H282" t="n">
         <v>2416</v>
@@ -8576,7 +8576,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G283" t="n">
-        <v>7.91749143600464</v>
+        <v>7.9174919128418</v>
       </c>
       <c r="H283" t="n">
         <v>1082</v>
@@ -8605,7 +8605,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G284" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H284" t="n">
         <v>12131</v>
@@ -8634,7 +8634,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G285" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H285" t="n">
         <v>2580</v>
@@ -8663,7 +8663,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G286" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H286" t="n">
         <v>2356</v>
@@ -8692,7 +8692,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G287" t="n">
-        <v>7.85955953598022</v>
+        <v>7.85955905914307</v>
       </c>
       <c r="H287" t="n">
         <v>14875</v>
@@ -8721,7 +8721,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G288" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H288" t="n">
         <v>4850</v>
@@ -8750,7 +8750,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G289" t="n">
-        <v>7.95611333847046</v>
+        <v>7.95611429214478</v>
       </c>
       <c r="H289" t="n">
         <v>6789</v>
@@ -8779,7 +8779,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>8.05266952514648</v>
+        <v>8.05266857147217</v>
       </c>
       <c r="H290" t="n">
         <v>1377</v>
@@ -8808,7 +8808,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G291" t="n">
-        <v>7.87886953353882</v>
+        <v>7.87887001037598</v>
       </c>
       <c r="H291" t="n">
         <v>6109</v>
@@ -8837,7 +8837,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G292" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H292" t="n">
         <v>2670</v>
@@ -8866,7 +8866,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G293" t="n">
-        <v>8.01404666900635</v>
+        <v>8.01404571533203</v>
       </c>
       <c r="H293" t="n">
         <v>11644</v>
@@ -8953,7 +8953,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G296" t="n">
-        <v>8.30371189117432</v>
+        <v>8.3037109375</v>
       </c>
       <c r="H296" t="n">
         <v>4509</v>
@@ -9040,7 +9040,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G299" t="n">
-        <v>8.43888759613037</v>
+        <v>8.43888664245605</v>
       </c>
       <c r="H299" t="n">
         <v>5531</v>
@@ -9069,7 +9069,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G300" t="n">
-        <v>8.61268615722656</v>
+        <v>8.61268711090088</v>
       </c>
       <c r="H300" t="n">
         <v>26734</v>
@@ -9156,7 +9156,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G303" t="n">
-        <v>8.63199615478516</v>
+        <v>8.63199710845947</v>
       </c>
       <c r="H303" t="n">
         <v>22705</v>
@@ -9214,7 +9214,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>8.65130805969238</v>
+        <v>8.65130710601807</v>
       </c>
       <c r="H305" t="n">
         <v>3325</v>
@@ -9243,7 +9243,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G306" t="n">
-        <v>8.38095474243164</v>
+        <v>8.38095569610596</v>
       </c>
       <c r="H306" t="n">
         <v>5373</v>
@@ -9272,7 +9272,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G307" t="n">
-        <v>8.65130805969238</v>
+        <v>8.65130710601807</v>
       </c>
       <c r="H307" t="n">
         <v>19782</v>
@@ -9475,7 +9475,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>8.61268615722656</v>
+        <v>8.61268711090088</v>
       </c>
       <c r="H314" t="n">
         <v>3755</v>
@@ -9533,7 +9533,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G316" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H316" t="n">
         <v>20275</v>
@@ -9562,7 +9562,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H317" t="n">
         <v>6105</v>
@@ -9591,7 +9591,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G318" t="n">
-        <v>8.47751045227051</v>
+        <v>8.47750949859619</v>
       </c>
       <c r="H318" t="n">
         <v>3095</v>
@@ -9620,7 +9620,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G319" t="n">
-        <v>8.41957759857178</v>
+        <v>8.41957664489746</v>
       </c>
       <c r="H319" t="n">
         <v>1746</v>
@@ -9736,7 +9736,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G323" t="n">
-        <v>8.38095474243164</v>
+        <v>8.38095569610596</v>
       </c>
       <c r="H323" t="n">
         <v>27377</v>
@@ -9881,7 +9881,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G328" t="n">
-        <v>8.43888759613037</v>
+        <v>8.43888664245605</v>
       </c>
       <c r="H328" t="n">
         <v>4105</v>
@@ -10055,7 +10055,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>8.72855281829834</v>
+        <v>8.72855186462402</v>
       </c>
       <c r="H334" t="n">
         <v>10228</v>
@@ -10113,7 +10113,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G336" t="n">
-        <v>8.47751045227051</v>
+        <v>8.47750949859619</v>
       </c>
       <c r="H336" t="n">
         <v>12212</v>
@@ -10171,7 +10171,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>8.65130805969238</v>
+        <v>8.65130710601807</v>
       </c>
       <c r="H338" t="n">
         <v>20928</v>
@@ -10432,7 +10432,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G347" t="n">
-        <v>8.65130805969238</v>
+        <v>8.65130710601807</v>
       </c>
       <c r="H347" t="n">
         <v>3955</v>
@@ -10635,7 +10635,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G354" t="n">
-        <v>8.63199615478516</v>
+        <v>8.63199710845947</v>
       </c>
       <c r="H354" t="n">
         <v>746</v>
@@ -10664,7 +10664,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G355" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H355" t="n">
         <v>649</v>
@@ -10693,7 +10693,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G356" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H356" t="n">
         <v>1221</v>
@@ -10722,7 +10722,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>8.65130805969238</v>
+        <v>8.65130710601807</v>
       </c>
       <c r="H357" t="n">
         <v>2883</v>
@@ -10751,7 +10751,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G358" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H358" t="n">
         <v>55213</v>
@@ -10780,7 +10780,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H359" t="n">
         <v>1434</v>
@@ -10809,7 +10809,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G360" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H360" t="n">
         <v>1072</v>
@@ -10838,7 +10838,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H361" t="n">
         <v>299</v>
@@ -10896,7 +10896,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G363" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H363" t="n">
         <v>1804</v>
@@ -10954,7 +10954,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G365" t="n">
-        <v>8.59337425231934</v>
+        <v>8.59337520599365</v>
       </c>
       <c r="H365" t="n">
         <v>6093</v>
@@ -11070,7 +11070,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G369" t="n">
-        <v>8.47751045227051</v>
+        <v>8.47750949859619</v>
       </c>
       <c r="H369" t="n">
         <v>1997</v>
@@ -11099,7 +11099,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G370" t="n">
-        <v>8.47751045227051</v>
+        <v>8.47750949859619</v>
       </c>
       <c r="H370" t="n">
         <v>3224</v>
@@ -11128,7 +11128,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G371" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H371" t="n">
         <v>5429</v>
@@ -11331,7 +11331,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G378" t="n">
-        <v>8.65484237670898</v>
+        <v>8.6548433303833</v>
       </c>
       <c r="H378" t="n">
         <v>4178</v>
@@ -11360,7 +11360,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G379" t="n">
-        <v>8.67433452606201</v>
+        <v>8.67433547973633</v>
       </c>
       <c r="H379" t="n">
         <v>8702</v>
@@ -11389,7 +11389,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G380" t="n">
-        <v>8.5573787689209</v>
+        <v>8.55737781524658</v>
       </c>
       <c r="H380" t="n">
         <v>3988</v>
@@ -11418,7 +11418,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>8.57687091827393</v>
+        <v>8.57687187194824</v>
       </c>
       <c r="H381" t="n">
         <v>581</v>
@@ -11447,7 +11447,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G382" t="n">
-        <v>8.79129314422607</v>
+        <v>8.79129409790039</v>
       </c>
       <c r="H382" t="n">
         <v>10780</v>
@@ -11505,7 +11505,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G384" t="n">
-        <v>8.67433452606201</v>
+        <v>8.67433547973633</v>
       </c>
       <c r="H384" t="n">
         <v>2635</v>
@@ -11592,7 +11592,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G387" t="n">
-        <v>8.7133207321167</v>
+        <v>8.71332168579102</v>
       </c>
       <c r="H387" t="n">
         <v>13870</v>
@@ -11650,7 +11650,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G389" t="n">
-        <v>8.73281383514404</v>
+        <v>8.73281478881836</v>
       </c>
       <c r="H389" t="n">
         <v>7250</v>
@@ -11679,7 +11679,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>8.73281383514404</v>
+        <v>8.73281478881836</v>
       </c>
       <c r="H390" t="n">
         <v>8078</v>
@@ -11708,7 +11708,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G391" t="n">
-        <v>8.73281383514404</v>
+        <v>8.73281478881836</v>
       </c>
       <c r="H391" t="n">
         <v>16733</v>
@@ -11737,7 +11737,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>8.73281383514404</v>
+        <v>8.73281478881836</v>
       </c>
       <c r="H392" t="n">
         <v>4956</v>
@@ -11766,7 +11766,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>8.73281383514404</v>
+        <v>8.73281478881836</v>
       </c>
       <c r="H393" t="n">
         <v>6859</v>
@@ -11795,7 +11795,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G394" t="n">
-        <v>8.73281383514404</v>
+        <v>8.73281478881836</v>
       </c>
       <c r="H394" t="n">
         <v>8968</v>
@@ -11853,7 +11853,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G396" t="n">
-        <v>8.67433452606201</v>
+        <v>8.67433547973633</v>
       </c>
       <c r="H396" t="n">
         <v>11489</v>
@@ -11882,7 +11882,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G397" t="n">
-        <v>8.73281383514404</v>
+        <v>8.73281478881836</v>
       </c>
       <c r="H397" t="n">
         <v>15733</v>
@@ -12520,7 +12520,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G419" t="n">
-        <v>8.79129314422607</v>
+        <v>8.79129409790039</v>
       </c>
       <c r="H419" t="n">
         <v>8156</v>
@@ -12549,7 +12549,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G420" t="n">
-        <v>8.79129314422607</v>
+        <v>8.79129409790039</v>
       </c>
       <c r="H420" t="n">
         <v>1912</v>
@@ -12810,7 +12810,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G429" t="n">
-        <v>8.94723606109619</v>
+        <v>8.94723701477051</v>
       </c>
       <c r="H429" t="n">
         <v>9874</v>
@@ -12897,7 +12897,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>8.67433452606201</v>
+        <v>8.67433547973633</v>
       </c>
       <c r="H432" t="n">
         <v>20846</v>
@@ -13013,7 +13013,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G436" t="n">
-        <v>8.94723606109619</v>
+        <v>8.94723701477051</v>
       </c>
       <c r="H436" t="n">
         <v>14343</v>
@@ -13071,7 +13071,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G438" t="n">
-        <v>8.98622131347656</v>
+        <v>8.98622226715088</v>
       </c>
       <c r="H438" t="n">
         <v>5816</v>
@@ -13100,7 +13100,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G439" t="n">
-        <v>8.96672821044922</v>
+        <v>8.96672916412354</v>
       </c>
       <c r="H439" t="n">
         <v>2547</v>
@@ -13129,7 +13129,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>8.96672821044922</v>
+        <v>8.96672916412354</v>
       </c>
       <c r="H440" t="n">
         <v>1343</v>
@@ -13158,7 +13158,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>8.96672821044922</v>
+        <v>8.96672916412354</v>
       </c>
       <c r="H441" t="n">
         <v>3058</v>
@@ -13274,7 +13274,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G445" t="n">
-        <v>9.12267208099365</v>
+        <v>9.12267112731934</v>
       </c>
       <c r="H445" t="n">
         <v>3603</v>
@@ -13332,7 +13332,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G447" t="n">
-        <v>9.20064353942871</v>
+        <v>9.20064258575439</v>
       </c>
       <c r="H447" t="n">
         <v>17365</v>
@@ -13448,7 +13448,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G451" t="n">
-        <v>9.51253032684326</v>
+        <v>9.51252937316895</v>
       </c>
       <c r="H451" t="n">
         <v>22601</v>
@@ -13477,7 +13477,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G452" t="n">
-        <v>9.51253032684326</v>
+        <v>9.51252937316895</v>
       </c>
       <c r="H452" t="n">
         <v>18345</v>
@@ -13680,7 +13680,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G459" t="n">
-        <v>9.37607955932617</v>
+        <v>9.37607860565186</v>
       </c>
       <c r="H459" t="n">
         <v>12381</v>
@@ -13767,7 +13767,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G462" t="n">
-        <v>9.37607955932617</v>
+        <v>9.37607860565186</v>
       </c>
       <c r="H462" t="n">
         <v>47114</v>
@@ -13796,7 +13796,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G463" t="n">
-        <v>9.37607955932617</v>
+        <v>9.37607860565186</v>
       </c>
       <c r="H463" t="n">
         <v>28654</v>
@@ -13825,7 +13825,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>9.37607955932617</v>
+        <v>9.37607860565186</v>
       </c>
       <c r="H464" t="n">
         <v>44888</v>
@@ -13883,7 +13883,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G466" t="n">
-        <v>9.29810810089111</v>
+        <v>9.2981071472168</v>
       </c>
       <c r="H466" t="n">
         <v>34817</v>
@@ -13941,7 +13941,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G468" t="n">
-        <v>9.62948799133301</v>
+        <v>9.62948703765869</v>
       </c>
       <c r="H468" t="n">
         <v>49815</v>
@@ -14028,7 +14028,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G471" t="n">
-        <v>9.29810810089111</v>
+        <v>9.2981071472168</v>
       </c>
       <c r="H471" t="n">
         <v>103158</v>
@@ -14057,7 +14057,7 @@
         <v>9.5</v>
       </c>
       <c r="G472" t="n">
-        <v>9.25912284851074</v>
+        <v>9.25912189483643</v>
       </c>
       <c r="H472" t="n">
         <v>75426</v>
@@ -14202,7 +14202,7 @@
         <v>9.5</v>
       </c>
       <c r="G477" t="n">
-        <v>9.25912284851074</v>
+        <v>9.25912189483643</v>
       </c>
       <c r="H477" t="n">
         <v>24059</v>
@@ -14231,7 +14231,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>9.29810810089111</v>
+        <v>9.2981071472168</v>
       </c>
       <c r="H478" t="n">
         <v>8181</v>
@@ -14318,7 +14318,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G481" t="n">
-        <v>9.59050178527832</v>
+        <v>9.590500831604</v>
       </c>
       <c r="H481" t="n">
         <v>27152</v>
@@ -14376,7 +14376,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G483" t="n">
-        <v>10.0875701904297</v>
+        <v>10.087571144104</v>
       </c>
       <c r="H483" t="n">
         <v>99460</v>
@@ -14405,7 +14405,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G484" t="n">
-        <v>10.1850337982178</v>
+        <v>10.1850347518921</v>
       </c>
       <c r="H484" t="n">
         <v>42643</v>
@@ -14463,7 +14463,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G486" t="n">
-        <v>10.3312320709229</v>
+        <v>10.3312311172485</v>
       </c>
       <c r="H486" t="n">
         <v>14224</v>
@@ -14492,7 +14492,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G487" t="n">
-        <v>10.3312320709229</v>
+        <v>10.3312311172485</v>
       </c>
       <c r="H487" t="n">
         <v>40436</v>
@@ -14521,7 +14521,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>10.1850337982178</v>
+        <v>10.1850347518921</v>
       </c>
       <c r="H488" t="n">
         <v>58963</v>
@@ -14550,7 +14550,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G489" t="n">
-        <v>10.0388383865356</v>
+        <v>10.0388374328613</v>
       </c>
       <c r="H489" t="n">
         <v>31431</v>
@@ -14608,7 +14608,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>10.3312320709229</v>
+        <v>10.3312311172485</v>
       </c>
       <c r="H491" t="n">
         <v>7253</v>
@@ -14666,7 +14666,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G493" t="n">
-        <v>10.3312320709229</v>
+        <v>10.3312311172485</v>
       </c>
       <c r="H493" t="n">
         <v>9014</v>
@@ -14753,7 +14753,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>10.1363010406494</v>
+        <v>10.1363019943237</v>
       </c>
       <c r="H496" t="n">
         <v>7452</v>
@@ -14782,7 +14782,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>10.1363010406494</v>
+        <v>10.1363019943237</v>
       </c>
       <c r="H497" t="n">
         <v>21636</v>
@@ -14811,7 +14811,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G498" t="n">
-        <v>10.1363010406494</v>
+        <v>10.1363019943237</v>
       </c>
       <c r="H498" t="n">
         <v>34176</v>
@@ -14840,7 +14840,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G499" t="n">
-        <v>10.1850337982178</v>
+        <v>10.1850347518921</v>
       </c>
       <c r="H499" t="n">
         <v>73943</v>
@@ -14869,7 +14869,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>10.0388383865356</v>
+        <v>10.0388374328613</v>
       </c>
       <c r="H500" t="n">
         <v>53170</v>
@@ -14927,7 +14927,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G502" t="n">
-        <v>10.6723566055298</v>
+        <v>10.6723556518555</v>
       </c>
       <c r="H502" t="n">
         <v>93835</v>
@@ -14985,7 +14985,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G504" t="n">
-        <v>10.6723566055298</v>
+        <v>10.6723556518555</v>
       </c>
       <c r="H504" t="n">
         <v>42791</v>
@@ -15217,7 +15217,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G512" t="n">
-        <v>11.013482093811</v>
+        <v>11.0134830474854</v>
       </c>
       <c r="H512" t="n">
         <v>81844</v>
@@ -15246,7 +15246,7 @@
         <v>11.25</v>
       </c>
       <c r="G513" t="n">
-        <v>10.964750289917</v>
+        <v>10.9647493362427</v>
       </c>
       <c r="H513" t="n">
         <v>65236</v>
@@ -15507,7 +15507,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G522" t="n">
-        <v>11.3058757781982</v>
+        <v>11.3058767318726</v>
       </c>
       <c r="H522" t="n">
         <v>74151</v>
@@ -15594,7 +15594,7 @@
         <v>12</v>
       </c>
       <c r="G525" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H525" t="n">
         <v>165830</v>
@@ -15681,7 +15681,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>12.0368585586548</v>
+        <v>12.0368595123291</v>
       </c>
       <c r="H528" t="n">
         <v>204255</v>
@@ -15913,7 +15913,7 @@
         <v>12</v>
       </c>
       <c r="G536" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H536" t="n">
         <v>25535</v>
@@ -16000,7 +16000,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G539" t="n">
-        <v>11.4033393859863</v>
+        <v>11.4033403396606</v>
       </c>
       <c r="H539" t="n">
         <v>20898</v>
@@ -16087,7 +16087,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G542" t="n">
-        <v>11.4033393859863</v>
+        <v>11.4033403396606</v>
       </c>
       <c r="H542" t="n">
         <v>25345</v>
@@ -16203,7 +16203,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G546" t="n">
-        <v>11.4033393859863</v>
+        <v>11.4033403396606</v>
       </c>
       <c r="H546" t="n">
         <v>47534</v>
@@ -16261,7 +16261,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G548" t="n">
-        <v>11.7931985855103</v>
+        <v>11.7931976318359</v>
       </c>
       <c r="H548" t="n">
         <v>47029</v>
@@ -16348,7 +16348,7 @@
         <v>12</v>
       </c>
       <c r="G551" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H551" t="n">
         <v>30358</v>
@@ -16435,7 +16435,7 @@
         <v>12</v>
       </c>
       <c r="G554" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H554" t="n">
         <v>8761</v>
@@ -16464,7 +16464,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G555" t="n">
-        <v>11.7931985855103</v>
+        <v>11.7931976318359</v>
       </c>
       <c r="H555" t="n">
         <v>13533</v>
@@ -16493,7 +16493,7 @@
         <v>12</v>
       </c>
       <c r="G556" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H556" t="n">
         <v>5809</v>
@@ -16522,7 +16522,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G557" t="n">
-        <v>11.8906621932983</v>
+        <v>11.890661239624</v>
       </c>
       <c r="H557" t="n">
         <v>10698</v>
@@ -16609,7 +16609,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>11.7931985855103</v>
+        <v>11.7931976318359</v>
       </c>
       <c r="H560" t="n">
         <v>93481</v>
@@ -16638,7 +16638,7 @@
         <v>12</v>
       </c>
       <c r="G561" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H561" t="n">
         <v>34950</v>
@@ -16667,7 +16667,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G562" t="n">
-        <v>11.6470003128052</v>
+        <v>11.6470012664795</v>
       </c>
       <c r="H562" t="n">
         <v>15367</v>
@@ -16696,7 +16696,7 @@
         <v>12</v>
       </c>
       <c r="G563" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H563" t="n">
         <v>39064</v>
@@ -16725,7 +16725,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>11.7931985855103</v>
+        <v>11.7931976318359</v>
       </c>
       <c r="H564" t="n">
         <v>22959</v>
@@ -16754,7 +16754,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G565" t="n">
-        <v>11.6470003128052</v>
+        <v>11.6470012664795</v>
       </c>
       <c r="H565" t="n">
         <v>14206</v>
@@ -16812,7 +16812,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G567" t="n">
-        <v>11.7931985855103</v>
+        <v>11.7931976318359</v>
       </c>
       <c r="H567" t="n">
         <v>56931</v>
@@ -16841,7 +16841,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>11.7931985855103</v>
+        <v>11.7931976318359</v>
       </c>
       <c r="H568" t="n">
         <v>12168</v>
@@ -16957,7 +16957,7 @@
         <v>12</v>
       </c>
       <c r="G572" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H572" t="n">
         <v>50297</v>
@@ -17102,7 +17102,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G577" t="n">
-        <v>11.8906621932983</v>
+        <v>11.890661239624</v>
       </c>
       <c r="H577" t="n">
         <v>8377</v>
@@ -17827,7 +17827,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G602" t="n">
-        <v>12.7093639373779</v>
+        <v>12.7093629837036</v>
       </c>
       <c r="H602" t="n">
         <v>70858</v>
@@ -17885,7 +17885,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G604" t="n">
-        <v>12.6898717880249</v>
+        <v>12.6898708343506</v>
       </c>
       <c r="H604" t="n">
         <v>57453</v>
@@ -17943,7 +17943,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G606" t="n">
-        <v>12.8653059005737</v>
+        <v>12.865306854248</v>
       </c>
       <c r="H606" t="n">
         <v>71717</v>
@@ -18088,7 +18088,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G611" t="n">
-        <v>13.3136425018311</v>
+        <v>13.3136434555054</v>
       </c>
       <c r="H611" t="n">
         <v>69440</v>
@@ -18233,7 +18233,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G616" t="n">
-        <v>13.4500942230225</v>
+        <v>13.4500932693481</v>
       </c>
       <c r="H616" t="n">
         <v>45178</v>
@@ -18320,7 +18320,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G619" t="n">
-        <v>13.3136425018311</v>
+        <v>13.3136434555054</v>
       </c>
       <c r="H619" t="n">
         <v>22500</v>
@@ -18349,7 +18349,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G620" t="n">
-        <v>13.3136425018311</v>
+        <v>13.3136434555054</v>
       </c>
       <c r="H620" t="n">
         <v>23712</v>
@@ -18407,7 +18407,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G622" t="n">
-        <v>13.6255283355713</v>
+        <v>13.6255292892456</v>
       </c>
       <c r="H622" t="n">
         <v>54015</v>
@@ -18523,7 +18523,7 @@
         <v>14.5</v>
       </c>
       <c r="G626" t="n">
-        <v>14.1323442459106</v>
+        <v>14.132345199585</v>
       </c>
       <c r="H626" t="n">
         <v>143325</v>
@@ -29230,6 +29230,35 @@
         <v>6273</v>
       </c>
       <c r="I995" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="s">
+        <v>9</v>
+      </c>
+      <c r="B996" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C996" t="n">
+        <v>22.1000003814697</v>
+      </c>
+      <c r="D996" t="n">
+        <v>22.8500003814697</v>
+      </c>
+      <c r="E996" t="n">
+        <v>22</v>
+      </c>
+      <c r="F996" t="n">
+        <v>22.6499996185303</v>
+      </c>
+      <c r="G996" t="n">
+        <v>22.6499996185303</v>
+      </c>
+      <c r="H996" t="n">
+        <v>17887</v>
+      </c>
+      <c r="I996" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H2" t="n">
         <v>4793</v>
@@ -514,7 +514,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G5" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H5" t="n">
         <v>15746</v>
@@ -543,7 +543,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G6" t="n">
-        <v>8.18784427642822</v>
+        <v>8.18784523010254</v>
       </c>
       <c r="H6" t="n">
         <v>2771</v>
@@ -572,7 +572,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G7" t="n">
-        <v>8.08163452148438</v>
+        <v>8.08163547515869</v>
       </c>
       <c r="H7" t="n">
         <v>2650</v>
@@ -601,7 +601,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G8" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H8" t="n">
         <v>3358</v>
@@ -630,7 +630,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G9" t="n">
-        <v>8.1009464263916</v>
+        <v>8.10094547271729</v>
       </c>
       <c r="H9" t="n">
         <v>1320</v>
@@ -659,7 +659,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G10" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H10" t="n">
         <v>6204</v>
@@ -688,7 +688,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G11" t="n">
-        <v>8.04301261901855</v>
+        <v>8.04301357269287</v>
       </c>
       <c r="H11" t="n">
         <v>66</v>
@@ -717,7 +717,7 @@
         <v>8.25</v>
       </c>
       <c r="G12" t="n">
-        <v>7.96576881408691</v>
+        <v>7.96576976776123</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
@@ -746,7 +746,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G13" t="n">
-        <v>8.18784427642822</v>
+        <v>8.18784523010254</v>
       </c>
       <c r="H13" t="n">
         <v>4230</v>
@@ -804,7 +804,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G15" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H15" t="n">
         <v>32</v>
@@ -862,7 +862,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G17" t="n">
-        <v>7.94645881652832</v>
+        <v>7.94645738601685</v>
       </c>
       <c r="H17" t="n">
         <v>2333</v>
@@ -891,7 +891,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G18" t="n">
-        <v>8.17819023132324</v>
+        <v>8.17818927764893</v>
       </c>
       <c r="H18" t="n">
         <v>980</v>
@@ -978,7 +978,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G21" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473524093628</v>
       </c>
       <c r="H21" t="n">
         <v>2849</v>
@@ -1007,7 +1007,7 @@
         <v>8.25</v>
       </c>
       <c r="G22" t="n">
-        <v>7.96576881408691</v>
+        <v>7.96576976776123</v>
       </c>
       <c r="H22" t="n">
         <v>1800</v>
@@ -1036,7 +1036,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G23" t="n">
-        <v>7.95611429214478</v>
+        <v>7.95611381530762</v>
       </c>
       <c r="H23" t="n">
         <v>480</v>
@@ -1065,7 +1065,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G24" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H24" t="n">
         <v>8168</v>
@@ -1094,7 +1094,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G25" t="n">
-        <v>8.17819023132324</v>
+        <v>8.17818927764893</v>
       </c>
       <c r="H25" t="n">
         <v>384</v>
@@ -1239,7 +1239,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G30" t="n">
-        <v>8.1009464263916</v>
+        <v>8.10094547271729</v>
       </c>
       <c r="H30" t="n">
         <v>578</v>
@@ -1268,7 +1268,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G31" t="n">
-        <v>8.1009464263916</v>
+        <v>8.10094547271729</v>
       </c>
       <c r="H31" t="n">
         <v>332</v>
@@ -1297,7 +1297,7 @@
         <v>8.25</v>
       </c>
       <c r="G32" t="n">
-        <v>7.96576881408691</v>
+        <v>7.96576976776123</v>
       </c>
       <c r="H32" t="n">
         <v>10305</v>
@@ -1326,7 +1326,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H33" t="n">
         <v>3280</v>
@@ -1384,7 +1384,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H35" t="n">
         <v>8723</v>
@@ -1413,7 +1413,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G36" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H36" t="n">
         <v>411</v>
@@ -1471,7 +1471,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H38" t="n">
         <v>80</v>
@@ -1529,7 +1529,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G40" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H40" t="n">
         <v>3659</v>
@@ -1558,7 +1558,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G41" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H41" t="n">
         <v>3082</v>
@@ -1674,7 +1674,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G45" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H45" t="n">
         <v>8898</v>
@@ -1790,7 +1790,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G49" t="n">
-        <v>7.90783548355103</v>
+        <v>7.90783596038818</v>
       </c>
       <c r="H49" t="n">
         <v>9413</v>
@@ -1993,7 +1993,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G56" t="n">
-        <v>7.98508024215698</v>
+        <v>7.98508071899414</v>
       </c>
       <c r="H56" t="n">
         <v>8601</v>
@@ -2022,7 +2022,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H57" t="n">
         <v>1380</v>
@@ -2051,7 +2051,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H58" t="n">
         <v>12623</v>
@@ -2080,7 +2080,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G59" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473524093628</v>
       </c>
       <c r="H59" t="n">
         <v>3310</v>
@@ -2109,7 +2109,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G60" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473524093628</v>
       </c>
       <c r="H60" t="n">
         <v>12417</v>
@@ -2138,7 +2138,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G61" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H61" t="n">
         <v>13315</v>
@@ -2225,7 +2225,7 @@
         <v>8.5</v>
       </c>
       <c r="G64" t="n">
-        <v>8.20715522766113</v>
+        <v>8.20715618133545</v>
       </c>
       <c r="H64" t="n">
         <v>659</v>
@@ -2312,7 +2312,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G67" t="n">
-        <v>8.12025737762451</v>
+        <v>8.12025547027588</v>
       </c>
       <c r="H67" t="n">
         <v>969</v>
@@ -2341,7 +2341,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G68" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H68" t="n">
         <v>7666</v>
@@ -2370,7 +2370,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G69" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H69" t="n">
         <v>3050</v>
@@ -2399,7 +2399,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G70" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H70" t="n">
         <v>7975</v>
@@ -2457,7 +2457,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H72" t="n">
         <v>10401</v>
@@ -2486,7 +2486,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G73" t="n">
-        <v>7.95611429214478</v>
+        <v>7.95611381530762</v>
       </c>
       <c r="H73" t="n">
         <v>21359</v>
@@ -2515,7 +2515,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G74" t="n">
-        <v>7.95611429214478</v>
+        <v>7.95611381530762</v>
       </c>
       <c r="H74" t="n">
         <v>9297</v>
@@ -2544,7 +2544,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G75" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473524093628</v>
       </c>
       <c r="H75" t="n">
         <v>1884</v>
@@ -2602,7 +2602,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G77" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H77" t="n">
         <v>4665</v>
@@ -2631,7 +2631,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G78" t="n">
-        <v>8.12025737762451</v>
+        <v>8.12025547027588</v>
       </c>
       <c r="H78" t="n">
         <v>3676</v>
@@ -2660,7 +2660,7 @@
         <v>8.25</v>
       </c>
       <c r="G79" t="n">
-        <v>7.96576881408691</v>
+        <v>7.96576976776123</v>
       </c>
       <c r="H79" t="n">
         <v>3004</v>
@@ -2689,7 +2689,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G80" t="n">
-        <v>7.98508024215698</v>
+        <v>7.98508071899414</v>
       </c>
       <c r="H80" t="n">
         <v>2183</v>
@@ -2718,7 +2718,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H81" t="n">
         <v>2117</v>
@@ -2747,7 +2747,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G82" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H82" t="n">
         <v>1745</v>
@@ -2805,7 +2805,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G84" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H84" t="n">
         <v>6600</v>
@@ -2834,7 +2834,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G85" t="n">
-        <v>8.08163452148438</v>
+        <v>8.08163547515869</v>
       </c>
       <c r="H85" t="n">
         <v>3150</v>
@@ -2863,7 +2863,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>8.08163452148438</v>
+        <v>8.08163547515869</v>
       </c>
       <c r="H86" t="n">
         <v>500</v>
@@ -2892,7 +2892,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G87" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473524093628</v>
       </c>
       <c r="H87" t="n">
         <v>7121</v>
@@ -2950,7 +2950,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G89" t="n">
-        <v>7.98508024215698</v>
+        <v>7.98508071899414</v>
       </c>
       <c r="H89" t="n">
         <v>14762</v>
@@ -3008,7 +3008,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G91" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H91" t="n">
         <v>928</v>
@@ -3037,7 +3037,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G92" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H92" t="n">
         <v>4665</v>
@@ -3124,7 +3124,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G95" t="n">
-        <v>7.8209376335144</v>
+        <v>7.82093715667725</v>
       </c>
       <c r="H95" t="n">
         <v>33055</v>
@@ -3211,7 +3211,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G98" t="n">
-        <v>7.68576002120972</v>
+        <v>7.68576049804688</v>
       </c>
       <c r="H98" t="n">
         <v>27915</v>
@@ -3240,7 +3240,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>7.68576002120972</v>
+        <v>7.68576049804688</v>
       </c>
       <c r="H99" t="n">
         <v>6541</v>
@@ -3385,7 +3385,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>7.68576002120972</v>
+        <v>7.68576049804688</v>
       </c>
       <c r="H104" t="n">
         <v>4845</v>
@@ -3501,7 +3501,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>7.62782764434814</v>
+        <v>7.6278281211853</v>
       </c>
       <c r="H108" t="n">
         <v>3757</v>
@@ -3617,7 +3617,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G112" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H112" t="n">
         <v>364</v>
@@ -3646,7 +3646,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G113" t="n">
-        <v>8.18784427642822</v>
+        <v>8.18784523010254</v>
       </c>
       <c r="H113" t="n">
         <v>4328</v>
@@ -3675,7 +3675,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>8.16853523254395</v>
+        <v>8.16853332519531</v>
       </c>
       <c r="H114" t="n">
         <v>4325</v>
@@ -3704,7 +3704,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>8.16853523254395</v>
+        <v>8.16853332519531</v>
       </c>
       <c r="H115" t="n">
         <v>3981</v>
@@ -3733,7 +3733,7 @@
         <v>8.5</v>
       </c>
       <c r="G116" t="n">
-        <v>8.20715522766113</v>
+        <v>8.20715618133545</v>
       </c>
       <c r="H116" t="n">
         <v>3300</v>
@@ -3791,7 +3791,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G118" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H118" t="n">
         <v>4146</v>
@@ -3820,7 +3820,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G119" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H119" t="n">
         <v>2963</v>
@@ -3849,7 +3849,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G120" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H120" t="n">
         <v>40121</v>
@@ -3907,7 +3907,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G122" t="n">
-        <v>8.41957664489746</v>
+        <v>8.41957759857178</v>
       </c>
       <c r="H122" t="n">
         <v>12777</v>
@@ -3936,7 +3936,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G123" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H123" t="n">
         <v>8043</v>
@@ -4052,7 +4052,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>8.61268711090088</v>
+        <v>8.61268615722656</v>
       </c>
       <c r="H127" t="n">
         <v>14042</v>
@@ -4081,7 +4081,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G128" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H128" t="n">
         <v>4585</v>
@@ -4139,7 +4139,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G130" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H130" t="n">
         <v>19296</v>
@@ -4168,7 +4168,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G131" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H131" t="n">
         <v>40100</v>
@@ -4197,7 +4197,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G132" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H132" t="n">
         <v>3386</v>
@@ -4255,7 +4255,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>8.65130710601807</v>
+        <v>8.65130805969238</v>
       </c>
       <c r="H134" t="n">
         <v>4553</v>
@@ -4284,7 +4284,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G135" t="n">
-        <v>8.47750949859619</v>
+        <v>8.47751045227051</v>
       </c>
       <c r="H135" t="n">
         <v>2684</v>
@@ -4313,7 +4313,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G136" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H136" t="n">
         <v>1044</v>
@@ -4371,7 +4371,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H138" t="n">
         <v>475</v>
@@ -4429,7 +4429,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H140" t="n">
         <v>1058</v>
@@ -4545,7 +4545,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G144" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H144" t="n">
         <v>1986</v>
@@ -4603,7 +4603,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G146" t="n">
-        <v>8.34233379364014</v>
+        <v>8.34233283996582</v>
       </c>
       <c r="H146" t="n">
         <v>13733</v>
@@ -4719,7 +4719,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G150" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H150" t="n">
         <v>4230</v>
@@ -4748,7 +4748,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G151" t="n">
-        <v>8.34233379364014</v>
+        <v>8.34233283996582</v>
       </c>
       <c r="H151" t="n">
         <v>4010</v>
@@ -4806,7 +4806,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G153" t="n">
-        <v>8.34233379364014</v>
+        <v>8.34233283996582</v>
       </c>
       <c r="H153" t="n">
         <v>16815</v>
@@ -4893,7 +4893,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G156" t="n">
-        <v>8.41957664489746</v>
+        <v>8.41957759857178</v>
       </c>
       <c r="H156" t="n">
         <v>9168</v>
@@ -4922,7 +4922,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G157" t="n">
-        <v>8.41957664489746</v>
+        <v>8.41957759857178</v>
       </c>
       <c r="H157" t="n">
         <v>10594</v>
@@ -5125,7 +5125,7 @@
         <v>8.5</v>
       </c>
       <c r="G164" t="n">
-        <v>8.20715522766113</v>
+        <v>8.20715618133545</v>
       </c>
       <c r="H164" t="n">
         <v>18147</v>
@@ -5183,7 +5183,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G166" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H166" t="n">
         <v>9385</v>
@@ -5386,7 +5386,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G173" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473524093628</v>
       </c>
       <c r="H173" t="n">
         <v>7608</v>
@@ -5415,7 +5415,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G174" t="n">
-        <v>7.95611429214478</v>
+        <v>7.95611381530762</v>
       </c>
       <c r="H174" t="n">
         <v>9388</v>
@@ -5444,7 +5444,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G175" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H175" t="n">
         <v>4377</v>
@@ -5531,7 +5531,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G178" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H178" t="n">
         <v>10600</v>
@@ -5734,7 +5734,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G185" t="n">
-        <v>7.8209376335144</v>
+        <v>7.82093715667725</v>
       </c>
       <c r="H185" t="n">
         <v>4523</v>
@@ -5792,7 +5792,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G187" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H187" t="n">
         <v>2250</v>
@@ -5821,7 +5821,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>7.8209376335144</v>
+        <v>7.82093715667725</v>
       </c>
       <c r="H188" t="n">
         <v>271</v>
@@ -5908,7 +5908,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G191" t="n">
-        <v>7.8209376335144</v>
+        <v>7.82093715667725</v>
       </c>
       <c r="H191" t="n">
         <v>8096</v>
@@ -5937,7 +5937,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G192" t="n">
-        <v>7.8209376335144</v>
+        <v>7.82093715667725</v>
       </c>
       <c r="H192" t="n">
         <v>9675</v>
@@ -5995,7 +5995,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G194" t="n">
-        <v>7.8209376335144</v>
+        <v>7.82093715667725</v>
       </c>
       <c r="H194" t="n">
         <v>25407</v>
@@ -6053,7 +6053,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>7.8209376335144</v>
+        <v>7.82093715667725</v>
       </c>
       <c r="H196" t="n">
         <v>9084</v>
@@ -6546,7 +6546,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H213" t="n">
         <v>55092</v>
@@ -6575,7 +6575,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G214" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H214" t="n">
         <v>8492</v>
@@ -6604,7 +6604,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G215" t="n">
-        <v>8.07197856903076</v>
+        <v>8.07197952270508</v>
       </c>
       <c r="H215" t="n">
         <v>4566</v>
@@ -6633,7 +6633,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G216" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H216" t="n">
         <v>16342</v>
@@ -6662,7 +6662,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G217" t="n">
-        <v>8.18784427642822</v>
+        <v>8.18784523010254</v>
       </c>
       <c r="H217" t="n">
         <v>3476</v>
@@ -6691,7 +6691,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G218" t="n">
-        <v>8.16853523254395</v>
+        <v>8.16853332519531</v>
       </c>
       <c r="H218" t="n">
         <v>1736</v>
@@ -6778,7 +6778,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>8.16853523254395</v>
+        <v>8.16853332519531</v>
       </c>
       <c r="H221" t="n">
         <v>7392</v>
@@ -6836,7 +6836,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G223" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H223" t="n">
         <v>5300</v>
@@ -6894,7 +6894,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>8.16853523254395</v>
+        <v>8.16853332519531</v>
       </c>
       <c r="H225" t="n">
         <v>1316</v>
@@ -6923,7 +6923,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G226" t="n">
-        <v>8.18784427642822</v>
+        <v>8.18784523010254</v>
       </c>
       <c r="H226" t="n">
         <v>1388</v>
@@ -7097,7 +7097,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H232" t="n">
         <v>11067</v>
@@ -7126,7 +7126,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>8.16853523254395</v>
+        <v>8.16853332519531</v>
       </c>
       <c r="H233" t="n">
         <v>6312</v>
@@ -7155,7 +7155,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G234" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H234" t="n">
         <v>826</v>
@@ -7184,7 +7184,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H235" t="n">
         <v>752</v>
@@ -7271,7 +7271,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G238" t="n">
-        <v>7.95611429214478</v>
+        <v>7.95611381530762</v>
       </c>
       <c r="H238" t="n">
         <v>3477</v>
@@ -7590,7 +7590,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G249" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H249" t="n">
         <v>1405</v>
@@ -7619,7 +7619,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G250" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H250" t="n">
         <v>4624</v>
@@ -7648,7 +7648,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G251" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473524093628</v>
       </c>
       <c r="H251" t="n">
         <v>17702</v>
@@ -7677,7 +7677,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G252" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473524093628</v>
       </c>
       <c r="H252" t="n">
         <v>4458</v>
@@ -7764,7 +7764,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G255" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473524093628</v>
       </c>
       <c r="H255" t="n">
         <v>18125</v>
@@ -7880,7 +7880,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H259" t="n">
         <v>13726</v>
@@ -7909,7 +7909,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G260" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H260" t="n">
         <v>14869</v>
@@ -7938,7 +7938,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G261" t="n">
-        <v>7.99473476409912</v>
+        <v>7.99473524093628</v>
       </c>
       <c r="H261" t="n">
         <v>2653</v>
@@ -7996,7 +7996,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H263" t="n">
         <v>15803</v>
@@ -8025,7 +8025,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G264" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H264" t="n">
         <v>7199</v>
@@ -8054,7 +8054,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G265" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H265" t="n">
         <v>18960</v>
@@ -8170,7 +8170,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>7.68576002120972</v>
+        <v>7.68576049804688</v>
       </c>
       <c r="H269" t="n">
         <v>22886</v>
@@ -8257,7 +8257,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>7.68576002120972</v>
+        <v>7.68576049804688</v>
       </c>
       <c r="H272" t="n">
         <v>12707</v>
@@ -8373,7 +8373,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>7.68576002120972</v>
+        <v>7.68576049804688</v>
       </c>
       <c r="H276" t="n">
         <v>22466</v>
@@ -8431,7 +8431,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G278" t="n">
-        <v>7.68576002120972</v>
+        <v>7.68576049804688</v>
       </c>
       <c r="H278" t="n">
         <v>7771</v>
@@ -8489,7 +8489,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G280" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H280" t="n">
         <v>7266</v>
@@ -8547,7 +8547,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G282" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H282" t="n">
         <v>2416</v>
@@ -8605,7 +8605,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G284" t="n">
-        <v>8.1106014251709</v>
+        <v>8.11060047149658</v>
       </c>
       <c r="H284" t="n">
         <v>12131</v>
@@ -8721,7 +8721,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G288" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H288" t="n">
         <v>4850</v>
@@ -8750,7 +8750,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G289" t="n">
-        <v>7.95611429214478</v>
+        <v>7.95611381530762</v>
       </c>
       <c r="H289" t="n">
         <v>6789</v>
@@ -8808,7 +8808,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G291" t="n">
-        <v>7.87887001037598</v>
+        <v>7.87886953353882</v>
       </c>
       <c r="H291" t="n">
         <v>6109</v>
@@ -8837,7 +8837,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G292" t="n">
-        <v>7.97542476654053</v>
+        <v>7.97542524337769</v>
       </c>
       <c r="H292" t="n">
         <v>2670</v>
@@ -8866,7 +8866,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G293" t="n">
-        <v>8.01404571533203</v>
+        <v>8.01404762268066</v>
       </c>
       <c r="H293" t="n">
         <v>11644</v>
@@ -8895,7 +8895,7 @@
         <v>8.5</v>
       </c>
       <c r="G294" t="n">
-        <v>8.20715522766113</v>
+        <v>8.20715618133545</v>
       </c>
       <c r="H294" t="n">
         <v>6062</v>
@@ -8953,7 +8953,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G296" t="n">
-        <v>8.3037109375</v>
+        <v>8.30371189117432</v>
       </c>
       <c r="H296" t="n">
         <v>4509</v>
@@ -9040,7 +9040,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G299" t="n">
-        <v>8.43888664245605</v>
+        <v>8.43888759613037</v>
       </c>
       <c r="H299" t="n">
         <v>5531</v>
@@ -9069,7 +9069,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G300" t="n">
-        <v>8.61268711090088</v>
+        <v>8.61268615722656</v>
       </c>
       <c r="H300" t="n">
         <v>26734</v>
@@ -9156,7 +9156,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G303" t="n">
-        <v>8.63199710845947</v>
+        <v>8.63199615478516</v>
       </c>
       <c r="H303" t="n">
         <v>22705</v>
@@ -9185,7 +9185,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G304" t="n">
-        <v>8.74786376953125</v>
+        <v>8.74786281585693</v>
       </c>
       <c r="H304" t="n">
         <v>26905</v>
@@ -9214,7 +9214,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>8.65130710601807</v>
+        <v>8.65130805969238</v>
       </c>
       <c r="H305" t="n">
         <v>3325</v>
@@ -9272,7 +9272,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G307" t="n">
-        <v>8.65130710601807</v>
+        <v>8.65130805969238</v>
       </c>
       <c r="H307" t="n">
         <v>19782</v>
@@ -9301,7 +9301,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G308" t="n">
-        <v>8.70924091339111</v>
+        <v>8.70924186706543</v>
       </c>
       <c r="H308" t="n">
         <v>19262</v>
@@ -9359,7 +9359,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G310" t="n">
-        <v>8.92166137695312</v>
+        <v>8.92166042327881</v>
       </c>
       <c r="H310" t="n">
         <v>29147</v>
@@ -9446,7 +9446,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G313" t="n">
-        <v>8.70924091339111</v>
+        <v>8.70924186706543</v>
       </c>
       <c r="H313" t="n">
         <v>7173</v>
@@ -9475,7 +9475,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>8.61268711090088</v>
+        <v>8.61268615722656</v>
       </c>
       <c r="H314" t="n">
         <v>3755</v>
@@ -9562,7 +9562,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H317" t="n">
         <v>6105</v>
@@ -9591,7 +9591,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G318" t="n">
-        <v>8.47750949859619</v>
+        <v>8.47751045227051</v>
       </c>
       <c r="H318" t="n">
         <v>3095</v>
@@ -9620,7 +9620,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G319" t="n">
-        <v>8.41957664489746</v>
+        <v>8.41957759857178</v>
       </c>
       <c r="H319" t="n">
         <v>1746</v>
@@ -9881,7 +9881,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G328" t="n">
-        <v>8.43888664245605</v>
+        <v>8.43888759613037</v>
       </c>
       <c r="H328" t="n">
         <v>4105</v>
@@ -10113,7 +10113,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G336" t="n">
-        <v>8.47750949859619</v>
+        <v>8.47751045227051</v>
       </c>
       <c r="H336" t="n">
         <v>12212</v>
@@ -10142,7 +10142,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G337" t="n">
-        <v>8.74786376953125</v>
+        <v>8.74786281585693</v>
       </c>
       <c r="H337" t="n">
         <v>26896</v>
@@ -10171,7 +10171,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>8.65130710601807</v>
+        <v>8.65130805969238</v>
       </c>
       <c r="H338" t="n">
         <v>20928</v>
@@ -10287,7 +10287,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G342" t="n">
-        <v>8.74786376953125</v>
+        <v>8.74786281585693</v>
       </c>
       <c r="H342" t="n">
         <v>36062</v>
@@ -10316,7 +10316,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G343" t="n">
-        <v>8.74786376953125</v>
+        <v>8.74786281585693</v>
       </c>
       <c r="H343" t="n">
         <v>59646</v>
@@ -10345,7 +10345,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G344" t="n">
-        <v>8.74786376953125</v>
+        <v>8.74786281585693</v>
       </c>
       <c r="H344" t="n">
         <v>998</v>
@@ -10432,7 +10432,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G347" t="n">
-        <v>8.65130710601807</v>
+        <v>8.65130805969238</v>
       </c>
       <c r="H347" t="n">
         <v>3955</v>
@@ -10461,7 +10461,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G348" t="n">
-        <v>8.76717376708984</v>
+        <v>8.76717472076416</v>
       </c>
       <c r="H348" t="n">
         <v>8969</v>
@@ -10490,7 +10490,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G349" t="n">
-        <v>8.70924091339111</v>
+        <v>8.70924186706543</v>
       </c>
       <c r="H349" t="n">
         <v>20895</v>
@@ -10635,7 +10635,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G354" t="n">
-        <v>8.63199710845947</v>
+        <v>8.63199615478516</v>
       </c>
       <c r="H354" t="n">
         <v>746</v>
@@ -10722,7 +10722,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>8.65130710601807</v>
+        <v>8.65130805969238</v>
       </c>
       <c r="H357" t="n">
         <v>2883</v>
@@ -10809,7 +10809,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G360" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H360" t="n">
         <v>1072</v>
@@ -10838,7 +10838,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H361" t="n">
         <v>299</v>
@@ -11070,7 +11070,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G369" t="n">
-        <v>8.47750949859619</v>
+        <v>8.47751045227051</v>
       </c>
       <c r="H369" t="n">
         <v>1997</v>
@@ -11099,7 +11099,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G370" t="n">
-        <v>8.47750949859619</v>
+        <v>8.47751045227051</v>
       </c>
       <c r="H370" t="n">
         <v>3224</v>
@@ -11128,7 +11128,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G371" t="n">
-        <v>8.53544330596924</v>
+        <v>8.53544235229492</v>
       </c>
       <c r="H371" t="n">
         <v>5429</v>
@@ -11157,7 +11157,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G372" t="n">
-        <v>8.74786376953125</v>
+        <v>8.74786281585693</v>
       </c>
       <c r="H372" t="n">
         <v>8776</v>
@@ -11331,7 +11331,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G378" t="n">
-        <v>8.6548433303833</v>
+        <v>8.65484237670898</v>
       </c>
       <c r="H378" t="n">
         <v>4178</v>
@@ -11360,7 +11360,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G379" t="n">
-        <v>8.67433547973633</v>
+        <v>8.67433452606201</v>
       </c>
       <c r="H379" t="n">
         <v>8702</v>
@@ -11389,7 +11389,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G380" t="n">
-        <v>8.55737781524658</v>
+        <v>8.5573787689209</v>
       </c>
       <c r="H380" t="n">
         <v>3988</v>
@@ -11418,7 +11418,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>8.57687187194824</v>
+        <v>8.57687091827393</v>
       </c>
       <c r="H381" t="n">
         <v>581</v>
@@ -11447,7 +11447,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G382" t="n">
-        <v>8.79129409790039</v>
+        <v>8.79129314422607</v>
       </c>
       <c r="H382" t="n">
         <v>10780</v>
@@ -11505,7 +11505,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G384" t="n">
-        <v>8.67433547973633</v>
+        <v>8.67433452606201</v>
       </c>
       <c r="H384" t="n">
         <v>2635</v>
@@ -11592,7 +11592,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G387" t="n">
-        <v>8.71332168579102</v>
+        <v>8.7133207321167</v>
       </c>
       <c r="H387" t="n">
         <v>13870</v>
@@ -11650,7 +11650,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G389" t="n">
-        <v>8.73281478881836</v>
+        <v>8.73281383514404</v>
       </c>
       <c r="H389" t="n">
         <v>7250</v>
@@ -11679,7 +11679,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>8.73281478881836</v>
+        <v>8.73281383514404</v>
       </c>
       <c r="H390" t="n">
         <v>8078</v>
@@ -11708,7 +11708,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G391" t="n">
-        <v>8.73281478881836</v>
+        <v>8.73281383514404</v>
       </c>
       <c r="H391" t="n">
         <v>16733</v>
@@ -11737,7 +11737,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>8.73281478881836</v>
+        <v>8.73281383514404</v>
       </c>
       <c r="H392" t="n">
         <v>4956</v>
@@ -11766,7 +11766,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>8.73281478881836</v>
+        <v>8.73281383514404</v>
       </c>
       <c r="H393" t="n">
         <v>6859</v>
@@ -11795,7 +11795,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G394" t="n">
-        <v>8.73281478881836</v>
+        <v>8.73281383514404</v>
       </c>
       <c r="H394" t="n">
         <v>8968</v>
@@ -11853,7 +11853,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G396" t="n">
-        <v>8.67433547973633</v>
+        <v>8.67433452606201</v>
       </c>
       <c r="H396" t="n">
         <v>11489</v>
@@ -11882,7 +11882,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G397" t="n">
-        <v>8.73281478881836</v>
+        <v>8.73281383514404</v>
       </c>
       <c r="H397" t="n">
         <v>15733</v>
@@ -12520,7 +12520,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G419" t="n">
-        <v>8.79129409790039</v>
+        <v>8.79129314422607</v>
       </c>
       <c r="H419" t="n">
         <v>8156</v>
@@ -12549,7 +12549,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G420" t="n">
-        <v>8.79129409790039</v>
+        <v>8.79129314422607</v>
       </c>
       <c r="H420" t="n">
         <v>1912</v>
@@ -12810,7 +12810,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G429" t="n">
-        <v>8.94723701477051</v>
+        <v>8.94723606109619</v>
       </c>
       <c r="H429" t="n">
         <v>9874</v>
@@ -12897,7 +12897,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>8.67433547973633</v>
+        <v>8.67433452606201</v>
       </c>
       <c r="H432" t="n">
         <v>20846</v>
@@ -13013,7 +13013,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G436" t="n">
-        <v>8.94723701477051</v>
+        <v>8.94723606109619</v>
       </c>
       <c r="H436" t="n">
         <v>14343</v>
@@ -13071,7 +13071,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G438" t="n">
-        <v>8.98622226715088</v>
+        <v>8.98622131347656</v>
       </c>
       <c r="H438" t="n">
         <v>5816</v>
@@ -13100,7 +13100,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G439" t="n">
-        <v>8.96672916412354</v>
+        <v>8.96672821044922</v>
       </c>
       <c r="H439" t="n">
         <v>2547</v>
@@ -13129,7 +13129,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>8.96672916412354</v>
+        <v>8.96672821044922</v>
       </c>
       <c r="H440" t="n">
         <v>1343</v>
@@ -13158,7 +13158,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>8.96672916412354</v>
+        <v>8.96672821044922</v>
       </c>
       <c r="H441" t="n">
         <v>3058</v>
@@ -13274,7 +13274,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G445" t="n">
-        <v>9.12267112731934</v>
+        <v>9.12267208099365</v>
       </c>
       <c r="H445" t="n">
         <v>3603</v>
@@ -13332,7 +13332,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G447" t="n">
-        <v>9.20064258575439</v>
+        <v>9.20064353942871</v>
       </c>
       <c r="H447" t="n">
         <v>17365</v>
@@ -13448,7 +13448,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G451" t="n">
-        <v>9.51252937316895</v>
+        <v>9.51253032684326</v>
       </c>
       <c r="H451" t="n">
         <v>22601</v>
@@ -13477,7 +13477,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G452" t="n">
-        <v>9.51252937316895</v>
+        <v>9.51253032684326</v>
       </c>
       <c r="H452" t="n">
         <v>18345</v>
@@ -13680,7 +13680,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G459" t="n">
-        <v>9.37607860565186</v>
+        <v>9.37607955932617</v>
       </c>
       <c r="H459" t="n">
         <v>12381</v>
@@ -13767,7 +13767,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G462" t="n">
-        <v>9.37607860565186</v>
+        <v>9.37607955932617</v>
       </c>
       <c r="H462" t="n">
         <v>47114</v>
@@ -13796,7 +13796,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G463" t="n">
-        <v>9.37607860565186</v>
+        <v>9.37607955932617</v>
       </c>
       <c r="H463" t="n">
         <v>28654</v>
@@ -13825,7 +13825,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>9.37607860565186</v>
+        <v>9.37607955932617</v>
       </c>
       <c r="H464" t="n">
         <v>44888</v>
@@ -13883,7 +13883,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G466" t="n">
-        <v>9.2981071472168</v>
+        <v>9.29810810089111</v>
       </c>
       <c r="H466" t="n">
         <v>34817</v>
@@ -13941,7 +13941,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G468" t="n">
-        <v>9.62948703765869</v>
+        <v>9.62948799133301</v>
       </c>
       <c r="H468" t="n">
         <v>49815</v>
@@ -14028,7 +14028,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G471" t="n">
-        <v>9.2981071472168</v>
+        <v>9.29810810089111</v>
       </c>
       <c r="H471" t="n">
         <v>103158</v>
@@ -14057,7 +14057,7 @@
         <v>9.5</v>
       </c>
       <c r="G472" t="n">
-        <v>9.25912189483643</v>
+        <v>9.25912284851074</v>
       </c>
       <c r="H472" t="n">
         <v>75426</v>
@@ -14202,7 +14202,7 @@
         <v>9.5</v>
       </c>
       <c r="G477" t="n">
-        <v>9.25912189483643</v>
+        <v>9.25912284851074</v>
       </c>
       <c r="H477" t="n">
         <v>24059</v>
@@ -14231,7 +14231,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>9.2981071472168</v>
+        <v>9.29810810089111</v>
       </c>
       <c r="H478" t="n">
         <v>8181</v>
@@ -14318,7 +14318,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G481" t="n">
-        <v>9.590500831604</v>
+        <v>9.59050178527832</v>
       </c>
       <c r="H481" t="n">
         <v>27152</v>
@@ -14376,7 +14376,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G483" t="n">
-        <v>10.087571144104</v>
+        <v>10.0875701904297</v>
       </c>
       <c r="H483" t="n">
         <v>99460</v>
@@ -14405,7 +14405,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G484" t="n">
-        <v>10.1850347518921</v>
+        <v>10.1850337982178</v>
       </c>
       <c r="H484" t="n">
         <v>42643</v>
@@ -14463,7 +14463,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G486" t="n">
-        <v>10.3312311172485</v>
+        <v>10.3312320709229</v>
       </c>
       <c r="H486" t="n">
         <v>14224</v>
@@ -14492,7 +14492,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G487" t="n">
-        <v>10.3312311172485</v>
+        <v>10.3312320709229</v>
       </c>
       <c r="H487" t="n">
         <v>40436</v>
@@ -14521,7 +14521,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>10.1850347518921</v>
+        <v>10.1850337982178</v>
       </c>
       <c r="H488" t="n">
         <v>58963</v>
@@ -14550,7 +14550,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G489" t="n">
-        <v>10.0388374328613</v>
+        <v>10.0388383865356</v>
       </c>
       <c r="H489" t="n">
         <v>31431</v>
@@ -14608,7 +14608,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>10.3312311172485</v>
+        <v>10.3312320709229</v>
       </c>
       <c r="H491" t="n">
         <v>7253</v>
@@ -14666,7 +14666,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G493" t="n">
-        <v>10.3312311172485</v>
+        <v>10.3312320709229</v>
       </c>
       <c r="H493" t="n">
         <v>9014</v>
@@ -14753,7 +14753,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>10.1363019943237</v>
+        <v>10.1363010406494</v>
       </c>
       <c r="H496" t="n">
         <v>7452</v>
@@ -14782,7 +14782,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>10.1363019943237</v>
+        <v>10.1363010406494</v>
       </c>
       <c r="H497" t="n">
         <v>21636</v>
@@ -14811,7 +14811,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G498" t="n">
-        <v>10.1363019943237</v>
+        <v>10.1363010406494</v>
       </c>
       <c r="H498" t="n">
         <v>34176</v>
@@ -14840,7 +14840,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G499" t="n">
-        <v>10.1850347518921</v>
+        <v>10.1850337982178</v>
       </c>
       <c r="H499" t="n">
         <v>73943</v>
@@ -14869,7 +14869,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>10.0388374328613</v>
+        <v>10.0388383865356</v>
       </c>
       <c r="H500" t="n">
         <v>53170</v>
@@ -14927,7 +14927,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G502" t="n">
-        <v>10.6723556518555</v>
+        <v>10.6723566055298</v>
       </c>
       <c r="H502" t="n">
         <v>93835</v>
@@ -14985,7 +14985,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G504" t="n">
-        <v>10.6723556518555</v>
+        <v>10.6723566055298</v>
       </c>
       <c r="H504" t="n">
         <v>42791</v>
@@ -15217,7 +15217,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G512" t="n">
-        <v>11.0134830474854</v>
+        <v>11.013482093811</v>
       </c>
       <c r="H512" t="n">
         <v>81844</v>
@@ -15246,7 +15246,7 @@
         <v>11.25</v>
       </c>
       <c r="G513" t="n">
-        <v>10.9647493362427</v>
+        <v>10.964750289917</v>
       </c>
       <c r="H513" t="n">
         <v>65236</v>
@@ -15507,7 +15507,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G522" t="n">
-        <v>11.3058767318726</v>
+        <v>11.3058757781982</v>
       </c>
       <c r="H522" t="n">
         <v>74151</v>
@@ -15594,7 +15594,7 @@
         <v>12</v>
       </c>
       <c r="G525" t="n">
-        <v>11.6957340240479</v>
+        <v>11.6957330703735</v>
       </c>
       <c r="H525" t="n">
         <v>165830</v>
@@ -15681,7 +15681,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>12.0368595123291</v>
+        <v>12.0368585586548</v>
       </c>
       <c r="H528" t="n">
         <v>204255</v>
@@ -15913,7 +15913,7 @@
         <v>12</v>
       </c>
       <c r="G536" t="n">
-        <v>11.6957340240479</v>
+        <v>11.6957330703735</v>
       </c>
       <c r="H536" t="n">
         <v>25535</v>
@@ -16000,7 +16000,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G539" t="n">
-        <v>11.4033403396606</v>
+        <v>11.4033393859863</v>
       </c>
       <c r="H539" t="n">
         <v>20898</v>
@@ -16087,7 +16087,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G542" t="n">
-        <v>11.4033403396606</v>
+        <v>11.4033393859863</v>
       </c>
       <c r="H542" t="n">
         <v>25345</v>
@@ -16203,7 +16203,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G546" t="n">
-        <v>11.4033403396606</v>
+        <v>11.4033393859863</v>
       </c>
       <c r="H546" t="n">
         <v>47534</v>
@@ -16261,7 +16261,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G548" t="n">
-        <v>11.7931976318359</v>
+        <v>11.7931985855103</v>
       </c>
       <c r="H548" t="n">
         <v>47029</v>
@@ -16348,7 +16348,7 @@
         <v>12</v>
       </c>
       <c r="G551" t="n">
-        <v>11.6957340240479</v>
+        <v>11.6957330703735</v>
       </c>
       <c r="H551" t="n">
         <v>30358</v>
@@ -16435,7 +16435,7 @@
         <v>12</v>
       </c>
       <c r="G554" t="n">
-        <v>11.6957340240479</v>
+        <v>11.6957330703735</v>
       </c>
       <c r="H554" t="n">
         <v>8761</v>
@@ -16464,7 +16464,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G555" t="n">
-        <v>11.7931976318359</v>
+        <v>11.7931985855103</v>
       </c>
       <c r="H555" t="n">
         <v>13533</v>
@@ -16493,7 +16493,7 @@
         <v>12</v>
       </c>
       <c r="G556" t="n">
-        <v>11.6957340240479</v>
+        <v>11.6957330703735</v>
       </c>
       <c r="H556" t="n">
         <v>5809</v>
@@ -16522,7 +16522,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G557" t="n">
-        <v>11.890661239624</v>
+        <v>11.8906621932983</v>
       </c>
       <c r="H557" t="n">
         <v>10698</v>
@@ -16609,7 +16609,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>11.7931976318359</v>
+        <v>11.7931985855103</v>
       </c>
       <c r="H560" t="n">
         <v>93481</v>
@@ -16638,7 +16638,7 @@
         <v>12</v>
       </c>
       <c r="G561" t="n">
-        <v>11.6957340240479</v>
+        <v>11.6957330703735</v>
       </c>
       <c r="H561" t="n">
         <v>34950</v>
@@ -16667,7 +16667,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G562" t="n">
-        <v>11.6470012664795</v>
+        <v>11.6470003128052</v>
       </c>
       <c r="H562" t="n">
         <v>15367</v>
@@ -16696,7 +16696,7 @@
         <v>12</v>
       </c>
       <c r="G563" t="n">
-        <v>11.6957340240479</v>
+        <v>11.6957330703735</v>
       </c>
       <c r="H563" t="n">
         <v>39064</v>
@@ -16725,7 +16725,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>11.7931976318359</v>
+        <v>11.7931985855103</v>
       </c>
       <c r="H564" t="n">
         <v>22959</v>
@@ -16754,7 +16754,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G565" t="n">
-        <v>11.6470012664795</v>
+        <v>11.6470003128052</v>
       </c>
       <c r="H565" t="n">
         <v>14206</v>
@@ -16812,7 +16812,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G567" t="n">
-        <v>11.7931976318359</v>
+        <v>11.7931985855103</v>
       </c>
       <c r="H567" t="n">
         <v>56931</v>
@@ -16841,7 +16841,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>11.7931976318359</v>
+        <v>11.7931985855103</v>
       </c>
       <c r="H568" t="n">
         <v>12168</v>
@@ -16957,7 +16957,7 @@
         <v>12</v>
       </c>
       <c r="G572" t="n">
-        <v>11.6957340240479</v>
+        <v>11.6957330703735</v>
       </c>
       <c r="H572" t="n">
         <v>50297</v>
@@ -17102,7 +17102,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G577" t="n">
-        <v>11.890661239624</v>
+        <v>11.8906621932983</v>
       </c>
       <c r="H577" t="n">
         <v>8377</v>
@@ -17827,7 +17827,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G602" t="n">
-        <v>12.7093629837036</v>
+        <v>12.7093639373779</v>
       </c>
       <c r="H602" t="n">
         <v>70858</v>
@@ -17885,7 +17885,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G604" t="n">
-        <v>12.6898708343506</v>
+        <v>12.6898717880249</v>
       </c>
       <c r="H604" t="n">
         <v>57453</v>
@@ -17943,7 +17943,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G606" t="n">
-        <v>12.865306854248</v>
+        <v>12.8653059005737</v>
       </c>
       <c r="H606" t="n">
         <v>71717</v>
@@ -18088,7 +18088,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G611" t="n">
-        <v>13.3136434555054</v>
+        <v>13.3136425018311</v>
       </c>
       <c r="H611" t="n">
         <v>69440</v>
@@ -18233,7 +18233,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G616" t="n">
-        <v>13.4500932693481</v>
+        <v>13.4500942230225</v>
       </c>
       <c r="H616" t="n">
         <v>45178</v>
@@ -18320,7 +18320,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G619" t="n">
-        <v>13.3136434555054</v>
+        <v>13.3136425018311</v>
       </c>
       <c r="H619" t="n">
         <v>22500</v>
@@ -18349,7 +18349,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G620" t="n">
-        <v>13.3136434555054</v>
+        <v>13.3136425018311</v>
       </c>
       <c r="H620" t="n">
         <v>23712</v>
@@ -18407,7 +18407,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G622" t="n">
-        <v>13.6255292892456</v>
+        <v>13.6255283355713</v>
       </c>
       <c r="H622" t="n">
         <v>54015</v>
@@ -18523,7 +18523,7 @@
         <v>14.5</v>
       </c>
       <c r="G626" t="n">
-        <v>14.132345199585</v>
+        <v>14.1323442459106</v>
       </c>
       <c r="H626" t="n">
         <v>143325</v>
@@ -29259,6 +29259,35 @@
         <v>17887</v>
       </c>
       <c r="I996" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="s">
+        <v>9</v>
+      </c>
+      <c r="B997" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C997" t="n">
+        <v>22.6499996185303</v>
+      </c>
+      <c r="D997" t="n">
+        <v>22.8999996185303</v>
+      </c>
+      <c r="E997" t="n">
+        <v>22.5499992370605</v>
+      </c>
+      <c r="F997" t="n">
+        <v>23</v>
+      </c>
+      <c r="G997" t="n">
+        <v>23</v>
+      </c>
+      <c r="H997" t="n">
+        <v>13460</v>
+      </c>
+      <c r="I997" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/REVO.MI.xlsx
+++ b/data/REVO.MI.xlsx
@@ -514,7 +514,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G5" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H5" t="n">
         <v>15746</v>
@@ -572,7 +572,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G7" t="n">
-        <v>8.08163547515869</v>
+        <v>8.08163452148438</v>
       </c>
       <c r="H7" t="n">
         <v>2650</v>
@@ -601,7 +601,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G8" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H8" t="n">
         <v>3358</v>
@@ -659,7 +659,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G10" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H10" t="n">
         <v>6204</v>
@@ -688,7 +688,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G11" t="n">
-        <v>8.04301357269287</v>
+        <v>8.04301261901855</v>
       </c>
       <c r="H11" t="n">
         <v>66</v>
@@ -717,7 +717,7 @@
         <v>8.25</v>
       </c>
       <c r="G12" t="n">
-        <v>7.96576976776123</v>
+        <v>7.96576881408691</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
@@ -804,7 +804,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G15" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H15" t="n">
         <v>32</v>
@@ -862,7 +862,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G17" t="n">
-        <v>7.94645738601685</v>
+        <v>7.946457862854</v>
       </c>
       <c r="H17" t="n">
         <v>2333</v>
@@ -978,7 +978,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G21" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H21" t="n">
         <v>2849</v>
@@ -1007,7 +1007,7 @@
         <v>8.25</v>
       </c>
       <c r="G22" t="n">
-        <v>7.96576976776123</v>
+        <v>7.96576881408691</v>
       </c>
       <c r="H22" t="n">
         <v>1800</v>
@@ -1036,7 +1036,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G23" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H23" t="n">
         <v>480</v>
@@ -1065,7 +1065,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G24" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H24" t="n">
         <v>8168</v>
@@ -1297,7 +1297,7 @@
         <v>8.25</v>
       </c>
       <c r="G32" t="n">
-        <v>7.96576976776123</v>
+        <v>7.96576881408691</v>
       </c>
       <c r="H32" t="n">
         <v>10305</v>
@@ -1326,7 +1326,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H33" t="n">
         <v>3280</v>
@@ -1384,7 +1384,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H35" t="n">
         <v>8723</v>
@@ -1413,7 +1413,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G36" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H36" t="n">
         <v>411</v>
@@ -1442,7 +1442,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G37" t="n">
-        <v>8.02370262145996</v>
+        <v>8.02370166778564</v>
       </c>
       <c r="H37" t="n">
         <v>4958</v>
@@ -1471,7 +1471,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H38" t="n">
         <v>80</v>
@@ -1529,7 +1529,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G40" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H40" t="n">
         <v>3659</v>
@@ -1558,7 +1558,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G41" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H41" t="n">
         <v>3082</v>
@@ -1645,7 +1645,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G44" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H44" t="n">
         <v>15725</v>
@@ -1674,7 +1674,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G45" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H45" t="n">
         <v>8898</v>
@@ -1790,7 +1790,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G49" t="n">
-        <v>7.90783596038818</v>
+        <v>7.90783548355103</v>
       </c>
       <c r="H49" t="n">
         <v>9413</v>
@@ -1819,7 +1819,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H50" t="n">
         <v>15331</v>
@@ -1848,7 +1848,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G51" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H51" t="n">
         <v>8900</v>
@@ -1993,7 +1993,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G56" t="n">
-        <v>7.98508071899414</v>
+        <v>7.98508024215698</v>
       </c>
       <c r="H56" t="n">
         <v>8601</v>
@@ -2022,7 +2022,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G57" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H57" t="n">
         <v>1380</v>
@@ -2051,7 +2051,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H58" t="n">
         <v>12623</v>
@@ -2080,7 +2080,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G59" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H59" t="n">
         <v>3310</v>
@@ -2109,7 +2109,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G60" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H60" t="n">
         <v>12417</v>
@@ -2312,7 +2312,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G67" t="n">
-        <v>8.12025547027588</v>
+        <v>8.1202564239502</v>
       </c>
       <c r="H67" t="n">
         <v>969</v>
@@ -2341,7 +2341,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G68" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H68" t="n">
         <v>7666</v>
@@ -2370,7 +2370,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G69" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H69" t="n">
         <v>3050</v>
@@ -2399,7 +2399,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G70" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H70" t="n">
         <v>7975</v>
@@ -2457,7 +2457,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H72" t="n">
         <v>10401</v>
@@ -2486,7 +2486,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G73" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H73" t="n">
         <v>21359</v>
@@ -2515,7 +2515,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G74" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H74" t="n">
         <v>9297</v>
@@ -2544,7 +2544,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G75" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H75" t="n">
         <v>1884</v>
@@ -2602,7 +2602,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G77" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H77" t="n">
         <v>4665</v>
@@ -2631,7 +2631,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G78" t="n">
-        <v>8.12025547027588</v>
+        <v>8.1202564239502</v>
       </c>
       <c r="H78" t="n">
         <v>3676</v>
@@ -2660,7 +2660,7 @@
         <v>8.25</v>
       </c>
       <c r="G79" t="n">
-        <v>7.96576976776123</v>
+        <v>7.96576881408691</v>
       </c>
       <c r="H79" t="n">
         <v>3004</v>
@@ -2689,7 +2689,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G80" t="n">
-        <v>7.98508071899414</v>
+        <v>7.98508024215698</v>
       </c>
       <c r="H80" t="n">
         <v>2183</v>
@@ -2718,7 +2718,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H81" t="n">
         <v>2117</v>
@@ -2747,7 +2747,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G82" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H82" t="n">
         <v>1745</v>
@@ -2805,7 +2805,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G84" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H84" t="n">
         <v>6600</v>
@@ -2834,7 +2834,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G85" t="n">
-        <v>8.08163547515869</v>
+        <v>8.08163452148438</v>
       </c>
       <c r="H85" t="n">
         <v>3150</v>
@@ -2863,7 +2863,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>8.08163547515869</v>
+        <v>8.08163452148438</v>
       </c>
       <c r="H86" t="n">
         <v>500</v>
@@ -2892,7 +2892,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G87" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H87" t="n">
         <v>7121</v>
@@ -2950,7 +2950,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G89" t="n">
-        <v>7.98508071899414</v>
+        <v>7.98508024215698</v>
       </c>
       <c r="H89" t="n">
         <v>14762</v>
@@ -3008,7 +3008,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G91" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H91" t="n">
         <v>928</v>
@@ -3037,7 +3037,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G92" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H92" t="n">
         <v>4665</v>
@@ -3066,7 +3066,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G93" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H93" t="n">
         <v>17678</v>
@@ -3095,7 +3095,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G94" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H94" t="n">
         <v>3001</v>
@@ -3124,7 +3124,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G95" t="n">
-        <v>7.82093715667725</v>
+        <v>7.8209376335144</v>
       </c>
       <c r="H95" t="n">
         <v>33055</v>
@@ -3153,7 +3153,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G96" t="n">
-        <v>7.78231573104858</v>
+        <v>7.78231525421143</v>
       </c>
       <c r="H96" t="n">
         <v>15390</v>
@@ -3182,7 +3182,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G97" t="n">
-        <v>7.74369382858276</v>
+        <v>7.74369335174561</v>
       </c>
       <c r="H97" t="n">
         <v>25102</v>
@@ -3211,7 +3211,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G98" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H98" t="n">
         <v>27915</v>
@@ -3240,7 +3240,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H99" t="n">
         <v>6541</v>
@@ -3269,7 +3269,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>7.70507097244263</v>
+        <v>7.70507144927979</v>
       </c>
       <c r="H100" t="n">
         <v>2228</v>
@@ -3356,7 +3356,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>7.70507097244263</v>
+        <v>7.70507144927979</v>
       </c>
       <c r="H103" t="n">
         <v>238</v>
@@ -3385,7 +3385,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H104" t="n">
         <v>4845</v>
@@ -3501,7 +3501,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>7.6278281211853</v>
+        <v>7.62782764434814</v>
       </c>
       <c r="H108" t="n">
         <v>3757</v>
@@ -3588,7 +3588,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G111" t="n">
-        <v>7.78231573104858</v>
+        <v>7.78231525421143</v>
       </c>
       <c r="H111" t="n">
         <v>40906</v>
@@ -3675,7 +3675,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H114" t="n">
         <v>4325</v>
@@ -3704,7 +3704,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H115" t="n">
         <v>3981</v>
@@ -3791,7 +3791,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G118" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H118" t="n">
         <v>4146</v>
@@ -3820,7 +3820,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G119" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H119" t="n">
         <v>2963</v>
@@ -3849,7 +3849,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G120" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H120" t="n">
         <v>40121</v>
@@ -3994,7 +3994,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H125" t="n">
         <v>42823</v>
@@ -4052,7 +4052,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>8.61268615722656</v>
+        <v>8.61268711090088</v>
       </c>
       <c r="H127" t="n">
         <v>14042</v>
@@ -4081,7 +4081,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G128" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H128" t="n">
         <v>4585</v>
@@ -4110,7 +4110,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G129" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H129" t="n">
         <v>6000</v>
@@ -4139,7 +4139,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G130" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H130" t="n">
         <v>19296</v>
@@ -4197,7 +4197,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G132" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H132" t="n">
         <v>3386</v>
@@ -4284,7 +4284,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G135" t="n">
-        <v>8.47751045227051</v>
+        <v>8.47750949859619</v>
       </c>
       <c r="H135" t="n">
         <v>2684</v>
@@ -4313,7 +4313,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G136" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H136" t="n">
         <v>1044</v>
@@ -4371,7 +4371,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H138" t="n">
         <v>475</v>
@@ -4400,7 +4400,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G139" t="n">
-        <v>8.5161304473877</v>
+        <v>8.51613140106201</v>
       </c>
       <c r="H139" t="n">
         <v>312</v>
@@ -4429,7 +4429,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H140" t="n">
         <v>1058</v>
@@ -4545,7 +4545,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G144" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H144" t="n">
         <v>1986</v>
@@ -4603,7 +4603,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G146" t="n">
-        <v>8.34233283996582</v>
+        <v>8.34233379364014</v>
       </c>
       <c r="H146" t="n">
         <v>13733</v>
@@ -4748,7 +4748,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G151" t="n">
-        <v>8.34233283996582</v>
+        <v>8.34233379364014</v>
       </c>
       <c r="H151" t="n">
         <v>4010</v>
@@ -4777,7 +4777,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G152" t="n">
-        <v>8.38095569610596</v>
+        <v>8.38095474243164</v>
       </c>
       <c r="H152" t="n">
         <v>7019</v>
@@ -4806,7 +4806,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G153" t="n">
-        <v>8.34233283996582</v>
+        <v>8.34233379364014</v>
       </c>
       <c r="H153" t="n">
         <v>16815</v>
@@ -5038,7 +5038,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G161" t="n">
-        <v>8.22646713256836</v>
+        <v>8.22646808624268</v>
       </c>
       <c r="H161" t="n">
         <v>18016</v>
@@ -5067,7 +5067,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G162" t="n">
-        <v>8.22646713256836</v>
+        <v>8.22646808624268</v>
       </c>
       <c r="H162" t="n">
         <v>257</v>
@@ -5183,7 +5183,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G166" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H166" t="n">
         <v>9385</v>
@@ -5386,7 +5386,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G173" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H173" t="n">
         <v>7608</v>
@@ -5415,7 +5415,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G174" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H174" t="n">
         <v>9388</v>
@@ -5444,7 +5444,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G175" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H175" t="n">
         <v>4377</v>
@@ -5531,7 +5531,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G178" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H178" t="n">
         <v>10600</v>
@@ -5618,7 +5618,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G181" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H181" t="n">
         <v>20346</v>
@@ -5734,7 +5734,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G185" t="n">
-        <v>7.82093715667725</v>
+        <v>7.8209376335144</v>
       </c>
       <c r="H185" t="n">
         <v>4523</v>
@@ -5763,7 +5763,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G186" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H186" t="n">
         <v>3135</v>
@@ -5821,7 +5821,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>7.82093715667725</v>
+        <v>7.8209376335144</v>
       </c>
       <c r="H188" t="n">
         <v>271</v>
@@ -5850,7 +5850,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G189" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H189" t="n">
         <v>5300</v>
@@ -5879,7 +5879,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G190" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H190" t="n">
         <v>3983</v>
@@ -5908,7 +5908,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G191" t="n">
-        <v>7.82093715667725</v>
+        <v>7.8209376335144</v>
       </c>
       <c r="H191" t="n">
         <v>8096</v>
@@ -5937,7 +5937,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G192" t="n">
-        <v>7.82093715667725</v>
+        <v>7.8209376335144</v>
       </c>
       <c r="H192" t="n">
         <v>9675</v>
@@ -5995,7 +5995,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G194" t="n">
-        <v>7.82093715667725</v>
+        <v>7.8209376335144</v>
       </c>
       <c r="H194" t="n">
         <v>25407</v>
@@ -6053,7 +6053,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>7.82093715667725</v>
+        <v>7.8209376335144</v>
       </c>
       <c r="H196" t="n">
         <v>9084</v>
@@ -6082,7 +6082,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G197" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H197" t="n">
         <v>21391</v>
@@ -6140,7 +6140,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G199" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H199" t="n">
         <v>20734</v>
@@ -6227,7 +6227,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G202" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H202" t="n">
         <v>3347</v>
@@ -6401,7 +6401,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G208" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H208" t="n">
         <v>1089</v>
@@ -6459,7 +6459,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G210" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H210" t="n">
         <v>1549</v>
@@ -6517,7 +6517,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G212" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H212" t="n">
         <v>12241</v>
@@ -6546,7 +6546,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H213" t="n">
         <v>55092</v>
@@ -6575,7 +6575,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G214" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H214" t="n">
         <v>8492</v>
@@ -6604,7 +6604,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G215" t="n">
-        <v>8.07197952270508</v>
+        <v>8.07197856903076</v>
       </c>
       <c r="H215" t="n">
         <v>4566</v>
@@ -6633,7 +6633,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G216" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H216" t="n">
         <v>16342</v>
@@ -6691,7 +6691,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G218" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H218" t="n">
         <v>1736</v>
@@ -6778,7 +6778,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H221" t="n">
         <v>7392</v>
@@ -6836,7 +6836,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G223" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H223" t="n">
         <v>5300</v>
@@ -6894,7 +6894,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H225" t="n">
         <v>1316</v>
@@ -7097,7 +7097,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H232" t="n">
         <v>11067</v>
@@ -7126,7 +7126,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>8.16853332519531</v>
+        <v>8.16853427886963</v>
       </c>
       <c r="H233" t="n">
         <v>6312</v>
@@ -7155,7 +7155,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G234" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H234" t="n">
         <v>826</v>
@@ -7184,7 +7184,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H235" t="n">
         <v>752</v>
@@ -7271,7 +7271,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G238" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H238" t="n">
         <v>3477</v>
@@ -7300,7 +7300,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G239" t="n">
-        <v>7.89818143844604</v>
+        <v>7.89818096160889</v>
       </c>
       <c r="H239" t="n">
         <v>6101</v>
@@ -7416,7 +7416,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G243" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H243" t="n">
         <v>3669</v>
@@ -7474,7 +7474,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G245" t="n">
-        <v>7.78231573104858</v>
+        <v>7.78231525421143</v>
       </c>
       <c r="H245" t="n">
         <v>2691</v>
@@ -7648,7 +7648,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G251" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H251" t="n">
         <v>17702</v>
@@ -7677,7 +7677,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G252" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H252" t="n">
         <v>4458</v>
@@ -7764,7 +7764,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G255" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H255" t="n">
         <v>18125</v>
@@ -7880,7 +7880,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H259" t="n">
         <v>13726</v>
@@ -7909,7 +7909,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G260" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H260" t="n">
         <v>14869</v>
@@ -7938,7 +7938,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G261" t="n">
-        <v>7.99473524093628</v>
+        <v>7.99473571777344</v>
       </c>
       <c r="H261" t="n">
         <v>2653</v>
@@ -7996,7 +7996,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H263" t="n">
         <v>15803</v>
@@ -8025,7 +8025,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G264" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H264" t="n">
         <v>7199</v>
@@ -8112,7 +8112,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G267" t="n">
-        <v>7.74369382858276</v>
+        <v>7.74369335174561</v>
       </c>
       <c r="H267" t="n">
         <v>16020</v>
@@ -8170,7 +8170,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G269" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H269" t="n">
         <v>22886</v>
@@ -8199,7 +8199,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G270" t="n">
-        <v>7.74369382858276</v>
+        <v>7.74369335174561</v>
       </c>
       <c r="H270" t="n">
         <v>40748</v>
@@ -8257,7 +8257,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H272" t="n">
         <v>12707</v>
@@ -8286,7 +8286,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G273" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H273" t="n">
         <v>7426</v>
@@ -8373,7 +8373,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H276" t="n">
         <v>22466</v>
@@ -8402,7 +8402,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G277" t="n">
-        <v>7.74369382858276</v>
+        <v>7.74369335174561</v>
       </c>
       <c r="H277" t="n">
         <v>3373</v>
@@ -8431,7 +8431,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G278" t="n">
-        <v>7.68576049804688</v>
+        <v>7.68576002120972</v>
       </c>
       <c r="H278" t="n">
         <v>7771</v>
@@ -8489,7 +8489,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G280" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H280" t="n">
         <v>7266</v>
@@ -8547,7 +8547,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G282" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H282" t="n">
         <v>2416</v>
@@ -8605,7 +8605,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G284" t="n">
-        <v>8.11060047149658</v>
+        <v>8.1106014251709</v>
       </c>
       <c r="H284" t="n">
         <v>12131</v>
@@ -8663,7 +8663,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G286" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H286" t="n">
         <v>2356</v>
@@ -8692,7 +8692,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G287" t="n">
-        <v>7.85955905914307</v>
+        <v>7.85955953598022</v>
       </c>
       <c r="H287" t="n">
         <v>14875</v>
@@ -8721,7 +8721,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G288" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H288" t="n">
         <v>4850</v>
@@ -8750,7 +8750,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G289" t="n">
-        <v>7.95611381530762</v>
+        <v>7.95611333847046</v>
       </c>
       <c r="H289" t="n">
         <v>6789</v>
@@ -8837,7 +8837,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G292" t="n">
-        <v>7.97542524337769</v>
+        <v>7.97542476654053</v>
       </c>
       <c r="H292" t="n">
         <v>2670</v>
@@ -8866,7 +8866,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G293" t="n">
-        <v>8.01404762268066</v>
+        <v>8.01404666900635</v>
       </c>
       <c r="H293" t="n">
         <v>11644</v>
@@ -9069,7 +9069,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G300" t="n">
-        <v>8.61268615722656</v>
+        <v>8.61268711090088</v>
       </c>
       <c r="H300" t="n">
         <v>26734</v>
@@ -9156,7 +9156,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G303" t="n">
-        <v>8.63199615478516</v>
+        <v>8.63199710845947</v>
       </c>
       <c r="H303" t="n">
         <v>22705</v>
@@ -9185,7 +9185,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G304" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H304" t="n">
         <v>26905</v>
@@ -9243,7 +9243,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G306" t="n">
-        <v>8.38095569610596</v>
+        <v>8.38095474243164</v>
       </c>
       <c r="H306" t="n">
         <v>5373</v>
@@ -9359,7 +9359,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G310" t="n">
-        <v>8.92166042327881</v>
+        <v>8.92166233062744</v>
       </c>
       <c r="H310" t="n">
         <v>29147</v>
@@ -9475,7 +9475,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>8.61268615722656</v>
+        <v>8.61268711090088</v>
       </c>
       <c r="H314" t="n">
         <v>3755</v>
@@ -9504,7 +9504,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G315" t="n">
-        <v>8.5161304473877</v>
+        <v>8.51613140106201</v>
       </c>
       <c r="H315" t="n">
         <v>3379</v>
@@ -9562,7 +9562,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H317" t="n">
         <v>6105</v>
@@ -9591,7 +9591,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G318" t="n">
-        <v>8.47751045227051</v>
+        <v>8.47750949859619</v>
       </c>
       <c r="H318" t="n">
         <v>3095</v>
@@ -9649,7 +9649,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H320" t="n">
         <v>952</v>
@@ -9678,7 +9678,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H321" t="n">
         <v>1603</v>
@@ -9707,7 +9707,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G322" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H322" t="n">
         <v>14286</v>
@@ -9736,7 +9736,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G323" t="n">
-        <v>8.38095569610596</v>
+        <v>8.38095474243164</v>
       </c>
       <c r="H323" t="n">
         <v>27377</v>
@@ -9823,7 +9823,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G326" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H326" t="n">
         <v>3583</v>
@@ -9852,7 +9852,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H327" t="n">
         <v>1758</v>
@@ -9997,7 +9997,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G332" t="n">
-        <v>8.5161304473877</v>
+        <v>8.51613140106201</v>
       </c>
       <c r="H332" t="n">
         <v>28344</v>
@@ -10055,7 +10055,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>8.72855186462402</v>
+        <v>8.72855281829834</v>
       </c>
       <c r="H334" t="n">
         <v>10228</v>
@@ -10084,7 +10084,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G335" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H335" t="n">
         <v>18023</v>
@@ -10113,7 +10113,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G336" t="n">
-        <v>8.47751045227051</v>
+        <v>8.47750949859619</v>
       </c>
       <c r="H336" t="n">
         <v>12212</v>
@@ -10142,7 +10142,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G337" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H337" t="n">
         <v>26896</v>
@@ -10287,7 +10287,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G342" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H342" t="n">
         <v>36062</v>
@@ -10316,7 +10316,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G343" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H343" t="n">
         <v>59646</v>
@@ -10345,7 +10345,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G344" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H344" t="n">
         <v>998</v>
@@ -10461,7 +10461,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G348" t="n">
-        <v>8.76717472076416</v>
+        <v>8.76717376708984</v>
       </c>
       <c r="H348" t="n">
         <v>8969</v>
@@ -10635,7 +10635,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G354" t="n">
-        <v>8.63199615478516</v>
+        <v>8.63199710845947</v>
       </c>
       <c r="H354" t="n">
         <v>746</v>
@@ -10809,7 +10809,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G360" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H360" t="n">
         <v>1072</v>
@@ -10838,7 +10838,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H361" t="n">
         <v>299</v>
@@ -10925,7 +10925,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G364" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H364" t="n">
         <v>1993</v>
@@ -10983,7 +10983,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G366" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H366" t="n">
         <v>3879</v>
@@ -11012,7 +11012,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G367" t="n">
-        <v>8.4968204498291</v>
+        <v>8.49682140350342</v>
       </c>
       <c r="H367" t="n">
         <v>17028</v>
@@ -11070,7 +11070,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G369" t="n">
-        <v>8.47751045227051</v>
+        <v>8.47750949859619</v>
       </c>
       <c r="H369" t="n">
         <v>1997</v>
@@ -11099,7 +11099,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G370" t="n">
-        <v>8.47751045227051</v>
+        <v>8.47750949859619</v>
       </c>
       <c r="H370" t="n">
         <v>3224</v>
@@ -11128,7 +11128,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G371" t="n">
-        <v>8.53544235229492</v>
+        <v>8.53544330596924</v>
       </c>
       <c r="H371" t="n">
         <v>5429</v>
@@ -11157,7 +11157,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G372" t="n">
-        <v>8.74786281585693</v>
+        <v>8.74786376953125</v>
       </c>
       <c r="H372" t="n">
         <v>8776</v>
@@ -11331,7 +11331,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G378" t="n">
-        <v>8.65484237670898</v>
+        <v>8.6548433303833</v>
       </c>
       <c r="H378" t="n">
         <v>4178</v>
@@ -11360,7 +11360,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G379" t="n">
-        <v>8.67433452606201</v>
+        <v>8.67433547973633</v>
       </c>
       <c r="H379" t="n">
         <v>8702</v>
@@ -11389,7 +11389,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G380" t="n">
-        <v>8.5573787689209</v>
+        <v>8.55737781524658</v>
       </c>
       <c r="H380" t="n">
         <v>3988</v>
@@ -11418,7 +11418,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>8.57687091827393</v>
+        <v>8.57687187194824</v>
       </c>
       <c r="H381" t="n">
         <v>581</v>
@@ -11447,7 +11447,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G382" t="n">
-        <v>8.79129314422607</v>
+        <v>8.79129409790039</v>
       </c>
       <c r="H382" t="n">
         <v>10780</v>
@@ -11505,7 +11505,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G384" t="n">
-        <v>8.67433452606201</v>
+        <v>8.67433547973633</v>
       </c>
       <c r="H384" t="n">
         <v>2635</v>
@@ -11592,7 +11592,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G387" t="n">
-        <v>8.7133207321167</v>
+        <v>8.71332168579102</v>
       </c>
       <c r="H387" t="n">
         <v>13870</v>
@@ -11650,7 +11650,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G389" t="n">
-        <v>8.73281383514404</v>
+        <v>8.73281478881836</v>
       </c>
       <c r="H389" t="n">
         <v>7250</v>
@@ -11679,7 +11679,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>8.73281383514404</v>
+        <v>8.73281478881836</v>
       </c>
       <c r="H390" t="n">
         <v>8078</v>
@@ -11708,7 +11708,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G391" t="n">
-        <v>8.73281383514404</v>
+        <v>8.73281478881836</v>
       </c>
       <c r="H391" t="n">
         <v>16733</v>
@@ -11737,7 +11737,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>8.73281383514404</v>
+        <v>8.73281478881836</v>
       </c>
       <c r="H392" t="n">
         <v>4956</v>
@@ -11766,7 +11766,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>8.73281383514404</v>
+        <v>8.73281478881836</v>
       </c>
       <c r="H393" t="n">
         <v>6859</v>
@@ -11795,7 +11795,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G394" t="n">
-        <v>8.73281383514404</v>
+        <v>8.73281478881836</v>
       </c>
       <c r="H394" t="n">
         <v>8968</v>
@@ -11853,7 +11853,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G396" t="n">
-        <v>8.67433452606201</v>
+        <v>8.67433547973633</v>
       </c>
       <c r="H396" t="n">
         <v>11489</v>
@@ -11882,7 +11882,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G397" t="n">
-        <v>8.73281383514404</v>
+        <v>8.73281478881836</v>
       </c>
       <c r="H397" t="n">
         <v>15733</v>
@@ -12520,7 +12520,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G419" t="n">
-        <v>8.79129314422607</v>
+        <v>8.79129409790039</v>
       </c>
       <c r="H419" t="n">
         <v>8156</v>
@@ -12549,7 +12549,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G420" t="n">
-        <v>8.79129314422607</v>
+        <v>8.79129409790039</v>
       </c>
       <c r="H420" t="n">
         <v>1912</v>
@@ -12810,7 +12810,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G429" t="n">
-        <v>8.94723606109619</v>
+        <v>8.94723701477051</v>
       </c>
       <c r="H429" t="n">
         <v>9874</v>
@@ -12897,7 +12897,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>8.67433452606201</v>
+        <v>8.67433547973633</v>
       </c>
       <c r="H432" t="n">
         <v>20846</v>
@@ -13013,7 +13013,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G436" t="n">
-        <v>8.94723606109619</v>
+        <v>8.94723701477051</v>
       </c>
       <c r="H436" t="n">
         <v>14343</v>
@@ -13071,7 +13071,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G438" t="n">
-        <v>8.98622131347656</v>
+        <v>8.98622226715088</v>
       </c>
       <c r="H438" t="n">
         <v>5816</v>
@@ -13100,7 +13100,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G439" t="n">
-        <v>8.96672821044922</v>
+        <v>8.96672916412354</v>
       </c>
       <c r="H439" t="n">
         <v>2547</v>
@@ -13129,7 +13129,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>8.96672821044922</v>
+        <v>8.96672916412354</v>
       </c>
       <c r="H440" t="n">
         <v>1343</v>
@@ -13158,7 +13158,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>8.96672821044922</v>
+        <v>8.96672916412354</v>
       </c>
       <c r="H441" t="n">
         <v>3058</v>
@@ -13274,7 +13274,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G445" t="n">
-        <v>9.12267208099365</v>
+        <v>9.12267112731934</v>
       </c>
       <c r="H445" t="n">
         <v>3603</v>
@@ -13332,7 +13332,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G447" t="n">
-        <v>9.20064353942871</v>
+        <v>9.20064258575439</v>
       </c>
       <c r="H447" t="n">
         <v>17365</v>
@@ -13448,7 +13448,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G451" t="n">
-        <v>9.51253032684326</v>
+        <v>9.51252937316895</v>
       </c>
       <c r="H451" t="n">
         <v>22601</v>
@@ -13477,7 +13477,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G452" t="n">
-        <v>9.51253032684326</v>
+        <v>9.51252937316895</v>
       </c>
       <c r="H452" t="n">
         <v>18345</v>
@@ -13680,7 +13680,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G459" t="n">
-        <v>9.37607955932617</v>
+        <v>9.37607860565186</v>
       </c>
       <c r="H459" t="n">
         <v>12381</v>
@@ -13767,7 +13767,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G462" t="n">
-        <v>9.37607955932617</v>
+        <v>9.37607860565186</v>
       </c>
       <c r="H462" t="n">
         <v>47114</v>
@@ -13796,7 +13796,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G463" t="n">
-        <v>9.37607955932617</v>
+        <v>9.37607860565186</v>
       </c>
       <c r="H463" t="n">
         <v>28654</v>
@@ -13825,7 +13825,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>9.37607955932617</v>
+        <v>9.37607860565186</v>
       </c>
       <c r="H464" t="n">
         <v>44888</v>
@@ -13883,7 +13883,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G466" t="n">
-        <v>9.29810810089111</v>
+        <v>9.2981071472168</v>
       </c>
       <c r="H466" t="n">
         <v>34817</v>
@@ -13941,7 +13941,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G468" t="n">
-        <v>9.62948799133301</v>
+        <v>9.62948703765869</v>
       </c>
       <c r="H468" t="n">
         <v>49815</v>
@@ -14028,7 +14028,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G471" t="n">
-        <v>9.29810810089111</v>
+        <v>9.2981071472168</v>
       </c>
       <c r="H471" t="n">
         <v>103158</v>
@@ -14057,7 +14057,7 @@
         <v>9.5</v>
       </c>
       <c r="G472" t="n">
-        <v>9.25912284851074</v>
+        <v>9.25912189483643</v>
       </c>
       <c r="H472" t="n">
         <v>75426</v>
@@ -14202,7 +14202,7 @@
         <v>9.5</v>
       </c>
       <c r="G477" t="n">
-        <v>9.25912284851074</v>
+        <v>9.25912189483643</v>
       </c>
       <c r="H477" t="n">
         <v>24059</v>
@@ -14231,7 +14231,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>9.29810810089111</v>
+        <v>9.2981071472168</v>
       </c>
       <c r="H478" t="n">
         <v>8181</v>
@@ -14318,7 +14318,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G481" t="n">
-        <v>9.59050178527832</v>
+        <v>9.590500831604</v>
       </c>
       <c r="H481" t="n">
         <v>27152</v>
@@ -14376,7 +14376,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G483" t="n">
-        <v>10.0875701904297</v>
+        <v>10.087571144104</v>
       </c>
       <c r="H483" t="n">
         <v>99460</v>
@@ -14405,7 +14405,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G484" t="n">
-        <v>10.1850337982178</v>
+        <v>10.1850347518921</v>
       </c>
       <c r="H484" t="n">
         <v>42643</v>
@@ -14463,7 +14463,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G486" t="n">
-        <v>10.3312320709229</v>
+        <v>10.3312311172485</v>
       </c>
       <c r="H486" t="n">
         <v>14224</v>
@@ -14492,7 +14492,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G487" t="n">
-        <v>10.3312320709229</v>
+        <v>10.3312311172485</v>
       </c>
       <c r="H487" t="n">
         <v>40436</v>
@@ -14521,7 +14521,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G488" t="n">
-        <v>10.1850337982178</v>
+        <v>10.1850347518921</v>
       </c>
       <c r="H488" t="n">
         <v>58963</v>
@@ -14550,7 +14550,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G489" t="n">
-        <v>10.0388383865356</v>
+        <v>10.0388374328613</v>
       </c>
       <c r="H489" t="n">
         <v>31431</v>
@@ -14608,7 +14608,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>10.3312320709229</v>
+        <v>10.3312311172485</v>
       </c>
       <c r="H491" t="n">
         <v>7253</v>
@@ -14666,7 +14666,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G493" t="n">
-        <v>10.3312320709229</v>
+        <v>10.3312311172485</v>
       </c>
       <c r="H493" t="n">
         <v>9014</v>
@@ -14753,7 +14753,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>10.1363010406494</v>
+        <v>10.1363019943237</v>
       </c>
       <c r="H496" t="n">
         <v>7452</v>
@@ -14782,7 +14782,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>10.1363010406494</v>
+        <v>10.1363019943237</v>
       </c>
       <c r="H497" t="n">
         <v>21636</v>
@@ -14811,7 +14811,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G498" t="n">
-        <v>10.1363010406494</v>
+        <v>10.1363019943237</v>
       </c>
       <c r="H498" t="n">
         <v>34176</v>
@@ -14840,7 +14840,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G499" t="n">
-        <v>10.1850337982178</v>
+        <v>10.1850347518921</v>
       </c>
       <c r="H499" t="n">
         <v>73943</v>
@@ -14869,7 +14869,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>10.0388383865356</v>
+        <v>10.0388374328613</v>
       </c>
       <c r="H500" t="n">
         <v>53170</v>
@@ -14927,7 +14927,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G502" t="n">
-        <v>10.6723566055298</v>
+        <v>10.6723556518555</v>
       </c>
       <c r="H502" t="n">
         <v>93835</v>
@@ -14985,7 +14985,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G504" t="n">
-        <v>10.6723566055298</v>
+        <v>10.6723556518555</v>
       </c>
       <c r="H504" t="n">
         <v>42791</v>
@@ -15217,7 +15217,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G512" t="n">
-        <v>11.013482093811</v>
+        <v>11.0134830474854</v>
       </c>
       <c r="H512" t="n">
         <v>81844</v>
@@ -15246,7 +15246,7 @@
         <v>11.25</v>
       </c>
       <c r="G513" t="n">
-        <v>10.964750289917</v>
+        <v>10.9647493362427</v>
       </c>
       <c r="H513" t="n">
         <v>65236</v>
@@ -15507,7 +15507,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G522" t="n">
-        <v>11.3058757781982</v>
+        <v>11.3058767318726</v>
       </c>
       <c r="H522" t="n">
         <v>74151</v>
@@ -15594,7 +15594,7 @@
         <v>12</v>
       </c>
       <c r="G525" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H525" t="n">
         <v>165830</v>
@@ -15681,7 +15681,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>12.0368585586548</v>
+        <v>12.0368595123291</v>
       </c>
       <c r="H528" t="n">
         <v>204255</v>
@@ -15913,7 +15913,7 @@
         <v>12</v>
       </c>
       <c r="G536" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H536" t="n">
         <v>25535</v>
@@ -16000,7 +16000,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G539" t="n">
-        <v>11.4033393859863</v>
+        <v>11.4033403396606</v>
       </c>
       <c r="H539" t="n">
         <v>20898</v>
@@ -16087,7 +16087,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G542" t="n">
-        <v>11.4033393859863</v>
+        <v>11.4033403396606</v>
       </c>
       <c r="H542" t="n">
         <v>25345</v>
@@ -16203,7 +16203,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G546" t="n">
-        <v>11.4033393859863</v>
+        <v>11.4033403396606</v>
       </c>
       <c r="H546" t="n">
         <v>47534</v>
@@ -16261,7 +16261,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G548" t="n">
-        <v>11.7931985855103</v>
+        <v>11.7931976318359</v>
       </c>
       <c r="H548" t="n">
         <v>47029</v>
@@ -16348,7 +16348,7 @@
         <v>12</v>
       </c>
       <c r="G551" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H551" t="n">
         <v>30358</v>
@@ -16435,7 +16435,7 @@
         <v>12</v>
       </c>
       <c r="G554" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H554" t="n">
         <v>8761</v>
@@ -16464,7 +16464,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G555" t="n">
-        <v>11.7931985855103</v>
+        <v>11.7931976318359</v>
       </c>
       <c r="H555" t="n">
         <v>13533</v>
@@ -16493,7 +16493,7 @@
         <v>12</v>
       </c>
       <c r="G556" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H556" t="n">
         <v>5809</v>
@@ -16522,7 +16522,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G557" t="n">
-        <v>11.8906621932983</v>
+        <v>11.890661239624</v>
       </c>
       <c r="H557" t="n">
         <v>10698</v>
@@ -16609,7 +16609,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>11.7931985855103</v>
+        <v>11.7931976318359</v>
       </c>
       <c r="H560" t="n">
         <v>93481</v>
@@ -16638,7 +16638,7 @@
         <v>12</v>
       </c>
       <c r="G561" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H561" t="n">
         <v>34950</v>
@@ -16667,7 +16667,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G562" t="n">
-        <v>11.6470003128052</v>
+        <v>11.6470012664795</v>
       </c>
       <c r="H562" t="n">
         <v>15367</v>
@@ -16696,7 +16696,7 @@
         <v>12</v>
       </c>
       <c r="G563" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H563" t="n">
         <v>39064</v>
@@ -16725,7 +16725,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>11.7931985855103</v>
+        <v>11.7931976318359</v>
       </c>
       <c r="H564" t="n">
         <v>22959</v>
@@ -16754,7 +16754,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G565" t="n">
-        <v>11.6470003128052</v>
+        <v>11.6470012664795</v>
       </c>
       <c r="H565" t="n">
         <v>14206</v>
@@ -16812,7 +16812,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G567" t="n">
-        <v>11.7931985855103</v>
+        <v>11.7931976318359</v>
       </c>
       <c r="H567" t="n">
         <v>56931</v>
@@ -16841,7 +16841,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>11.7931985855103</v>
+        <v>11.7931976318359</v>
       </c>
       <c r="H568" t="n">
         <v>12168</v>
@@ -16957,7 +16957,7 @@
         <v>12</v>
       </c>
       <c r="G572" t="n">
-        <v>11.6957330703735</v>
+        <v>11.6957340240479</v>
       </c>
       <c r="H572" t="n">
         <v>50297</v>
@@ -17102,7 +17102,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G577" t="n">
-        <v>11.8906621932983</v>
+        <v>11.890661239624</v>
       </c>
       <c r="H577" t="n">
         <v>8377</v>
@@ -17827,7 +17827,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G602" t="n">
-        <v>12.7093639373779</v>
+        <v>12.7093629837036</v>
       </c>
       <c r="H602" t="n">
         <v>70858</v>
@@ -17885,7 +17885,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G604" t="n">
-        <v>12.6898717880249</v>
+        <v>12.6898708343506</v>
       </c>
       <c r="H604" t="n">
         <v>57453</v>
@@ -17943,7 +17943,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G606" t="n">
-        <v>12.8653059005737</v>
+        <v>12.865306854248</v>
       </c>
       <c r="H606" t="n">
         <v>71717</v>
@@ -18088,7 +18088,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G611" t="n">
-        <v>13.3136425018311</v>
+        <v>13.3136434555054</v>
       </c>
       <c r="H611" t="n">
         <v>69440</v>
@@ -18233,7 +18233,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G616" t="n">
-        <v>13.4500942230225</v>
+        <v>13.4500932693481</v>
       </c>
       <c r="H616" t="n">
         <v>45178</v>
@@ -18320,7 +18320,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G619" t="n">
-        <v>13.3136425018311</v>
+        <v>13.3136434555054</v>
       </c>
       <c r="H619" t="n">
         <v>22500</v>
@@ -18349,7 +18349,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G620" t="n">
-        <v>13.3136425018311</v>
+        <v>13.3136434555054</v>
       </c>
       <c r="H620" t="n">
         <v>23712</v>
@@ -18407,7 +18407,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G622" t="n">
-        <v>13.6255283355713</v>
+        <v>13.6255292892456</v>
       </c>
       <c r="H622" t="n">
         <v>54015</v>
@@ -18523,7 +18523,7 @@
         <v>14.5</v>
       </c>
       <c r="G626" t="n">
-        <v>14.1323442459106</v>
+        <v>14.132345199585</v>
       </c>
       <c r="H626" t="n">
         <v>143325</v>
@@ -29273,7 +29273,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="D997" t="n">
-        <v>22.8999996185303</v>
+        <v>23</v>
       </c>
       <c r="E997" t="n">
         <v>22.5499992370605</v>
@@ -29288,6 +29288,35 @@
         <v>13460</v>
       </c>
       <c r="I997" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="s">
+        <v>9</v>
+      </c>
+      <c r="B998" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C998" t="n">
+        <v>22.8999996185303</v>
+      </c>
+      <c r="D998" t="n">
+        <v>23.4500007629395</v>
+      </c>
+      <c r="E998" t="n">
+        <v>22.5499992370605</v>
+      </c>
+      <c r="F998" t="n">
+        <v>22.8500003814697</v>
+      </c>
+      <c r="G998" t="n">
+        <v>22.8500003814697</v>
+      </c>
+      <c r="H998" t="n">
+        <v>19686</v>
+      </c>
+      <c r="I998" t="s">
         <v>9</v>
       </c>
     </row>
